--- a/Turkcell-Destek-Sayfa-Onerileri-22-09-2026.xlsx
+++ b/Turkcell-Destek-Sayfa-Onerileri-22-09-2026.xlsx
@@ -1345,7 +1345,7 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Tek bir soru ve onun cevabını taşıyan sayfaları tanımlayan schema tipi.</t>
+          <t>Kullanıcıların bir soruya cevap ekleyebildiği sayfaları (forum gibi) tanımlayan schema tipi; site tarafından yazılan tek cevaplı sayfalarda kullanılmaz.</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Bir sayfadaki birden fazla soru-cevap bloğunu tanımlayan schema tipi.</t>
+          <t>Sitenin kendi yazdığı soru-cevap içeriğini tanımlayan schema tipi; tek soru ya da birden fazla soru taşıyabilir.</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Soru-cevap yapısının QAPage schema ile işaretlenmesi</t>
+          <t>Soru-cevap yapısının FAQPage schema ile işaretlenmesi</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -1905,20 +1905,19 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>Destek soru şablonuna QAPage tipinde JSON-LD eklenmelidir; soru metni H1'den, cevap metni cevap gövdesinden sunucu tarafında üretilmelidir. Mevcut BreadcrumbList ve WebPage blokları korunmalıdır. Ticari sayfaların SSS bölümlerinde (ör. /esim, /turkcellailem/) FAQPage kullanılmalıdır. İşaretleme, soft 404 düzeltmesi tamamlanmadan yaygınlaştırılmamalıdır; aksi halde başka sayfanın içeriğini gösteren adresler de soru-cevap olarak işaretlenir.</t>
+          <t>Destek soru şablonuna FAQPage tipinde JSON-LD eklenmelidir; tek Question içerir, soru metni H1'den, cevap metni cevap gövdesinden sunucu tarafında üretilmelidir. QAPage kullanılmamalıdır: Google yönergesine göre QAPage yalnızca kullanıcıların cevap ekleyebildiği sayfalar içindir; sitenin yazdığı tek cevaplı sayfalar bu kapsamda değildir. FAQ rich result Mayıs 2026'dan bu yana Google Arama'da gösterilmediği için işaretlemeden rich result beklenmez; amaç soru ve cevabın arama motorlarına ve yapay zeka araçlarına kodla bildirilmesidir. Mevcut BreadcrumbList ve WebPage blokları korunmalıdır. Ticari sayfaların SSS bölümlerinde (ör. /esim, /turkcellailem/) her soru ayrı Question olarak FAQPage'e eklenmelidir. İşaretleme, soft 404 düzeltmesi tamamlanmadan yaygınlaştırılmamalıdır; aksi halde başka sayfanın içeriğini gösteren adresler de soru-cevap olarak işaretlenir.</t>
         </is>
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
           <t>{
   "@context": "https://schema.org",
-  "@type": "QAPage",
-  "mainEntity": {
+  "@type": "FAQPage",
+  "mainEntity": [{
     "@type": "Question",
     "name": "&lt;H1&gt;",
-    "answerCount": 1,
-    "acceptedAnswer": {"@type": "Answer", "text": "&lt;cevap gövdesi&gt;", "url": "&lt;sayfa adresi&gt;"}
-  }
+    "acceptedAnswer": {"@type": "Answer", "text": "&lt;cevap gövdesinin düz metni&gt;"}
+  }]
 }</t>
         </is>
       </c>

--- a/Turkcell-Destek-Sayfa-Onerileri-22-09-2026.xlsx
+++ b/Turkcell-Destek-Sayfa-Onerileri-22-09-2026.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mevcut Sayfa Güçlendirme" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sitemap Dışı Adresler" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doğrulanacak Bilgiler" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mükerrer Sayfalar" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Duplicate Adresler" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rakip Karşılaştırması" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt Eşleştirme" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Terim Sözlüğü" sheetId="10" state="visible" r:id="rId10"/>
@@ -24,10 +24,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Mevcut Sayfa Güçlendirme'!$A$4:$O$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sitemap Dışı Adresler'!$A$4:$L$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Doğrulanacak Bilgiler'!$A$4:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Mükerrer Sayfalar'!$A$4:$G$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Duplicate Adresler'!$A$4:$G$129</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Rakip Karşılaştırması'!$A$4:$K$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Prompt Eşleştirme'!$A$4:$G$104</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Terim Sözlüğü'!$A$4:$C$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Terim Sözlüğü'!$A$4:$C$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -822,7 +822,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Soft 404 adresi</t>
+          <t xml:space="preserve">  Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="B17" s="6">
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B21" s="6">
-        <f>COUNTA('Mükerrer Sayfalar'!C5:C1000)</f>
+        <f>COUNTA('Duplicate Adresler'!C5:C1000)</f>
         <v/>
       </c>
       <c r="C21" s="7" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1204,12 +1204,12 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Canonical</t>
+          <t>Duplicate adres</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>Aynı içeriğe birden çok adresten ulaşılabildiğinde 'asıl adres budur' diyen işaret.</t>
+          <t>Aynı başlığı ve cevabı taşıyan birden fazla adres; tek adreste birleştirilmesi önerilir.</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>Canonical</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Bir adresin kalıcı olarak başka bir adrese taşındığını bildiren yönlendirme.</t>
+          <t>Aynı içeriğe birden çok adresten ulaşılabildiğinde 'asıl adres budur' diyen işaret.</t>
         </is>
       </c>
     </row>
@@ -1238,12 +1238,12 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>404 / 410</t>
+          <t>301</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>Sayfanın bulunamadığını (404) ya da kalıcı olarak kaldırıldığını (410) bildiren yanıt kodu.</t>
+          <t>Bir adresin kalıcı olarak başka bir adrese taşındığını bildiren yönlendirme.</t>
         </is>
       </c>
     </row>
@@ -1255,12 +1255,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>404 / 410</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>Gerçekte var olmayan bir adresin hata kodu yerine 200 dönüp başka bir içerik göstermesi.</t>
+          <t>Sayfanın bulunamadığını (404) ya da kalıcı olarak kaldırıldığını (410) bildiren yanıt kodu.</t>
         </is>
       </c>
     </row>
@@ -1272,12 +1272,12 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Sitemap</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Sitenin arama motorlarına bildirdiği sayfa listesi dosyası.</t>
+          <t>Gerçekte var olmayan bir adresin hata kodu yerine 200 dönüp başka bir sayfanın içeriğini tekrar etmesi.</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>Internal linking</t>
+          <t>Sitemap</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>Site içindeki sayfaların birbirine verdiği bağlantılar.</t>
+          <t>Sitenin arama motorlarına bildirdiği sayfa listesi dosyası.</t>
         </is>
       </c>
     </row>
@@ -1306,29 +1306,29 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>SERP</t>
+          <t>Internal linking</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>Arama sonuç sayfası.</t>
+          <t>Site içindeki sayfaların birbirine verdiği bağlantılar.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="17" t="inlineStr">
         <is>
-          <t>Yapısal veri</t>
+          <t>SEO</t>
         </is>
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>Schema / JSON-LD</t>
+          <t>SERP</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>Sayfadaki içeriğin ne olduğunu arama motoruna makine tarafından okunabilir biçimde bildiren etiket.</t>
+          <t>Arama sonuç sayfası.</t>
         </is>
       </c>
     </row>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>QAPage</t>
+          <t>Schema / JSON-LD</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Kullanıcıların bir soruya cevap ekleyebildiği sayfaları (forum gibi) tanımlayan schema tipi; site tarafından yazılan tek cevaplı sayfalarda kullanılmaz.</t>
+          <t>Sayfadaki içeriğin ne olduğunu arama motoruna makine tarafından okunabilir biçimde bildiren etiket.</t>
         </is>
       </c>
     </row>
@@ -1357,29 +1357,29 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>FAQPage</t>
+          <t>QAPage</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>Sitenin kendi yazdığı soru-cevap içeriğini tanımlayan schema tipi; tek soru ya da birden fazla soru taşıyabilir.</t>
+          <t>Kullanıcıların bir soruya cevap ekleyebildiği sayfaları (forum gibi) tanımlayan schema tipi; site tarafından yazılan tek cevaplı sayfalarda kullanılmaz.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="17" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>Yapısal veri</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>FAQPage</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>İçeriğin yapay zeka cevaplarında kaynak olarak seçilmesine yönelik çalışma.</t>
+          <t>Sitenin kendi yazdığı soru-cevap içeriğini tanımlayan schema tipi; tek soru ya da birden fazla soru taşıyabilir.</t>
         </is>
       </c>
     </row>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>AI Overview</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>Google'ın arama sonuçlarının üstünde gösterdiği yapay zeka özet paneli.</t>
+          <t>İçeriğin yapay zeka cevaplarında kaynak olarak seçilmesine yönelik çalışma.</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>AI Overview</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>People Also Ask; arama sonuçlarındaki İlgili sorular paneli.</t>
+          <t>Google'ın arama sonuçlarının üstünde gösterdiği yapay zeka özet paneli.</t>
         </is>
       </c>
     </row>
@@ -1425,29 +1425,29 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>Prompt</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>Kullanıcının yapay zeka aracına yazdığı soru ya da talep.</t>
+          <t>People Also Ask; arama sonuçlarındaki İlgili sorular paneli.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>Teknik</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>USSD kodu</t>
+          <t>Prompt</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>Telefonun tuş takımından girilen ve * ile # içeren servis kodu (ör. *#06#).</t>
+          <t>Kullanıcının yapay zeka aracına yazdığı soru ya da talep.</t>
         </is>
       </c>
     </row>
@@ -1459,17 +1459,34 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
+          <t>USSD kodu</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="inlineStr">
+        <is>
+          <t>Telefonun tuş takımından girilen ve * ile # içeren servis kodu (ör. *#06#).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>Teknik</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
           <t>APN</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C29" s="14" t="inlineStr">
         <is>
           <t>Telefonun mobil internete bağlanmak için kullandığı erişim noktası ayarı.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C28"/>
+  <autoFilter ref="A4:C29"/>
   <mergeCells count="1">
     <mergeCell ref="A2:C2"/>
   </mergeCells>
@@ -1632,12 +1649,12 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Var olmayan destek adreslerinin 200 dönüp başka sayfanın içeriğini göstermesi (soft 404)</t>
+          <t>Soft 404 - tekrar eden sayfalar: yayında olmayan adreslerin başka sayfanın içeriğini göstermesi</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Geçerli bir kategori ve alt bölüm altında yayında olmayan bir soru adresi istendiğinde sunucu 200 status code döndürmekte, alt bölümdeki başka bir sayfanın içeriğini göstermekte, adresin kendisine canonical vermekte ve index,follow taşımaktadır (test: /destek/tarife-ve-paketler/konusma/bu-sayfa-yok-deneme-xyz, 14 Eyl 2026). Geçersiz kategori ya da alt bölüm altında adres doğru biçimde 404 dönmektedir. Search Console'da 1 Eyl 2025 - 31 Ağu 2026 penceresinde bu davranışı gösteren 30 adres görülmüştür: 26 adres başka bir sayfanın içeriğini göstermekte (215.336 impression, 6.790 tıklama), 4 adres ise gerçek bir sayfanın yazım varyantı olarak kopyasını sunmaktadır (95.306 impression). Toplam 310.642 impression.</t>
+          <t>Geçerli bir kategori ve alt bölüm altında yayında olmayan bir soru adresi istendiğinde sunucu 200 status code döndürmekte, alt bölümdeki başka bir sayfanın içeriğini göstermekte, adresin kendisine canonical vermekte ve index,follow taşımaktadır (test: /destek/tarife-ve-paketler/konusma/bu-sayfa-yok-deneme-xyz, 14 Eyl 2026). Geçersiz kategori ya da alt bölüm altında adres doğru biçimde 404 dönmektedir. Search Console'da 1 Eyl 2025 - 31 Ağu 2026 penceresinde bu davranışı gösteren 28 adres görülmüştür: 24 adres başka bir sayfanın içeriğini tekrar etmekte (212.184 impression, 5.168 tıklama), 4 adres ise gerçek bir sayfanın yazım varyantı olarak kopyasını sunmaktadır (95.306 impression). Toplam 307.490 impression. Şikayet talebi oluşturma ve Pasaj satıcı sayfaları kendi içeriğini gösterdiği için bu listeye alınmamıştır.</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
@@ -1647,7 +1664,7 @@
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>Var olmayan destek adresleri 404 (kalıcı olarak kaldırılanlar için 410) status code döndürmelidir. Kaldırılmış soru sayfalarının adresleri, sorunun güncel cevabını veren sayfaya 301 ile yönlendirilmelidir (adres bazlı liste 'Kaldırılmış soru sayfaları' maddesinde). Yazım varyantı adresler gerçek adrese 301 ile yönlendirilmeli; canonical, istenen adrese değil gösterilen içeriğin asıl adresine verilmelidir. Yeni önerilen sayfalar yayına alınmadan önce önerilen adreslerin bu davranış nedeniyle zaten 200 döndüğü dikkate alınmalıdır.</t>
+          <t>Var olmayan destek adresleri 404 (kalıcı olarak kaldırılanlar için 410) status code döndürmelidir. Kaldırılmış soru sayfalarının adresleri, sorunun güncel cevabını veren sayfaya 301 ile yönlendirilmelidir (adres bazlı liste 'Kaldırılmış soru sayfaları' maddesinde ve aksiyon listesinin Soft 404 - tekrar eden sayfalar sekmesinde). Yazım varyantı adresler gerçek adrese 301 ile yönlendirilmeli; canonical, istenen adrese değil gösterilen içeriğin asıl adresine verilmelidir. Yeni önerilen sayfalar yayına alınmadan önce önerilen adreslerin bu davranış nedeniyle zaten 200 döndüğü dikkate alınmalıdır.</t>
         </is>
       </c>
       <c r="H5" s="15" t="inlineStr">
@@ -1664,7 +1681,7 @@
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
-          <t>30 adres · 310.642 impression (Search Console, 1 Eyl 2025 - 31 Ağu 2026)</t>
+          <t>28 adres · 307.490 impression (Search Console, 1 Eyl 2025 - 31 Ağu 2026) + şablon kuralı</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1716,7 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>Adreslerin sitemap dosyasına eklenmesi, H1 bulunmayan araç sayfalarına sayfa konusunu tarif eden bir H1 eklenmesi ve 'Numaramı nasıl taşıyabilirim?' sayfasının dijital başvuru kanallarını da içerecek şekilde güncellenmesi önerilir. '/destek/turkcell-akademi' adresi destek ana sayfasına yönlendiği için sitemap'e eklenmemelidir.</t>
+          <t>Adreslerin sitemap dosyasına eklenmesi ve H1 bulunmayan araç ve form sayfalarına (şikayet talebi oluşturma dahil) sayfa konusunu tarif eden title ve H1 eklenmesi önerilir. 'Numaramı nasıl taşıyabilirim?' sayfası noindex ve canonical'i paket seçimi sayfasına veriyor; canonical'in yönlenen /trc/turkcellli-olmak/paket-secimi yerine son adrese (/turkcellli-olmak/paket-secimi) verilmesi, sayfanın sitemap'e eklenmemesi önerilir. '/destek/turkcell-akademi' adresi destek ana sayfasına yönlendiği için sitemap'e eklenmemelidir.</t>
         </is>
       </c>
       <c r="H6" s="15" t="inlineStr">
@@ -1751,26 +1768,39 @@
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>Aşağıdaki eşleme uygulanmalıdır. Yeniden açılacak iki adres (paket aşım ücreti ve tarife bilgisi sorgulama), arama geçmişini korumak için aynı adreste yeni içerikle yayınlanmalıdır. Yönlendirilecek adreslerde 301 hedefi, gösterilen içeriğin değil sorunun cevabını veren sayfanın adresi olmalıdır.</t>
+          <t>Aşağıdaki eşleme uygulanmalıdır. Hedefler, her adresin Search Console sorguları ve hedef sayfanın canlı içeriği karşılaştırılarak belirlenmiştir; 301 hedefi, adreste bugün görünen içeriğin değil, adresin aldığı sorguları cevaplayan sayfanın adresidir. Paket aşım ücreti adresi, arama geçmişini korumak için aynı adreste yeni içerikle yayınlanmalıdır.</t>
         </is>
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>/destek/online-alisveris/odeme/paycell-dijital-para-ile-odeme-secenegi-nedir · 73.878 impression → 301 → /servisler/uygulamalar/paycell ('paycell nedir' talebi)
+          <t>/destek/hattiniz/faturali/faturami-son-odeme-tarihinde-odenmedigimde-hattimin-kisitlanma-ve-durdurma-sure-ve-surecleri-nelerdir · 95.156 impression → 301 → /destek/hattiniz/faturali/faturami-son-odeme-tarihinde-odemedigimde-hattimin-kisitlanma-ve-durdurma-sure-ve-surecleri-nelerdir
+/destek/online-alisveris/odeme/paycell-dijital-para-ile-odeme-secenegi-nedir · 73.878 impression → 301 → /servisler/uygulamalar/paycell
 /destek/hizmet-kanallarimiz/musteri-hizmetleri/bip-turkcell-musteri-hizmetleri · 34.940 impression → 301 → /destek/hizmet-kanallarimiz/musteri-hizmetleri/532-turkcell-musteri-hizmetleri
-/destek/kampanya/kampanyalar-faturali/numara-tasima-nedir · 31.695 impression → 301 → /destek/turkcellli-olmak/numara-tasima/numara-tasima-nedir
-/destek/tarife-ve-paketler/konusma/paket-asim-ucreti-nedir · 24.167 impression → İçerik olarak yeniden açılmalı: yeni sayfa seti 'Paket aşımı nedir, paket bittikten sonra aşım nasıl kapatılır?'
+/destek/kampanya/kampanyalar-faturali/numara-tasima-nedir · 31.695 impression → 301 → /turkcellli-olmak/paket-secimi
+/destek/tarife-ve-paketler/konusma/paket-asim-ucreti-nedir · 24.167 impression → aynı adreste yeni içerikle yeniden açılış
 /destek/online-alisveris/odeme/faturama-yansit-odeme-secenegi-nedir · 11.454 impression → 301 → /servisler/arama-fatura-tl/turkcellmobilodeme
-/destek/tarife-ve-paketler/konusma/tarife-bilgilerimi-nasil-sorgularim · 6.518 impression → İçerik olarak yeniden açılmalı: yeni sayfa seti 'Tarife bilgilerimi nasıl sorgularım, mevcut tarifem nasıl öğrenilir?'
-/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/turkcell-hesabimda-servislerim-sayfasindan-hangi-bilgilere-ulasabilirim · 5.510 impression → 301 → /destek/islem-merkezi/hat-ozetim/hat-ozetim-nedir
-/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/turkcell-hesabimda-kampanyalarimla-hangi-islemleri-yapabilirim · 5.152 impression → 301 → /destek/islem-merkezi/hat-ozetim/hat-ozetim-nedir
-/destek/servisler-ve-internet/servisler/avans-tl-nedir-nasil-abone-olurum · 4.580 impression → Servisin yayında olup olmadığı marka tarafından teyit edilmeli; yayında değilse 410
-/destek/kampanya/kampanyalar-faturali/numarami-nasil-tasiyabilirim · 4.541 impression → 301 → /destek/turkcellli-olmak/numara-tasima/numarami-nasil-tasiyabilirim
-/destek/tuketici-sikayetleri/sikayet-talebi-olusturma · 3.123 impression → H1 ve title boş dönüyor; form sayfasının güncel adresi teyit edilmeli (1.614 tıklama alıyor)
+/destek/tarife-ve-paketler/konusma/tarife-bilgilerimi-nasil-sorgularim · 6.518 impression → 301 → /paket-ve-tarifeler
+/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/turkcell-hesabimda-servislerim-sayfasindan-hangi-bilgilere-ulasabilirim · 5.510 impression → 301 → /destek/islem-merkezi
+/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/turkcell-hesabimda-kampanyalarimla-hangi-islemleri-yapabilirim · 5.152 impression → 301 → /destek/islem-merkezi
+/destek/servisler-ve-internet/servisler/avans-tl-nedir-nasil-abone-olurum · 4.580 impression → 410 dönmesi (Avans TL servis sayfası da kaldırılmış)
+/destek/kampanya/kampanyalar-faturali/numarami-nasil-tasiyabilirim · 4.541 impression → 301 → /turkcellli-olmak/paket-secimi
 /destek/turkcellli-olmak/turkcellli-olmak/nasil-hazirkart-alirim · 2.934 impression → 301 → /destek/turkcellli-olmak/numara-tasima/nasil-hazirkart-alirim
+/destek/turkcell-akademi/sikca-sorulan-sorular/turkcell-akademi-egitimlerine-nereden-ulasabilirim · 2.481 impression → 301 → https://tag.turkcell.com.tr/
 /destek/servisler-ve-internet/servisler/kredi-transfer-nedir · 1.268 impression → 301 → /destek/hattiniz/hazirkart/kreditransfer-nedir
-/destek/servisler-ve-internet/servisler/telefonumu-mobil-odeme-kullanimina-nasil-acabilirim · 1.227 impression → 301 → /servisler/arama-fatura-tl/turkcellmobilodeme
-/destek/kampanya/kampanyalar-faturali/numarami-tasirken-hattim-kullanima-kapanir-mi · 779 impression → 301 → /destek/turkcellli-olmak/numara-tasima/numarami-tasirken-hattim-kullanima-kapanir-mi</t>
+/destek/servisler-ve-internet/servisler/telefonumu-mobil-odeme-kullanimina-nasil-acabilirim · 1.227 impression → 301 → /servisler/arama-fatura-tl/yonlendir
+/destek/kampanya/kampanyalar-faturali/numarami-tasirken-hattim-kullanima-kapanir-mi · 779 impression → 301 → /destek/turkcellli-olmak/numara-tasima/numarami-tasirken-hattim-kullanima-kapanir-mi
+/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/paket-ve-tarifelerim-sayfasindan-hangi-islemleri-yapabilirim · 382 impression → 301 → /destek/islem-merkezi
+/destek/sosyal-destek-iletisim · 257 impression → 301 → /sosyal-destek
+/destek/turkcell-akademi/sikca-sorulan-sorular/mevcut-egitimlerden-baska-egitimler-olacak-mi · 172 impression → 301 → https://tag.turkcell.com.tr/
+/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/tl-ayarlarim-sayfasindan-hangi-ayarlari-yapabilirim · 145 impression → 404 ya da 410 dönmesi (karşılayan sayfa yok)
+/destek/islem-merkezi/ayarlarim/arayan-numarayi-goster-clip-ozelligi-nedir · 129 impression → 301 → /destek/hattiniz/sikca-sorulan-sorular/arayan-numarayi-goster-clip-ozelligi-nedir
+/destek/tarife-ve-paketler/konusma/tarifemi-nerden-ogrenebilirim-ve-nasil-degistirebilirim · 55 impression → 301 → /destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim
+/kurumsal/destek/hattiniz/faturali/hattimi-gecici-olarak- · 33 impression → 301 → /kurumsal/destek/hattiniz/faturali/hattimi-gecici-olarak-gelen-ve-gelen-giden-iletisime-ne-kadar-sureyle-kapatabilirim-ve-faturama-herhangi-bir-ucret-yansir-m
+/destek/islem-merkezi/ayarlarim/hat-iptalimi-nasil-gerceklestirebilirim · 14 impression → 301 → /destek/hattiniz/abonelik-islemleri/hattimi-nasil-iptal-ettirebilirim
+/destek/financell/ucretlendirme/financell-kredi-taksitlerim-disinda-odemem-gereken · 14 impression → 301 → /destek/financell/ucretlendirme/financell-kredi-taksitlerim-disinda-odemem-gereken-diger-ucretler-nelerdir
+/destek/financell/paycell-alisveris-limiti/online-alisverislerde-paycell-alisveris-limiti-nasil-kullanilir · 7 impression → 301 → /destek/financell/paycell-alisveris-limiti/online-alisverislerde-paycell-alisveris-limiti-nasil-kullanilir
+/destek/hizmet-kanallarimiz/musteri-hizmetleri/gencaver · 1 impression → 404 ya da 410 dönmesi
+/destek/online-alisveris · 1 impression → 301 → /destek/online-alisveris</t>
         </is>
       </c>
       <c r="I7" s="14" t="inlineStr">
@@ -1865,7 +1895,7 @@
           <t>Kurumsal: /kurumsal/destek/hattiniz/hazirkart/telsiz-kullanim-ucreti-nedir
 Bireysel: /destek/hattiniz/hazirkart/telsiz-kullanim-ucreti
 Kurumsal: /kurumsal/destek/tarife-ve-paketler/konusma/tarife-bilgilerimi-nasil-sorgularim
-Bireysel: önerilen /destek/tarife-ve-paketler/konusma/tarife-bilgilerimi-nasil-sorgularim (yeniden açılış)</t>
+Bireysel: önerilen /destek/tarife-ve-paketler/konusma/mevcut-tarifemi-nasil-ogrenebilirim (yeniden açılış)</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
@@ -1943,7 +1973,7 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Aynı içeriği taşıyan adreslerin birleştirilmesi</t>
+          <t>Duplicate adreslerin birleştirilmesi (aynı içeriği taşıyan adresler)</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -4244,7 +4274,7 @@
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarife-bilgilerimi-nasil-sorgularim</t>
+          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/mevcut-tarifemi-nasil-ogrenebilirim</t>
         </is>
       </c>
       <c r="E21" s="17" t="inlineStr">
@@ -4300,7 +4330,7 @@
 • Search Console: 25.689 impression · 1.390 click · ağırlıklı konum 4,6
 • Tıklama alan sayfa: https://www.turkcell.com.tr/kurumsal/destek/tarife-ve-paketler/konusma/tarife-bilgilerimi-nasil-sorgularim
 • Bireysel destekte bu soruyu cevaplayan sayfa bir dönem yayındaydı; adres bugün başka bir sayfanın içeriğini gösterdiği için talep kurumsal kopyaya kaymaktadır.
-• Adres bugün başka bir sayfanın içeriğini göstermekte ancak arama talebi almaya devam etmektedir; sayfanın aynı adreste yeniden açılması önerilir.</t>
+• Eski bireysel adresin kendi sorguları genel paket ve tarife araması olduğundan eski adres /paket-ve-tarifeler sayfasına yönlendirilir; sayfa yeni adreste açılır.</t>
         </is>
       </c>
       <c r="Q21" s="14" t="inlineStr">
@@ -7958,7 +7988,7 @@
               <color rgb="00FF7B52"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Mükerrer adresler: </t>
+            <t xml:space="preserve">Duplicate adresler: </t>
           </r>
           <r>
             <rPr>
@@ -8025,7 +8055,7 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>Mükerrer adresler</t>
+          <t>Duplicate adresler</t>
         </is>
       </c>
       <c r="H4" s="10" t="inlineStr">
@@ -12315,7 +12345,7 @@
               <color rgb="0010332F"/>
               <sz val="10"/>
             </rPr>
-            <t>Sayfa yayında ve doğru içeriği gösteriyor; Önerilen işlem sütunundaki düzenleme uygulanır.</t>
+            <t>Sayfa yayında ve kendi içeriğini gösteriyor; Önerilen işlem sütunundaki düzenleme uygulanır.</t>
           </r>
           <r>
             <t>
@@ -12328,7 +12358,7 @@
               <color rgb="00FF7B52"/>
               <sz val="10"/>
             </rPr>
-            <t xml:space="preserve">Soft 404: </t>
+            <t xml:space="preserve">Soft 404 - tekrar eden sayfa: </t>
           </r>
           <r>
             <rPr>
@@ -12336,7 +12366,7 @@
               <color rgb="0010332F"/>
               <sz val="10"/>
             </rPr>
-            <t>Adres yayında değil ama 404 yerine 200 dönüyor. Görünen H1 ve cevap başka bir sayfaya aittir (asıl adresi İçeriğin asıl adresi sütununda); canonical açılan adresin kendisine veriliyor ve adres indekslenebilir durumda.</t>
+            <t>Adres yayında değil ama 404 yerine 200 dönüyor ve başka bir sayfanın içeriğini tekrar ediyor. Görünen H1 ve cevap başka bir sayfaya aittir (asıl adresi İçeriğin asıl adresi sütununda); canonical açılan adresin kendisine veriliyor ve adres indekslenebilir durumda.</t>
           </r>
           <r>
             <t>
@@ -12582,7 +12612,7 @@
       </c>
       <c r="L7" s="14" t="inlineStr">
         <is>
-          <t>noindex etiketinin kaldırılması, canonical'in kendi adresine verilmesi ve sitemap'e eklenmesi</t>
+          <t>Canonical'in yönlenen /trc/turkcellli-olmak/paket-secimi yerine son adrese (/turkcellli-olmak/paket-secimi) verilmesi; sayfa noindex olduğu için sitemap'e eklenmemesi</t>
         </is>
       </c>
     </row>
@@ -12759,7 +12789,7 @@
       </c>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/kurumsal/destek/cihaz-satisi</t>
+          <t>https://www.turkcell.com.tr/destek/tuketici-sikayetleri/sikayet-talebi-olusturma</t>
         </is>
       </c>
       <c r="D11" s="11" t="n">
@@ -12777,12 +12807,12 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>Cihaz Satışı</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>Cihaz Satışı</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">
@@ -12791,14 +12821,14 @@
         </is>
       </c>
       <c r="J11" s="19" t="n">
-        <v>35</v>
+        <v>3123</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>11</v>
+        <v>1614</v>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>Sitemap'e eklenmesi</t>
+          <t>Çalışan şikayet formu; title ve H1 boş dönüyor. Title ve H1 eklenmesi, sitemap'e eklenmesi</t>
         </is>
       </c>
     </row>
@@ -12806,14 +12836,14 @@
       <c r="A12" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>Soft 404 · yazım varyantı</t>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>Açık sayfa · sitemap'te yok</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/hattiniz/faturali/faturami-son-odeme-tarihinde-odenmedigimde-hattimin-kisitlanma-ve-durdurma-sure-ve-surecleri-nelerdir</t>
+          <t>https://www.turkcell.com.tr/kurumsal/destek/cihaz-satisi</t>
         </is>
       </c>
       <c r="D12" s="11" t="n">
@@ -12831,28 +12861,28 @@
       </c>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>Faturamı Son Ödeme Tarihinde Ödenmediğimde Hattımın Kısıtlanma ve Durdurma Süre ve Süreçleri Nelerdir?</t>
+          <t>Cihaz Satışı</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Faturamı son ödeme tarihinde ödemediğimde hattımın kısıtlanma ve durdurma süre ve süreçleri nelerdir?</t>
+          <t>Cihaz Satışı</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/hattiniz/faturali/faturami-son-odeme-tarihinde-odemedigimde-hattimin-kisitlanma-ve-durdurma-sure-ve-surecleri-nelerdir</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" s="19" t="n">
-        <v>95156</v>
+        <v>35</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>8406</v>
+        <v>11</v>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>Doğru adrese 301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/hattiniz/faturali/faturami-son-odeme-tarihinde-odemedigimde-hattimin-kisitlanma-ve-durdurma-sure-ve-surecleri-nelerdir</t>
+          <t>Sitemap'e eklenmesi</t>
         </is>
       </c>
     </row>
@@ -12860,14 +12890,14 @@
       <c r="A13" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>Soft 404</t>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>Açık sayfa · sitemap'te yok</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/online-alisveris/odeme/paycell-dijital-para-ile-odeme-secenegi-nedir</t>
+          <t>https://www.turkcell.com.tr/destek/online-alisveris/turkcell-pasaj/turkcell-pasajda-satici-olmak-istiyorum-nereye-basvurabilirim</t>
         </is>
       </c>
       <c r="D13" s="11" t="n">
@@ -12880,33 +12910,33 @@
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>index,follow</t>
+          <t>noindex,nofollow</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>Paycell Dijital Para ile Ödeme Seçeneği Nedir?</t>
+          <t>Turkcell Pasaj’da Satıcı Olmak İstiyorum, Nereye Başvurabilirim?</t>
         </is>
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>Ödeme seçeneklerim nelerdir?</t>
+          <t>Turkcell Pasaj'da satıcı olmak istiyorum.</t>
         </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/online-alisveris/odeme/odeme-seceneklerim-nelerdir</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J13" s="19" t="n">
-        <v>73878</v>
+        <v>29</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>2239</v>
+        <v>8</v>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/servisler/uygulamalar/paycell</t>
+          <t>Kendi içeriğini gösteriyor, bilinçli olarak noindex; işlem gerekmiyor</t>
         </is>
       </c>
     </row>
@@ -12916,12 +12946,12 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa · yazım varyantı</t>
         </is>
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/hizmet-kanallarimiz/musteri-hizmetleri/bip-turkcell-musteri-hizmetleri</t>
+          <t>https://www.turkcell.com.tr/destek/hattiniz/faturali/faturami-son-odeme-tarihinde-odenmedigimde-hattimin-kisitlanma-ve-durdurma-sure-ve-surecleri-nelerdir</t>
         </is>
       </c>
       <c r="D14" s="11" t="n">
@@ -12939,28 +12969,28 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>BiP Turkcell Müşteri Hizmetleri | Turkcell Destek</t>
+          <t>Faturamı Son Ödeme Tarihinde Ödenmediğimde Hattımın Kısıtlanma ve Durdurma Süre ve Süreçleri Nelerdir?</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Turkcell Hizmet</t>
+          <t>Faturamı son ödeme tarihinde ödemediğimde hattımın kısıtlanma ve durdurma süre ve süreçleri nelerdir?</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/hizmet-kanallarimiz/musteri-hizmetleri/turkcell-hizmet</t>
+          <t>https://www.turkcell.com.tr/destek/hattiniz/faturali/faturami-son-odeme-tarihinde-odemedigimde-hattimin-kisitlanma-ve-durdurma-sure-ve-surecleri-nelerdir</t>
         </is>
       </c>
       <c r="J14" s="19" t="n">
-        <v>34940</v>
+        <v>95156</v>
       </c>
       <c r="K14" s="19" t="n">
-        <v>277</v>
+        <v>8406</v>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/hizmet-kanallarimiz/musteri-hizmetleri/532-turkcell-musteri-hizmetleri</t>
+          <t>Doğru adrese 301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/hattiniz/faturali/faturami-son-odeme-tarihinde-odemedigimde-hattimin-kisitlanma-ve-durdurma-sure-ve-surecleri-nelerdir</t>
         </is>
       </c>
     </row>
@@ -12970,12 +13000,12 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/kampanya/kampanyalar-faturali/numara-tasima-nedir</t>
+          <t>https://www.turkcell.com.tr/destek/online-alisveris/odeme/paycell-dijital-para-ile-odeme-secenegi-nedir</t>
         </is>
       </c>
       <c r="D15" s="11" t="n">
@@ -12993,28 +13023,28 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>Numara Taşıma Kampanyaları Nelerdir?</t>
+          <t>Paycell Dijital Para ile Ödeme Seçeneği Nedir?</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>Numaramı taşımak ücretli midir?</t>
+          <t>Ödeme seçeneklerim nelerdir?</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numarami-tasimak-ucretli-midir</t>
+          <t>https://www.turkcell.com.tr/destek/online-alisveris/odeme/odeme-seceneklerim-nelerdir</t>
         </is>
       </c>
       <c r="J15" s="19" t="n">
-        <v>31695</v>
+        <v>73878</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>729</v>
+        <v>2239</v>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numara-tasima-nedir</t>
+          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/servisler/uygulamalar/paycell</t>
         </is>
       </c>
     </row>
@@ -13024,12 +13054,12 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/paket-asim-ucreti-nedir</t>
+          <t>https://www.turkcell.com.tr/destek/hizmet-kanallarimiz/musteri-hizmetleri/bip-turkcell-musteri-hizmetleri</t>
         </is>
       </c>
       <c r="D16" s="11" t="n">
@@ -13047,28 +13077,28 @@
       </c>
       <c r="G16" s="14" t="inlineStr">
         <is>
-          <t>Paket Aşım Ücreti Nedir? | Turkcell Destek</t>
+          <t>BiP Turkcell Müşteri Hizmetleri | Turkcell Destek</t>
         </is>
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Paket / Tarife değişikliğini nasıl yapabilirim?</t>
+          <t>Turkcell Hizmet</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim</t>
+          <t>https://www.turkcell.com.tr/destek/hizmet-kanallarimiz/musteri-hizmetleri/turkcell-hizmet</t>
         </is>
       </c>
       <c r="J16" s="19" t="n">
-        <v>24167</v>
+        <v>34940</v>
       </c>
       <c r="K16" s="19" t="n">
-        <v>202</v>
+        <v>277</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>Aynı adreste yeni içerikle yeniden açılması</t>
+          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/hizmet-kanallarimiz/musteri-hizmetleri/532-turkcell-musteri-hizmetleri</t>
         </is>
       </c>
     </row>
@@ -13078,12 +13108,12 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/online-alisveris/odeme/faturama-yansit-odeme-secenegi-nedir</t>
+          <t>https://www.turkcell.com.tr/destek/kampanya/kampanyalar-faturali/numara-tasima-nedir</t>
         </is>
       </c>
       <c r="D17" s="11" t="n">
@@ -13101,28 +13131,28 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>Faturama Yansıt Ödeme Seçeneği Nedir?</t>
+          <t>Numara Taşıma Kampanyaları Nelerdir?</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>Ödeme seçeneklerim nelerdir?</t>
+          <t>Numaramı taşımak ücretli midir?</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/online-alisveris/odeme/odeme-seceneklerim-nelerdir</t>
+          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numarami-tasimak-ucretli-midir</t>
         </is>
       </c>
       <c r="J17" s="19" t="n">
-        <v>11454</v>
+        <v>31695</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>944</v>
+        <v>729</v>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/servisler/arama-fatura-tl/turkcellmobilodeme</t>
+          <t>301 ile yönlendirilmesi (sorgular numara taşıma kampanyası ve tarifesi arıyor): https://www.turkcell.com.tr/turkcellli-olmak/paket-secimi</t>
         </is>
       </c>
     </row>
@@ -13132,12 +13162,12 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarife-bilgilerimi-nasil-sorgularim</t>
+          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/paket-asim-ucreti-nedir</t>
         </is>
       </c>
       <c r="D18" s="11" t="n">
@@ -13155,24 +13185,24 @@
       </c>
       <c r="G18" s="14" t="inlineStr">
         <is>
+          <t>Paket Aşım Ücreti Nedir? | Turkcell Destek</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
+        <is>
           <t>Paket / Tarife değişikliğini nasıl yapabilirim?</t>
         </is>
       </c>
-      <c r="H18" s="14" t="inlineStr">
-        <is>
-          <t>Paket / Tarife değişikliğini nasıl yapabilirim?</t>
-        </is>
-      </c>
       <c r="I18" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim</t>
         </is>
       </c>
       <c r="J18" s="19" t="n">
-        <v>6518</v>
+        <v>24167</v>
       </c>
       <c r="K18" s="19" t="n">
-        <v>66</v>
+        <v>202</v>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
@@ -13186,12 +13216,12 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/turkcell-hesabimda-servislerim-sayfasindan-hangi-bilgilere-ulasabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/online-alisveris/odeme/faturama-yansit-odeme-secenegi-nedir</t>
         </is>
       </c>
       <c r="D19" s="11" t="n">
@@ -13209,28 +13239,28 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>Servislerim Sayfasında Hangi Bilgiler Var?</t>
+          <t>Faturama Yansıt Ödeme Seçeneği Nedir?</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>Hat Özetimde hattım ile ilgili hangi bilgilere ulaşabilirim?</t>
+          <t>Ödeme seçeneklerim nelerdir?</t>
         </is>
       </c>
       <c r="I19" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/hat-ozetimde-hattim-ile-ilgili-hangi-bilgilere-ulasabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/online-alisveris/odeme/odeme-seceneklerim-nelerdir</t>
         </is>
       </c>
       <c r="J19" s="19" t="n">
-        <v>5510</v>
+        <v>11454</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>7</v>
+        <v>944</v>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/islem-merkezi/hat-ozetim/hat-ozetim-nedir</t>
+          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/servisler/arama-fatura-tl/turkcellmobilodeme</t>
         </is>
       </c>
     </row>
@@ -13240,12 +13270,12 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/turkcell-hesabimda-kampanyalarimla-hangi-islemleri-yapabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarife-bilgilerimi-nasil-sorgularim</t>
         </is>
       </c>
       <c r="D20" s="11" t="n">
@@ -13263,28 +13293,28 @@
       </c>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>Kampanyalarım Sayfasında Hangi İşlemleri Yapabilirim?</t>
+          <t>Paket / Tarife değişikliğini nasıl yapabilirim?</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>Hat Özetimde hattım ile ilgili hangi bilgilere ulaşabilirim?</t>
+          <t>Paket / Tarife değişikliğini nasıl yapabilirim?</t>
         </is>
       </c>
       <c r="I20" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/hat-ozetimde-hattim-ile-ilgili-hangi-bilgilere-ulasabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim</t>
         </is>
       </c>
       <c r="J20" s="19" t="n">
-        <v>5152</v>
+        <v>6518</v>
       </c>
       <c r="K20" s="19" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/islem-merkezi/hat-ozetim/hat-ozetim-nedir</t>
+          <t>301 ile yönlendirilmesi (sorgular genel paket ve tarife araması): https://www.turkcell.com.tr/paket-ve-tarifeler</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13324,12 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/avans-tl-nedir-nasil-abone-olurum</t>
+          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/turkcell-hesabimda-servislerim-sayfasindan-hangi-bilgilere-ulasabilirim</t>
         </is>
       </c>
       <c r="D21" s="11" t="n">
@@ -13317,28 +13347,28 @@
       </c>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>Avans TL Nedir? Nasıl Abone Olurum?</t>
+          <t>Servislerim Sayfasında Hangi Bilgiler Var?</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>Kendi numaramı nasıl gizleyebilirim?</t>
+          <t>Hat Özetimde hattım ile ilgili hangi bilgilere ulaşabilirim?</t>
         </is>
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/kendi-numarami-nasil-gizleyebilirim</t>
+          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/hat-ozetimde-hattim-ile-ilgili-hangi-bilgilere-ulasabilirim</t>
         </is>
       </c>
       <c r="J21" s="19" t="n">
-        <v>4580</v>
+        <v>5510</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>98</v>
+        <v>7</v>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>Servisin yayında olup olmadığının teyit edilmesi; yayında değilse 410 dönmesi</t>
+          <t>301 ile yönlendirilmesi (sorgular 'turkcell online işlemler'): https://www.turkcell.com.tr/destek/islem-merkezi</t>
         </is>
       </c>
     </row>
@@ -13348,12 +13378,12 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/kampanya/kampanyalar-faturali/numarami-nasil-tasiyabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/turkcell-hesabimda-kampanyalarimla-hangi-islemleri-yapabilirim</t>
         </is>
       </c>
       <c r="D22" s="11" t="n">
@@ -13371,28 +13401,28 @@
       </c>
       <c r="G22" s="14" t="inlineStr">
         <is>
-          <t>Numaramı Turkcell’e Taşımak için Ne Yapmalıyım?</t>
+          <t>Kampanyalarım Sayfasında Hangi İşlemleri Yapabilirim?</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Numaramı taşımak ücretli midir?</t>
+          <t>Hat Özetimde hattım ile ilgili hangi bilgilere ulaşabilirim?</t>
         </is>
       </c>
       <c r="I22" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numarami-tasimak-ucretli-midir</t>
+          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/hat-ozetimde-hattim-ile-ilgili-hangi-bilgilere-ulasabilirim</t>
         </is>
       </c>
       <c r="J22" s="19" t="n">
-        <v>4541</v>
+        <v>5152</v>
       </c>
       <c r="K22" s="19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numarami-nasil-tasiyabilirim</t>
+          <t>301 ile yönlendirilmesi (sorgular 'turkcell online işlemler'): https://www.turkcell.com.tr/destek/islem-merkezi</t>
         </is>
       </c>
     </row>
@@ -13402,12 +13432,12 @@
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/tuketici-sikayetleri/sikayet-talebi-olusturma</t>
+          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/avans-tl-nedir-nasil-abone-olurum</t>
         </is>
       </c>
       <c r="D23" s="11" t="n">
@@ -13425,28 +13455,28 @@
       </c>
       <c r="G23" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Avans TL Nedir? Nasıl Abone Olurum?</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Kendi numaramı nasıl gizleyebilirim?</t>
         </is>
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/kendi-numarami-nasil-gizleyebilirim</t>
         </is>
       </c>
       <c r="J23" s="19" t="n">
-        <v>3123</v>
+        <v>4580</v>
       </c>
       <c r="K23" s="19" t="n">
-        <v>1614</v>
+        <v>98</v>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>Şikayet formunun güncel adresinin teyit edilmesi ve bu adrese 301 ile yönlendirilmesi (sayfa bugün H1 ve title olmadan dönüyor)</t>
+          <t>410 dönmesi (Avans TL servis sayfası da kaldırılmış)</t>
         </is>
       </c>
     </row>
@@ -13456,12 +13486,12 @@
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcellli-olmak/nasil-hazirkart-alirim</t>
+          <t>https://www.turkcell.com.tr/destek/kampanya/kampanyalar-faturali/numarami-nasil-tasiyabilirim</t>
         </is>
       </c>
       <c r="D24" s="11" t="n">
@@ -13479,28 +13509,28 @@
       </c>
       <c r="G24" s="14" t="inlineStr">
         <is>
-          <t>Nasıl faturalı hat alabilirim?</t>
+          <t>Numaramı Turkcell’e Taşımak için Ne Yapmalıyım?</t>
         </is>
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Nasıl faturalı hat alabilirim?</t>
+          <t>Numaramı taşımak ücretli midir?</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcellli-olmak/nasil-faturali-hat-alabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numarami-tasimak-ucretli-midir</t>
         </is>
       </c>
       <c r="J24" s="19" t="n">
-        <v>2934</v>
+        <v>4541</v>
       </c>
       <c r="K24" s="19" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/nasil-hazirkart-alirim</t>
+          <t>301 ile yönlendirilmesi (sorgular Turkcell'e geçiş ve numara taşıma arıyor): https://www.turkcell.com.tr/turkcellli-olmak/paket-secimi</t>
         </is>
       </c>
     </row>
@@ -13510,12 +13540,12 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/turkcell-akademi-egitimlerine-nereden-ulasabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcellli-olmak/nasil-hazirkart-alirim</t>
         </is>
       </c>
       <c r="D25" s="11" t="n">
@@ -13523,7 +13553,7 @@
       </c>
       <c r="E25" s="14" t="inlineStr">
         <is>
-          <t>Yönleniyor: https://www.turkcell.com.tr/destek</t>
+          <t>Kendi adresi</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
@@ -13533,28 +13563,28 @@
       </c>
       <c r="G25" s="14" t="inlineStr">
         <is>
-          <t>Turkcell Destek - Size Nasıl Yardımcı Olabiliriz?</t>
+          <t>Nasıl faturalı hat alabilirim?</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Merhaba, Size Nasıl Yardımcı Olabiliriz?</t>
+          <t>Nasıl faturalı hat alabilirim?</t>
         </is>
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcellli-olmak/nasil-faturali-hat-alabilirim</t>
         </is>
       </c>
       <c r="J25" s="19" t="n">
-        <v>2481</v>
+        <v>2934</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>404 ya da 410 dönmesi (bugün destek ana sayfasına yönleniyor)</t>
+          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/nasil-hazirkart-alirim</t>
         </is>
       </c>
     </row>
@@ -13564,12 +13594,12 @@
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/kredi-transfer-nedir</t>
+          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/turkcell-akademi-egitimlerine-nereden-ulasabilirim</t>
         </is>
       </c>
       <c r="D26" s="11" t="n">
@@ -13577,7 +13607,7 @@
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Kendi adresi</t>
+          <t>Yönleniyor: https://www.turkcell.com.tr/destek</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -13587,28 +13617,28 @@
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>Kredi Transfer Nedir? | Sıkça Sorulan Sorular</t>
+          <t>Turkcell Destek - Size Nasıl Yardımcı Olabiliriz?</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Kendi numaramı nasıl gizleyebilirim?</t>
+          <t>Merhaba, Size Nasıl Yardımcı Olabiliriz?</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/kendi-numarami-nasil-gizleyebilirim</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J26" s="19" t="n">
-        <v>1268</v>
+        <v>2481</v>
       </c>
       <c r="K26" s="19" t="n">
-        <v>242</v>
+        <v>108</v>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/hattiniz/hazirkart/kreditransfer-nedir</t>
+          <t>301 ile Turkcell Akademi platformuna yönlendirilmesi (sorgular 'turkcell akademi'): https://tag.turkcell.com.tr/</t>
         </is>
       </c>
     </row>
@@ -13618,12 +13648,12 @@
       </c>
       <c r="B27" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/telefonumu-mobil-odeme-kullanimina-nasil-acabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/kredi-transfer-nedir</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
@@ -13641,28 +13671,28 @@
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
+          <t>Kredi Transfer Nedir? | Sıkça Sorulan Sorular</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
           <t>Kendi numaramı nasıl gizleyebilirim?</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr">
-        <is>
-          <t>Kendi numaramı nasıl gizleyebilirim?</t>
-        </is>
-      </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/kendi-numarami-nasil-gizleyebilirim</t>
         </is>
       </c>
       <c r="J27" s="19" t="n">
-        <v>1227</v>
+        <v>1268</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>12</v>
+        <v>242</v>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/servisler/arama-fatura-tl/turkcellmobilodeme</t>
+          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/hattiniz/hazirkart/kreditransfer-nedir</t>
         </is>
       </c>
     </row>
@@ -13672,12 +13702,12 @@
       </c>
       <c r="B28" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/kampanya/kampanyalar-faturali/numarami-tasirken-hattim-kullanima-kapanir-mi</t>
+          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/telefonumu-mobil-odeme-kullanimina-nasil-acabilirim</t>
         </is>
       </c>
       <c r="D28" s="11" t="n">
@@ -13695,28 +13725,28 @@
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>Numaramı Taşırken Hattım Kullanıma Kapanır Mı?</t>
+          <t>Kendi numaramı nasıl gizleyebilirim?</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Numaramı taşımak ücretli midir?</t>
+          <t>Kendi numaramı nasıl gizleyebilirim?</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numarami-tasimak-ucretli-midir</t>
+          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/kendi-numarami-nasil-gizleyebilirim</t>
         </is>
       </c>
       <c r="J28" s="19" t="n">
-        <v>779</v>
+        <v>1227</v>
       </c>
       <c r="K28" s="19" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numarami-tasirken-hattim-kullanima-kapanir-mi</t>
+          <t>301 ile yönlendirilmesi (sorgular 'telefonu kapalı gösterme', 'açıkken ulaşılamıyor'): https://www.turkcell.com.tr/servisler/arama-fatura-tl/yonlendir</t>
         </is>
       </c>
     </row>
@@ -13726,12 +13756,12 @@
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/paket-ve-tarifelerim-sayfasindan-hangi-islemleri-yapabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/kampanya/kampanyalar-faturali/numarami-tasirken-hattim-kullanima-kapanir-mi</t>
         </is>
       </c>
       <c r="D29" s="11" t="n">
@@ -13749,28 +13779,28 @@
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>Paket ve Tarifelerim Sayfasında Neler Yapabilirim?</t>
+          <t>Numaramı Taşırken Hattım Kullanıma Kapanır Mı?</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Hat Özetimde hattım ile ilgili hangi bilgilere ulaşabilirim?</t>
+          <t>Numaramı taşımak ücretli midir?</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/hat-ozetimde-hattim-ile-ilgili-hangi-bilgilere-ulasabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numarami-tasimak-ucretli-midir</t>
         </is>
       </c>
       <c r="J29" s="19" t="n">
-        <v>382</v>
+        <v>779</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>7</v>
+        <v>55</v>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>404 ya da 410 dönmesi</t>
+          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numarami-tasirken-hattim-kullanima-kapanir-mi</t>
         </is>
       </c>
     </row>
@@ -13780,12 +13810,12 @@
       </c>
       <c r="B30" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/sosyal-destek-iletisim</t>
+          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/paket-ve-tarifelerim-sayfasindan-hangi-islemleri-yapabilirim</t>
         </is>
       </c>
       <c r="D30" s="11" t="n">
@@ -13803,28 +13833,28 @@
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Paket ve Tarifelerim Sayfasında Neler Yapabilirim?</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Hat Özetimde hattım ile ilgili hangi bilgilere ulaşabilirim?</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/hat-ozetimde-hattim-ile-ilgili-hangi-bilgilere-ulasabilirim</t>
         </is>
       </c>
       <c r="J30" s="19" t="n">
-        <v>257</v>
+        <v>382</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>404 ya da 410 dönmesi</t>
+          <t>301 ile yönlendirilmesi (sorgular 'turkcell online işlemler'): https://www.turkcell.com.tr/destek/islem-merkezi</t>
         </is>
       </c>
     </row>
@@ -13834,12 +13864,12 @@
       </c>
       <c r="B31" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/mevcut-egitimlerden-baska-egitimler-olacak-mi</t>
+          <t>https://www.turkcell.com.tr/destek/sosyal-destek-iletisim</t>
         </is>
       </c>
       <c r="D31" s="11" t="n">
@@ -13847,7 +13877,7 @@
       </c>
       <c r="E31" s="14" t="inlineStr">
         <is>
-          <t>Yönleniyor: https://www.turkcell.com.tr/destek</t>
+          <t>Kendi adresi</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
@@ -13857,12 +13887,12 @@
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>Turkcell Destek - Size Nasıl Yardımcı Olabiliriz?</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Merhaba, Size Nasıl Yardımcı Olabiliriz?</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
@@ -13871,14 +13901,14 @@
         </is>
       </c>
       <c r="J31" s="19" t="n">
-        <v>172</v>
+        <v>257</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>404 ya da 410 dönmesi (bugün destek ana sayfasına yönleniyor)</t>
+          <t>301 ile yönlendirilmesi (sorgular 'turkcell sosyal destek'): https://www.turkcell.com.tr/sosyal-destek</t>
         </is>
       </c>
     </row>
@@ -13888,12 +13918,12 @@
       </c>
       <c r="B32" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/tl-ayarlarim-sayfasindan-hangi-ayarlari-yapabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/mevcut-egitimlerden-baska-egitimler-olacak-mi</t>
         </is>
       </c>
       <c r="D32" s="11" t="n">
@@ -13901,7 +13931,7 @@
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Kendi adresi</t>
+          <t>Yönleniyor: https://www.turkcell.com.tr/destek</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
@@ -13911,28 +13941,28 @@
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>TL Ayarlarım Sayfasından Neler Yapabilirim?</t>
+          <t>Turkcell Destek - Size Nasıl Yardımcı Olabiliriz?</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Hat Özetimde hattım ile ilgili hangi bilgilere ulaşabilirim?</t>
+          <t>Merhaba, Size Nasıl Yardımcı Olabiliriz?</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/hat-ozetimde-hattim-ile-ilgili-hangi-bilgilere-ulasabilirim</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J32" s="19" t="n">
-        <v>145</v>
+        <v>172</v>
       </c>
       <c r="K32" s="19" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>404 ya da 410 dönmesi</t>
+          <t>301 ile Turkcell Akademi platformuna yönlendirilmesi (sorgular 'turkcell akademi'): https://tag.turkcell.com.tr/</t>
         </is>
       </c>
     </row>
@@ -13942,12 +13972,12 @@
       </c>
       <c r="B33" s="22" t="inlineStr">
         <is>
-          <t>Soft 404 · yazım varyantı</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/islem-merkezi/ayarlarim/arayan-numarayi-goster-clip-ozelligi-nedir</t>
+          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/tl-ayarlarim-sayfasindan-hangi-ayarlari-yapabilirim</t>
         </is>
       </c>
       <c r="D33" s="11" t="n">
@@ -13955,38 +13985,38 @@
       </c>
       <c r="E33" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/hattiniz/sikca-sorulan-sorular/arayan-numarayi-goster-clip-ozelligi-nedir</t>
+          <t>Kendi adresi</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>noindex,follow</t>
+          <t>index,follow</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>CLIP Özelliği Nedir? | Turkcell Destek</t>
+          <t>TL Ayarlarım Sayfasından Neler Yapabilirim?</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Arayan numarayı göster (CLIP) özelliği nedir?</t>
+          <t>Hat Özetimde hattım ile ilgili hangi bilgilere ulaşabilirim?</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcellli-olmak/arayan-numarayi-goster-clip-ozelligi-nedir</t>
+          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/hat-ozetimde-hattim-ile-ilgili-hangi-bilgilere-ulasabilirim</t>
         </is>
       </c>
       <c r="J33" s="19" t="n">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>Doğru adrese 301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/hattiniz/sikca-sorulan-sorular/arayan-numarayi-goster-clip-ozelligi-nedir</t>
+          <t>404 ya da 410 dönmesi (karşılayan sayfa yok)</t>
         </is>
       </c>
     </row>
@@ -13996,12 +14026,12 @@
       </c>
       <c r="B34" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa · yazım varyantı</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nerden-ogrenebilirim-ve-nasil-degistirebilirim</t>
+          <t>https://www.turkcell.com.tr/destek/islem-merkezi/ayarlarim/arayan-numarayi-goster-clip-ozelligi-nedir</t>
         </is>
       </c>
       <c r="D34" s="11" t="n">
@@ -14009,38 +14039,38 @@
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Kendi adresi</t>
+          <t>https://www.turkcell.com.tr/destek/hattiniz/sikca-sorulan-sorular/arayan-numarayi-goster-clip-ozelligi-nedir</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>index,follow</t>
+          <t>noindex,follow</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>Paket / Tarife değişikliğini nasıl yapabilirim?</t>
+          <t>CLIP Özelliği Nedir? | Turkcell Destek</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Paket / Tarife değişikliğini nasıl yapabilirim?</t>
+          <t>Arayan numarayı göster (CLIP) özelliği nedir?</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim</t>
+          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcellli-olmak/arayan-numarayi-goster-clip-ozelligi-nedir</t>
         </is>
       </c>
       <c r="J34" s="19" t="n">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>404 ya da 410 dönmesi</t>
+          <t>Doğru adrese 301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/hattiniz/sikca-sorulan-sorular/arayan-numarayi-goster-clip-ozelligi-nedir</t>
         </is>
       </c>
     </row>
@@ -14050,12 +14080,12 @@
       </c>
       <c r="B35" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/kurumsal/destek/hattiniz/faturali/hattimi-gecici-olarak-</t>
+          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nerden-ogrenebilirim-ve-nasil-degistirebilirim</t>
         </is>
       </c>
       <c r="D35" s="11" t="n">
@@ -14073,28 +14103,28 @@
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>Hattım fatura borcu nedeniyle kapanırsa, yeniden kapama/açma için bir ücret öder miyim?</t>
+          <t>Paket / Tarife değişikliğini nasıl yapabilirim?</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Hattım fatura borcu nedeniyle kapanırsa, yeniden kapama/açma için bir ücret öder miyim?</t>
+          <t>Paket / Tarife değişikliğini nasıl yapabilirim?</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/hattiniz/faturali/hattim-fatura-borcu-nedeniyle-kapanirsa-yeniden-actirmak-icin-bir-ucret-oder-miyim</t>
+          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim</t>
         </is>
       </c>
       <c r="J35" s="19" t="n">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>404 ya da 410 dönmesi</t>
+          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim</t>
         </is>
       </c>
     </row>
@@ -14104,12 +14134,12 @@
       </c>
       <c r="B36" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/online-alisveris/turkcell-pasaj/turkcell-pasajda-satici-olmak-istiyorum-nereye-basvurabilirim</t>
+          <t>https://www.turkcell.com.tr/kurumsal/destek/hattiniz/faturali/hattimi-gecici-olarak-</t>
         </is>
       </c>
       <c r="D36" s="11" t="n">
@@ -14122,33 +14152,33 @@
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>noindex,nofollow</t>
+          <t>index,follow</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>Turkcell Pasaj’da Satıcı Olmak İstiyorum, Nereye Başvurabilirim?</t>
+          <t>Hattım fatura borcu nedeniyle kapanırsa, yeniden kapama/açma için bir ücret öder miyim?</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Turkcell Pasaj'da satıcı olmak istiyorum.</t>
+          <t>Hattım fatura borcu nedeniyle kapanırsa, yeniden kapama/açma için bir ücret öder miyim?</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.turkcell.com.tr/destek/hattiniz/faturali/hattim-fatura-borcu-nedeniyle-kapanirsa-yeniden-actirmak-icin-bir-ucret-oder-miyim</t>
         </is>
       </c>
       <c r="J36" s="19" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>404 ya da 410 dönmesi</t>
+          <t>Kesik adresin sayfanın tam adresine 301 ile yönlendirilmesi: https://www.turkcell.com.tr/kurumsal/destek/hattiniz/faturali/hattimi-gecici-olarak-gelen-ve-gelen-giden-iletisime-ne-kadar-sureyle-kapatabilirim-ve-faturama-herhangi-bir-ucret-yansir-m</t>
         </is>
       </c>
     </row>
@@ -14158,7 +14188,7 @@
       </c>
       <c r="B37" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C37" s="14" t="inlineStr">
@@ -14202,7 +14232,7 @@
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>404 ya da 410 dönmesi</t>
+          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/hattimi-nasil-iptal-ettirebilirim</t>
         </is>
       </c>
     </row>
@@ -14212,7 +14242,7 @@
       </c>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>Soft 404 · yazım varyantı</t>
+          <t>Soft 404 - tekrar eden sayfa · yazım varyantı</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
@@ -14266,7 +14296,7 @@
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>Soft 404 · yazım varyantı</t>
+          <t>Soft 404 - tekrar eden sayfa · yazım varyantı</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
@@ -14320,7 +14350,7 @@
       </c>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
@@ -14374,7 +14404,7 @@
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>Soft 404</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr">
@@ -15870,7 +15900,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Aynı Başlığı Taşıyan Destek Sayfaları</t>
+          <t>Duplicate Adresler · Aynı Başlığı ve Cevabı Taşıyan Destek Sayfaları</t>
         </is>
       </c>
     </row>

--- a/Turkcell-Destek-Sayfa-Onerileri-22-09-2026.xlsx
+++ b/Turkcell-Destek-Sayfa-Onerileri-22-09-2026.xlsx
@@ -20,8 +20,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Talepler'!$A$4:$I$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Yeni Sayfa Önerileri'!$A$4:$U$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Mevcut Sayfa Güçlendirme'!$A$4:$O$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Yeni Sayfa Önerileri'!$A$4:$U$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Mevcut Sayfa Güçlendirme'!$A$4:$O$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sitemap Dışı Adresler'!$A$4:$L$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Doğrulanacak Bilgiler'!$A$4:$G$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Duplicate Adresler'!$A$4:$G$129</definedName>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
-          <t>Şablon · 590 sitemap sayfası + 8 sitemap dışı sayfa + yeni açılacak 51 sayfa</t>
+          <t>Şablon · 590 sitemap sayfası + sitemap dışı sayfalar + yeni açılacak 52 sayfa</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U55"/>
+  <dimension ref="A1:U56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6352,62 +6352,173 @@
       </c>
       <c r="C41" s="14" t="inlineStr">
         <is>
+          <t>Turkcell Rahat paketi nasıl iptal edilir, Rahat'tan faturalı ya da faturasız hatta nasıl geçilir?</t>
+        </is>
+      </c>
+      <c r="D41" s="14" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/turkcell-rahat-paketi-nasil-iptal-edilir</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>tarife-ve-paketler</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>konusma</t>
+        </is>
+      </c>
+      <c r="G41" s="20" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>turkcell rahat paket iptali</t>
+        </is>
+      </c>
+      <c r="I41" s="19" t="n">
+        <v>140</v>
+      </c>
+      <c r="J41" s="19" t="n">
+        <v>5075</v>
+      </c>
+      <c r="K41" s="19" t="n">
+        <v>1136</v>
+      </c>
+      <c r="L41" s="11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M41" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="14" t="inlineStr">
+        <is>
+          <t>B · Sorgu başka sayfa tipine düşüyor</t>
+        </is>
+      </c>
+      <c r="O41" s="14" t="inlineStr">
+        <is>
+          <t>Search Console 12 ay · Marka geri bildirimi</t>
+        </is>
+      </c>
+      <c r="P41" s="14" t="inlineStr">
+        <is>
+          <t>• Aylık hacim: 'turkcell rahat paket iptali' 140
+• Search Console: 5.075 impression · 1.136 click · ağırlıklı konum 3,6
+• Tıklama alan sayfa: https://www.turkcell.com.tr/paket-ve-tarifeler/turkcell-rahat
+• Rahat sorgu ailesinin tamamı 146.402 impression üretmekte, tanım ve geçiş sorularını ticari Rahat sayfası karşılamaktadır.
+• Karşılıksız kalan bölüm iptal ve Rahat'tan çıkış sorularıdır; bu sorgular bugün tarife değişikliği destek sayfasına ve hat iptali sayfasına düşmekte, iki sayfa da Rahat modelini anlatmamaktadır.
+• Destek bölümünde Turkcell Rahat konusunda hiç sayfa bulunmamaktadır.</t>
+        </is>
+      </c>
+      <c r="Q41" s="14" t="inlineStr">
+        <is>
+          <t>Turkcell Rahat taahhütsüz bir tarife modelidir; geçiş için imzalanan bağlayıcı bir sözleşme ve cayma bedeli bulunmaz. Rahat paketinden çıkmak için hattın iptal edilmesi gerekmez, tarife değişikliği yapılması yeterlidir.
+Rahat'tan faturalı bir tarifeye geçiş: Turkcell Uygulaması'ndaki Paketlerim alanından, 532 Müşteri Hizmetleri'nden ya da Turkcell İletişim Merkezlerinden tarife değişikliği talep edilebilir. Rahat kullanıcılarına özel faturalı paketler Rahat'tan Faturalıya Geçiş sayfasında listelenir.
+Rahat'tan faturasız (Hazır Kart) hatta geçiş: Ödeme tipi değişikliği kapsamında değerlendirilir; başvuru Turkcell Uygulaması, 532 Müşteri Hizmetleri ya da Turkcell İletişim Merkezleri üzerinden yapılır. [Marka doğrulaması bekliyor: Rahat'tan faturasıza geçişin yapılabildiği kanallar ve varsa bekleme süresi.]
+Hattın tamamen kapatılması isteniyorsa hat iptali süreci işletilir; iptal kanalları Hattımı nasıl iptal ettirebilirim sayfasında anlatılır.
+[Marka doğrulaması bekliyor: Rahat paket iptalinin hangi tarihte yürürlüğe girdiği (ay sonu ya da talep anı), iptal sonrası kalan paket hakkının ne olduğu ve iptal için kısa mesaj kanalı bulunup bulunmadığı.]</t>
+        </is>
+      </c>
+      <c r="R41" s="14" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/paket-ve-tarifeler/turkcell-rahat
+https://www.turkcell.com.tr/paket-ve-tarifeler/rahattan-faturaliya-gecis
+https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim
+https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/hattimi-nasil-iptal-ettirebilirim</t>
+        </is>
+      </c>
+      <c r="S41" s="14" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/paket-ve-tarifeler/turkcell-rahat
+https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim
+https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/hattimi-nasil-iptal-ettirebilirim</t>
+        </is>
+      </c>
+      <c r="T41" s="14" t="inlineStr">
+        <is>
+          <t>Rahat paket iptalinin yürürlük tarihi, kalan paket hakkı, kısa mesaj kanalı ve Rahat'tan faturasıza geçiş kanalları.</t>
+        </is>
+      </c>
+      <c r="U41" s="14" t="inlineStr">
+        <is>
+          <t>turkcell rahat paket iptali · turkcell rahat paket iptal etme · turkcell rahat paket iptali sms · rahat paket nasıl iptal edilir · turkcell rahat paketten faturasıza geçiş · turkcell rahattan faturalıya geçiş · turkcell rahat hat iptal etme · turkcell faturalıdan rahata geçiş</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>Faz 2</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
           <t>Superbox farklı bir adreste kullanılabilir mi?</t>
         </is>
       </c>
-      <c r="D41" s="14" t="inlineStr">
+      <c r="D42" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/tasinabilir-internet/superbox-farkli-bir-adreste-kullanilabilir-mi</t>
         </is>
       </c>
-      <c r="E41" s="17" t="inlineStr">
+      <c r="E42" s="17" t="inlineStr">
         <is>
           <t>servisler-ve-internet</t>
         </is>
       </c>
-      <c r="F41" s="17" t="inlineStr">
+      <c r="F42" s="17" t="inlineStr">
         <is>
           <t>tasinabilir-internet</t>
         </is>
       </c>
-      <c r="G41" s="18" t="inlineStr">
+      <c r="G42" s="18" t="inlineStr">
         <is>
           <t>Evet</t>
         </is>
       </c>
-      <c r="H41" s="14" t="inlineStr">
+      <c r="H42" s="14" t="inlineStr">
         <is>
           <t>superbox taşınabilir mi</t>
         </is>
       </c>
-      <c r="I41" s="19" t="n">
+      <c r="I42" s="19" t="n">
         <v>70</v>
       </c>
-      <c r="J41" s="19" t="n">
+      <c r="J42" s="19" t="n">
         <v>1662</v>
       </c>
-      <c r="K41" s="19" t="n">
+      <c r="K42" s="19" t="n">
         <v>402</v>
       </c>
-      <c r="L41" s="11" t="n">
+      <c r="L42" s="11" t="n">
         <v>2.5</v>
       </c>
-      <c r="M41" s="18" t="inlineStr">
+      <c r="M42" s="18" t="inlineStr">
         <is>
           <t>Var</t>
         </is>
       </c>
-      <c r="N41" s="14" t="inlineStr">
+      <c r="N42" s="14" t="inlineStr">
         <is>
           <t>C · Talep var, sayfa yok</t>
         </is>
       </c>
-      <c r="O41" s="14" t="inlineStr">
+      <c r="O42" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
-      <c r="P41" s="14" t="inlineStr">
+      <c r="P42" s="14" t="inlineStr">
         <is>
           <t>• Aylık hacim: 'superbox taşınabilir mi' 70
 • Search Console: 1.662 impression · 402 click · ağırlıklı konum 2,5
@@ -6416,101 +6527,101 @@
 • Sitedeki iki sayfa aynı soruya farklı cevap verdiğinden cevabın özü marka doğrulamasına bırakılmıştır; bu tutarsızlık doğrulanması gereken bilgiler listesinde yer almaktadır.</t>
         </is>
       </c>
-      <c r="Q41" s="14" t="inlineStr">
+      <c r="Q42" s="14" t="inlineStr">
         <is>
           <t>Superbox, elektrik prizi bulunan ve 5G ya da 4.5G kapsaması olan noktalarda çalışır. Bağlantı hızı, bulunulan noktadaki kapsama, şebeke yoğunluğu ve kullanılan cihaza göre değişebilir. Bir adresin uygunluğu Superbox başvuru ve altyapı sorgulama sayfasında adres girilerek kontrol edilebilir. [Marka doğrulaması bekliyor] (paket türüne göre hizmet adresi dışında kullanım koşulu ve hizmet adresinin değiştirilme yolu)</t>
         </is>
       </c>
-      <c r="R41" s="14" t="inlineStr">
+      <c r="R42" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/ev-interneti/superbox
 https://www.turkcell.com.tr/ev-interneti/superbox-basvuru-ve-altyapi-sorgulama</t>
         </is>
       </c>
-      <c r="S41" s="14" t="inlineStr">
+      <c r="S42" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/ev-interneti/superbox-basvuru-ve-altyapi-sorgulama
 Önerilen: https://www.turkcell.com.tr/destek/servisler-ve-internet/tasinabilir-internet/altyapisi-olmayan-eve-nasil-internet-baglanir</t>
         </is>
       </c>
-      <c r="T41" s="14" t="inlineStr">
+      <c r="T42" s="14" t="inlineStr">
         <is>
           <t>Farklı adreste kullanım koşulu (ticari sayfa ve tarife detay sayfası farklı ifade taşıyor); hizmet adresi değişikliği kanalı.</t>
         </is>
       </c>
-      <c r="U41" s="14" t="inlineStr">
+      <c r="U42" s="14" t="inlineStr">
         <is>
           <t>superbox her yerde çeker mi · superbox her yerde kullanılır mı · superbox adres değişikliği</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="11" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C42" s="14" t="inlineStr">
+      <c r="C43" s="14" t="inlineStr">
         <is>
           <t>Fatura itirazı nasıl yapılır?</t>
         </is>
       </c>
-      <c r="D42" s="14" t="inlineStr">
+      <c r="D43" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/faturali/fatura-itirazi-nasil-yapilir</t>
         </is>
       </c>
-      <c r="E42" s="17" t="inlineStr">
+      <c r="E43" s="17" t="inlineStr">
         <is>
           <t>hattiniz</t>
         </is>
       </c>
-      <c r="F42" s="17" t="inlineStr">
+      <c r="F43" s="17" t="inlineStr">
         <is>
           <t>faturali</t>
         </is>
       </c>
-      <c r="G42" s="20" t="inlineStr">
+      <c r="G43" s="20" t="inlineStr">
         <is>
           <t>Hayır</t>
         </is>
       </c>
-      <c r="H42" s="14" t="inlineStr">
+      <c r="H43" s="14" t="inlineStr">
         <is>
           <t>fatura itirazı nasıl yapılır</t>
         </is>
       </c>
-      <c r="I42" s="19" t="n">
+      <c r="I43" s="19" t="n">
         <v>170</v>
       </c>
-      <c r="J42" s="19" t="n">
+      <c r="J43" s="19" t="n">
         <v>1271</v>
       </c>
-      <c r="K42" s="19" t="n">
+      <c r="K43" s="19" t="n">
         <v>735</v>
       </c>
-      <c r="L42" s="11" t="n">
+      <c r="L43" s="11" t="n">
         <v>2.1</v>
       </c>
-      <c r="M42" s="18" t="inlineStr">
+      <c r="M43" s="18" t="inlineStr">
         <is>
           <t>Var</t>
         </is>
       </c>
-      <c r="N42" s="14" t="inlineStr">
+      <c r="N43" s="14" t="inlineStr">
         <is>
           <t>A · Sayfa var, konum ilk 5 dışında</t>
         </is>
       </c>
-      <c r="O42" s="14" t="inlineStr">
+      <c r="O43" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi · Search Console 12 ay · Rakip destek karşılaştırması</t>
         </is>
       </c>
-      <c r="P42" s="14" t="inlineStr">
+      <c r="P43" s="14" t="inlineStr">
         <is>
           <t>• Aylık hacim: 'fatura itirazı nasıl yapılır' 170
 • Search Console: 1.271 impression · 735 click · ağırlıklı konum 2,1
@@ -6519,101 +6630,101 @@
 • İtiraz süresi ve sonuçlandırma süresi sitede bulunamadığı için cevabın bu kısmı marka verisine bağlıdır.</t>
         </is>
       </c>
-      <c r="Q42" s="14" t="inlineStr">
+      <c r="Q43" s="14" t="inlineStr">
         <is>
           <t>Faturadaki bir kalemin hangi kullanımdan oluştuğu, fatura detayları ve Turkcell Müşteri Hizmetleri (532) üzerinden incelenebilir. Fatura tutarına itiraz edilmesi durumunda, borç nedeniyle uygulanan kısıtlama süreleri fatura itirazı gibi istisna durumlarda farklı işler. [Marka doğrulaması bekliyor] (fatura itirazının iletileceği kanallar, itiraz süresi, itiraz sürecinde ödeme yükümlülüğü ve sonuçlandırma süresi)</t>
         </is>
       </c>
-      <c r="R42" s="14" t="inlineStr">
+      <c r="R43" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/faturali/faturami-son-odeme-tarihinde-odemedigimde-hattimin-kisitlanma-ve-durdurma-sure-ve-surecleri-nelerdir
 https://www.turkcell.com.tr/destek/hattiniz/faturali/faturamin-hangi-ucretlerden-olustugunu-nasil-ogrenebilirim</t>
         </is>
       </c>
-      <c r="S42" s="14" t="inlineStr">
+      <c r="S43" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/tuketici-sikayetleri/sikayet-takibi
 https://www.turkcell.com.tr/destek/hattiniz/faturali/faturamin-hangi-ucretlerden-olustugunu-nasil-ogrenebilirim</t>
         </is>
       </c>
-      <c r="T42" s="14" t="inlineStr">
+      <c r="T43" s="14" t="inlineStr">
         <is>
           <t>İtiraz kanalları, süre, ödeme yükümlülüğü ve sonuçlandırma süresi; Şikayet Talebi Oluşturma formunun güncel adresi.</t>
         </is>
       </c>
-      <c r="U42" s="14" t="inlineStr">
+      <c r="U43" s="14" t="inlineStr">
         <is>
           <t>turkcell fatura itirazı · turkcell fatura itiraz dilekçesi · turkcell faturam fazla geldi ne yapmalıyım</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="11" t="n">
-        <v>39</v>
-      </c>
-      <c r="B43" s="16" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C43" s="14" t="inlineStr">
+      <c r="C44" s="14" t="inlineStr">
         <is>
           <t>Telefonum çalındı ya da kayboldu, ne yapılmalı?</t>
         </is>
       </c>
-      <c r="D43" s="14" t="inlineStr">
+      <c r="D44" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/cihaz-kaydi-ve-imei/telefonum-calindi-ne-yapmaliyim</t>
         </is>
       </c>
-      <c r="E43" s="17" t="inlineStr">
+      <c r="E44" s="17" t="inlineStr">
         <is>
           <t>hattiniz</t>
         </is>
       </c>
-      <c r="F43" s="17" t="inlineStr">
+      <c r="F44" s="17" t="inlineStr">
         <is>
           <t>cihaz-kaydi-ve-imei</t>
         </is>
       </c>
-      <c r="G43" s="18" t="inlineStr">
+      <c r="G44" s="18" t="inlineStr">
         <is>
           <t>Evet</t>
         </is>
       </c>
-      <c r="H43" s="14" t="inlineStr">
+      <c r="H44" s="14" t="inlineStr">
         <is>
           <t>telefon çalındı ne yapmalıyım</t>
         </is>
       </c>
-      <c r="I43" s="19" t="n">
+      <c r="I44" s="19" t="n">
         <v>390</v>
       </c>
-      <c r="J43" s="19" t="n">
+      <c r="J44" s="19" t="n">
         <v>110</v>
       </c>
-      <c r="K43" s="19" t="n">
+      <c r="K44" s="19" t="n">
         <v>36</v>
       </c>
-      <c r="L43" s="11" t="n">
+      <c r="L44" s="11" t="n">
         <v>4.5</v>
       </c>
-      <c r="M43" s="18" t="inlineStr">
+      <c r="M44" s="18" t="inlineStr">
         <is>
           <t>Var</t>
         </is>
       </c>
-      <c r="N43" s="14" t="inlineStr">
+      <c r="N44" s="14" t="inlineStr">
         <is>
           <t>C · Talep var, sayfa yok</t>
         </is>
       </c>
-      <c r="O43" s="14" t="inlineStr">
+      <c r="O44" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi · Rakip destek karşılaştırması</t>
         </is>
       </c>
-      <c r="P43" s="14" t="inlineStr">
+      <c r="P44" s="14" t="inlineStr">
         <is>
           <t>• Aylık hacim: 'telefon çalındı ne yapmalıyım' 390
 • Search Console: 110 impression · 36 click · ağırlıklı konum 4,5
@@ -6623,102 +6734,102 @@
 • Telefonu bulma sorusu blog yazısı tarafından karşılandığı için kapsam dışında bırakılmış, blogdan bu sayfaya iç link önerilmiştir.</t>
         </is>
       </c>
-      <c r="Q43" s="14" t="inlineStr">
+      <c r="Q44" s="14" t="inlineStr">
         <is>
           <t>Cihaz çalındığında ya da kaybolduğunda, başkası tarafından kullanılmasını engellemek için IMEI numarası ile kayıp/çalıntı ihbarı yapılır. İhbar, e-Devlet Kapısı'ndaki Kayıp/Çalıntı İhbar Bildirimi hizmetinden, BTK Tüketici İletişim Merkezi 120 aranarak ya da adli merciler aracılığıyla yapılabilir; ihbar için cihazın 15 haneli IMEI numarasının bilinmesi ve başvurunun hattın yasal sahibi tarafından yapılması gerekir. Cihaz bulunduğunda ihbarın iptali, ihbarın yapıldığı kanaldan yapılır. Hattın aynı numarayla kullanılmaya devam edilmesi için Turkcell Mağazaları'ndan kimlik belgesiyle yedek SIM kart alınabilir ya da Turkcell Uygulaması üzerinden eSIM talep edilebilir; yedek SIM kart hizmeti KDV dahil 205 TL'dir. [Marka doğrulaması bekliyor] (kayıp ya da çalıntı durumunda hattın ücretsiz kullanıma kapatılma kanalı)</t>
         </is>
       </c>
-      <c r="R43" s="14" t="inlineStr">
+      <c r="R44" s="14" t="inlineStr">
         <is>
           <t>https://tuketici.btk.gov.tr/kayip-calinti-islemleri
 https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/simkartimi-kaybettim-yeni-simkarti-nasil-alabilirim</t>
         </is>
       </c>
-      <c r="S43" s="14" t="inlineStr">
+      <c r="S44" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/simkartimi-kaybettim-yeni-simkarti-nasil-alabilirim
 https://www.turkcell.com.tr/blog/telefonum-nerede-kayip-ve-kapali-telefon-nasil-bulunur
 Önerilen: https://www.turkcell.com.tr/destek/hattiniz/cihaz-kaydi-ve-imei/imei-sorgulama-nasil-yapilir</t>
         </is>
       </c>
-      <c r="T43" s="14" t="inlineStr">
+      <c r="T44" s="14" t="inlineStr">
         <is>
           <t>Kayıp/çalıntı durumunda hattın kullanıma kapatılması için Turkcell kanalı ve ücreti; kurumsal sayfadaki eski BTK numarasının güncellenmesi (çelişki listesinde).</t>
         </is>
       </c>
-      <c r="U43" s="14" t="inlineStr">
+      <c r="U44" s="14" t="inlineStr">
         <is>
           <t>kayıp çalıntı bildirimi · telefonum çalındı hattımı nasıl kapatabilirim · kayıp telefon bildirimi</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="11" t="n">
-        <v>40</v>
-      </c>
-      <c r="B44" s="20" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="11" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="20" t="inlineStr">
         <is>
           <t>Faz 3</t>
         </is>
       </c>
-      <c r="C44" s="14" t="inlineStr">
+      <c r="C45" s="14" t="inlineStr">
         <is>
           <t>Turkcell Platinum nedir ve kimler yararlanabilir?</t>
         </is>
       </c>
-      <c r="D44" s="14" t="inlineStr">
+      <c r="D45" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/baglilik-programlari/turkcell-platinum-nedir-ve-kimler-yararlanabilir</t>
         </is>
       </c>
-      <c r="E44" s="17" t="inlineStr">
+      <c r="E45" s="17" t="inlineStr">
         <is>
           <t>turkcellli-olmak</t>
         </is>
       </c>
-      <c r="F44" s="17" t="inlineStr">
+      <c r="F45" s="17" t="inlineStr">
         <is>
           <t>baglilik-programlari</t>
         </is>
       </c>
-      <c r="G44" s="20" t="inlineStr">
+      <c r="G45" s="20" t="inlineStr">
         <is>
           <t>Hayır</t>
         </is>
       </c>
-      <c r="H44" s="14" t="inlineStr">
+      <c r="H45" s="14" t="inlineStr">
         <is>
           <t>turkcell platinum nedir</t>
         </is>
       </c>
-      <c r="I44" s="19" t="n">
+      <c r="I45" s="19" t="n">
         <v>720</v>
       </c>
-      <c r="J44" s="19" t="n">
+      <c r="J45" s="19" t="n">
         <v>32983</v>
       </c>
-      <c r="K44" s="19" t="n">
+      <c r="K45" s="19" t="n">
         <v>2248</v>
       </c>
-      <c r="L44" s="11" t="n">
+      <c r="L45" s="11" t="n">
         <v>4.1</v>
       </c>
-      <c r="M44" s="20" t="inlineStr">
+      <c r="M45" s="20" t="inlineStr">
         <is>
           <t>Yok</t>
         </is>
       </c>
-      <c r="N44" s="14" t="inlineStr">
+      <c r="N45" s="14" t="inlineStr">
         <is>
           <t>B · Sorgu başka sayfa tipine düşüyor</t>
         </is>
       </c>
-      <c r="O44" s="14" t="inlineStr">
+      <c r="O45" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi · Search Console 12 ay</t>
         </is>
       </c>
-      <c r="P44" s="14" t="inlineStr">
+      <c r="P45" s="14" t="inlineStr">
         <is>
           <t>• Aylık hacim: 'turkcell platinum nedir' 720
 • Search Console: 32.983 impression · 2.248 click · ağırlıklı konum 4,1
@@ -6726,99 +6837,99 @@
 • Program sayfası sorguda 2 civarında sıralanmakla birlikte soru-cevap biçiminde bir tanım taşımamaktadır; ayrıcalık listesi dönemsel olduğundan metin genel tutulmuştur.</t>
         </is>
       </c>
-      <c r="Q44" s="14" t="inlineStr">
+      <c r="Q45" s="14" t="inlineStr">
         <is>
           <t>Turkcell Platinum, Platinum paketlerini kullanan bireysel ve kurumsal müşterilere ayrıcalıklar sunan bir programdır. Programa dahil olmak için Platinum paketlerinden birinin kullanılması gerekir; ayrıcalıklar Platinum mobil uygulaması üzerinden takip edilir. Platinum müşterileri 7/24 Platinum Müşteri Hizmetleri'nden hizmet alabilir. Program kapsamında seyahat, alışveriş ve teknoloji alanlarında dönemsel ayrıcalıklar sunulur; güncel ayrıcalıklar Platinum sayfasında yer alır. [Marka doğrulaması bekliyor] (bireysel Platinum Müşteri Hizmetleri numarası ve Tarifen Yurt Dışında Geçerli ayrıcalığının güncel kapsamı)</t>
         </is>
       </c>
-      <c r="R44" s="14" t="inlineStr">
+      <c r="R45" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/platinum</t>
         </is>
       </c>
-      <c r="S44" s="14" t="inlineStr">
+      <c r="S45" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/platinum</t>
         </is>
       </c>
-      <c r="T44" s="14" t="inlineStr">
+      <c r="T45" s="14" t="inlineStr">
         <is>
           <t>Bireysel Platinum Müşteri Hizmetleri numarası; yurt dışı ayrıcalığının ülke ve gün kapsamı.</t>
         </is>
       </c>
-      <c r="U44" s="14" t="inlineStr">
+      <c r="U45" s="14" t="inlineStr">
         <is>
           <t>turkcell platinum nasıl olunur · platinum black nedir</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="11" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="20" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
         <is>
           <t>Faz 3</t>
         </is>
       </c>
-      <c r="C45" s="14" t="inlineStr">
+      <c r="C46" s="14" t="inlineStr">
         <is>
           <t>Turkcell Gaming ücretli mi?</t>
         </is>
       </c>
-      <c r="D45" s="14" t="inlineStr">
+      <c r="D46" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/turkcell-gaming-ucretli-mi</t>
         </is>
       </c>
-      <c r="E45" s="17" t="inlineStr">
+      <c r="E46" s="17" t="inlineStr">
         <is>
           <t>servisler-ve-internet</t>
         </is>
       </c>
-      <c r="F45" s="17" t="inlineStr">
+      <c r="F46" s="17" t="inlineStr">
         <is>
           <t>servisler</t>
         </is>
       </c>
-      <c r="G45" s="20" t="inlineStr">
+      <c r="G46" s="20" t="inlineStr">
         <is>
           <t>Hayır</t>
         </is>
       </c>
-      <c r="H45" s="14" t="inlineStr">
+      <c r="H46" s="14" t="inlineStr">
         <is>
           <t>turkcell gaming ücretli mi</t>
         </is>
       </c>
-      <c r="I45" s="19" t="n">
+      <c r="I46" s="19" t="n">
         <v>480</v>
       </c>
-      <c r="J45" s="19" t="n">
+      <c r="J46" s="19" t="n">
         <v>27410</v>
       </c>
-      <c r="K45" s="19" t="n">
+      <c r="K46" s="19" t="n">
         <v>1291</v>
       </c>
-      <c r="L45" s="11" t="n">
+      <c r="L46" s="11" t="n">
         <v>4.5</v>
       </c>
-      <c r="M45" s="20" t="inlineStr">
+      <c r="M46" s="20" t="inlineStr">
         <is>
           <t>Yok</t>
         </is>
       </c>
-      <c r="N45" s="14" t="inlineStr">
+      <c r="N46" s="14" t="inlineStr">
         <is>
           <t>B · Sorgu başka sayfa tipine düşüyor</t>
         </is>
       </c>
-      <c r="O45" s="14" t="inlineStr">
+      <c r="O46" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi · Search Console 12 ay</t>
         </is>
       </c>
-      <c r="P45" s="14" t="inlineStr">
+      <c r="P46" s="14" t="inlineStr">
         <is>
           <t>• Aylık hacim: 'turkcell gaming ücretli mi' 480
 • Search Console: 27.410 impression · 1.291 click · ağırlıklı konum 4,5
@@ -6827,101 +6938,101 @@
 • Alternatif olarak aynı cevap /gaming/ SSS'ine soru olarak da eklenebilir; ayrı sayfa açılırsa iki metnin birebir tutarlı tutulması gerekir.</t>
         </is>
       </c>
-      <c r="Q45" s="14" t="inlineStr">
+      <c r="Q46" s="14" t="inlineStr">
         <is>
           <t>Turkcell Gaming, Turkcell Uygulaması içindeki oyunlar ile oyun ve içerik platformlarında geçerli internet paketlerini bir araya getiren bir alandır. Turkcell Gaming oyunları bireysel ve kurumsal, faturalı ve faturasız tüm abonelere açıktır; oyunlara Turkcell Uygulaması'ndaki Hediyeler bölümünden ya da Keşfet sekmesindeki Turkcell Gaming bölümünden erişilir. Turkcell Gaming paketleri ise ücretli ek paketlerdir; örneğin Oyna İzle Paketi seçili oyunlarda ve YouTube, Kick ve Twitch'te geçerli internet sunar. [Marka doğrulaması bekliyor] (oyunların oynanmasının ücretsiz olduğu bilgisinin açık ifadesi)</t>
         </is>
       </c>
-      <c r="R45" s="14" t="inlineStr">
+      <c r="R46" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/gaming/
 https://www.turkcell.com.tr/paket-ve-tarifeler/ek-paketler/oyna-izle-paketi</t>
         </is>
       </c>
-      <c r="S45" s="14" t="inlineStr">
+      <c r="S46" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/gaming/
 https://www.turkcell.com.tr/paket-ve-tarifeler/ek-paketler/oyna-izle-paketi</t>
         </is>
       </c>
-      <c r="T45" s="14" t="inlineStr">
+      <c r="T46" s="14" t="inlineStr">
         <is>
           <t>Oyunların ücretsiz oynandığının açık teyidi.</t>
         </is>
       </c>
-      <c r="U45" s="14" t="inlineStr">
+      <c r="U46" s="14" t="inlineStr">
         <is>
           <t>turkcell gaming oyunları ücretli mi · turkcell gaming paralı mı</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="20" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="11" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
         <is>
           <t>Faz 3</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C47" s="14" t="inlineStr">
         <is>
           <t>Turkcell Uygulaması'na giriş yapılamıyorsa ne yapılabilir?</t>
         </is>
       </c>
-      <c r="D46" s="14" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hizmet-kanallarimiz/self-servis/turkcell-uygulamasina-giris-yapilamiyorsa-ne-yapilabilir</t>
         </is>
       </c>
-      <c r="E46" s="17" t="inlineStr">
+      <c r="E47" s="17" t="inlineStr">
         <is>
           <t>hizmet-kanallarimiz</t>
         </is>
       </c>
-      <c r="F46" s="17" t="inlineStr">
+      <c r="F47" s="17" t="inlineStr">
         <is>
           <t>self-servis</t>
         </is>
       </c>
-      <c r="G46" s="20" t="inlineStr">
+      <c r="G47" s="20" t="inlineStr">
         <is>
           <t>Hayır</t>
         </is>
       </c>
-      <c r="H46" s="14" t="inlineStr">
+      <c r="H47" s="14" t="inlineStr">
         <is>
           <t>turkcell uygulamasına giriş yapamıyorum</t>
         </is>
       </c>
-      <c r="I46" s="19" t="n">
+      <c r="I47" s="19" t="n">
         <v>110</v>
       </c>
-      <c r="J46" s="19" t="n">
+      <c r="J47" s="19" t="n">
         <v>22225</v>
       </c>
-      <c r="K46" s="19" t="n">
+      <c r="K47" s="19" t="n">
         <v>1929</v>
       </c>
-      <c r="L46" s="11" t="n">
+      <c r="L47" s="11" t="n">
         <v>5.2</v>
       </c>
-      <c r="M46" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N46" s="14" t="inlineStr">
+      <c r="M47" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="14" t="inlineStr">
         <is>
           <t>B · Sorgu başka sayfa tipine düşüyor</t>
         </is>
       </c>
-      <c r="O46" s="14" t="inlineStr">
+      <c r="O47" s="14" t="inlineStr">
         <is>
           <t>Rakip destek karşılaştırması · Search Console 12 ay</t>
         </is>
       </c>
-      <c r="P46" s="14" t="inlineStr">
+      <c r="P47" s="14" t="inlineStr">
         <is>
           <t>• Aylık hacim: 'turkcell uygulamasına giriş yapamıyorum' 110
 • Search Console: 22.225 impression · 1.929 click · ağırlıklı konum 5,2
@@ -6930,101 +7041,101 @@
 • Cevabın büyük bölümü marka verisine bağlı olduğu için sayfa son faza alınmıştır.</t>
         </is>
       </c>
-      <c r="Q46" s="14" t="inlineStr">
+      <c r="Q47" s="14" t="inlineStr">
         <is>
           <t>Turkcell Uygulaması ile kalan kullanım ve paket bilgileri görüntülenebilir, fatura incelenip ödenebilir ve talepler iletilebilir. [Marka doğrulaması bekliyor] (bireysel hatlarda uygulamaya giriş yöntemleri, şifre alma ve şifre yenileme adımları, uygulama açılmadığında önerilen kontroller) Giriş yapılamamaya devam ederse Turkcell Müşteri Hizmetleri'nden (532) destek alınabilir.</t>
         </is>
       </c>
-      <c r="R46" s="14" t="inlineStr">
+      <c r="R47" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hizmet-kanallarimiz/self-servis/turkcell-uygulamasi
 https://www.turkcell.com.tr/destek/hizmet-kanallarimiz/musteri-hizmetleri/532-turkcell-musteri-hizmetleri</t>
         </is>
       </c>
-      <c r="S46" s="14" t="inlineStr">
+      <c r="S47" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hizmet-kanallarimiz/self-servis/turkcell-uygulamasi
 https://www.turkcell.com.tr/servisler/uygulamalar/turkcell-uygulamasi</t>
         </is>
       </c>
-      <c r="T46" s="14" t="inlineStr">
+      <c r="T47" s="14" t="inlineStr">
         <is>
           <t>Bireysel hatlarda şifre alma yöntemi (SMS anahtar kelimesi, uygulama içi akış), Hızlı Giriş'in güncelliği, sık görülen giriş engelleri.</t>
         </is>
       </c>
-      <c r="U46" s="14" t="inlineStr">
+      <c r="U47" s="14" t="inlineStr">
         <is>
           <t>turkcell şifre alma · turkcell uygulama giriş yapamıyorum · turkcell uygulama açılmıyor</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="11" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="20" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="11" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
         <is>
           <t>Faz 3</t>
         </is>
       </c>
-      <c r="C47" s="14" t="inlineStr">
+      <c r="C48" s="14" t="inlineStr">
         <is>
           <t>Turkcell'de GNÇ paketlerinden kimler yararlanabilir?</t>
         </is>
       </c>
-      <c r="D47" s="14" t="inlineStr">
+      <c r="D48" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/paket-ve-tarife-satisi/turkcellde-ogrenci-ve-genc-paketlerinden-kimler-yararlanabilir</t>
         </is>
       </c>
-      <c r="E47" s="17" t="inlineStr">
+      <c r="E48" s="17" t="inlineStr">
         <is>
           <t>tarife-ve-paketler</t>
         </is>
       </c>
-      <c r="F47" s="17" t="inlineStr">
+      <c r="F48" s="17" t="inlineStr">
         <is>
           <t>paket-ve-tarife-satisi</t>
         </is>
       </c>
-      <c r="G47" s="20" t="inlineStr">
+      <c r="G48" s="20" t="inlineStr">
         <is>
           <t>Hayır</t>
         </is>
       </c>
-      <c r="H47" s="14" t="inlineStr">
+      <c r="H48" s="14" t="inlineStr">
         <is>
           <t>turkcell gnç paketleri</t>
         </is>
       </c>
-      <c r="I47" s="19" t="n">
+      <c r="I48" s="19" t="n">
         <v>1600</v>
       </c>
-      <c r="J47" s="19" t="n">
+      <c r="J48" s="19" t="n">
         <v>11980</v>
       </c>
-      <c r="K47" s="19" t="n">
+      <c r="K48" s="19" t="n">
         <v>1082</v>
       </c>
-      <c r="L47" s="11" t="n">
+      <c r="L48" s="11" t="n">
         <v>6.2</v>
       </c>
-      <c r="M47" s="20" t="inlineStr">
+      <c r="M48" s="20" t="inlineStr">
         <is>
           <t>Yok</t>
         </is>
       </c>
-      <c r="N47" s="14" t="inlineStr">
+      <c r="N48" s="14" t="inlineStr">
         <is>
           <t>B · Sorgu başka sayfa tipine düşüyor</t>
         </is>
       </c>
-      <c r="O47" s="14" t="inlineStr">
+      <c r="O48" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi · Search Console 12 ay</t>
         </is>
       </c>
-      <c r="P47" s="14" t="inlineStr">
+      <c r="P48" s="14" t="inlineStr">
         <is>
           <t>• Aylık hacim: 'turkcell gnç paketleri' 1.600
 • Search Console: 11.980 impression · 1.082 click · ağırlıklı konum 6,2
@@ -7034,103 +7145,103 @@
 • 5G Ultra GNÇ sayfasında yaş sınırı başlıkta ve katılım koşulunda farklı yazıldığından bu paketin yaş sınırı cevaba konmamıştır.</t>
         </is>
       </c>
-      <c r="Q47" s="14" t="inlineStr">
+      <c r="Q48" s="14" t="inlineStr">
         <is>
           <t>Turkcell'de gençlere yönelik paketler GNÇ paketleri adıyla sunulur ve yaş koşuluna bağlıdır. Örneğin faturasız GNÇ Fırsat 20 GB paketinden 7 yaş ve üzeri, 25 yaş ve altındaki bireysel faturasız ses hattı müşterileri yararlanabilir. Faturalı GNÇ paketlerinin katılım koşulları, yaş sınırı ve yeni hat ya da numara taşıma şartı ilgili paketin sayfasında yer alır. GNÇ mobil uygulaması ise operatör ayrımı olmadan gençlere açıktır. [Marka doğrulaması bekliyor] (faturalı 5G Ultra GNÇ paketinde geçerli yaş sınırı)</t>
         </is>
       </c>
-      <c r="R47" s="14" t="inlineStr">
+      <c r="R48" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/paket-ve-tarifeler/ana-paketler/gnc-firsat-20-gb
 https://www.turkcell.com.tr/paket-ve-tarifeler/yeni-musteri-paketleri/5g-ultra-gnc-40-gb
 https://www.turkcell.com.tr/gnc/</t>
         </is>
       </c>
-      <c r="S47" s="14" t="inlineStr">
+      <c r="S48" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/gnc/
 https://www.turkcell.com.tr/paket-ve-tarifeler/ana-paketler/gnc-firsat-20-gb
 https://www.turkcell.com.tr/paket-ve-tarifeler/yeni-musteri-paketleri/5g-ultra-gnc-40-gb</t>
         </is>
       </c>
-      <c r="T47" s="14" t="inlineStr">
+      <c r="T48" s="14" t="inlineStr">
         <is>
           <t>5G Ultra GNÇ yaş sınırı (başlıkta 25, katılım koşulunda 26; çelişki listesinde).</t>
         </is>
       </c>
-      <c r="U47" s="14" t="inlineStr">
+      <c r="U48" s="14" t="inlineStr">
         <is>
           <t>gnç turkcell yaş sınırı · turkcell gnc kaç yaş · gnç kaç yaşa kadar · turkcell öğrenci tarifeleri</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="11" t="n">
-        <v>44</v>
-      </c>
-      <c r="B48" s="20" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
         <is>
           <t>Faz 3</t>
         </is>
       </c>
-      <c r="C48" s="14" t="inlineStr">
+      <c r="C49" s="14" t="inlineStr">
         <is>
           <t>Turkcell eSIM yurt dışında kullanılabilir mi?</t>
         </is>
       </c>
-      <c r="D48" s="14" t="inlineStr">
+      <c r="D49" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/esim/esim-yurt-disinda-kullanilabilir-mi</t>
         </is>
       </c>
-      <c r="E48" s="17" t="inlineStr">
+      <c r="E49" s="17" t="inlineStr">
         <is>
           <t>servisler-ve-internet</t>
         </is>
       </c>
-      <c r="F48" s="17" t="inlineStr">
+      <c r="F49" s="17" t="inlineStr">
         <is>
           <t>esim</t>
         </is>
       </c>
-      <c r="G48" s="18" t="inlineStr">
+      <c r="G49" s="18" t="inlineStr">
         <is>
           <t>Evet</t>
         </is>
       </c>
-      <c r="H48" s="14" t="inlineStr">
+      <c r="H49" s="14" t="inlineStr">
         <is>
           <t>esim yurtdışı</t>
         </is>
       </c>
-      <c r="I48" s="19" t="n">
+      <c r="I49" s="19" t="n">
         <v>480</v>
       </c>
-      <c r="J48" s="19" t="n">
+      <c r="J49" s="19" t="n">
         <v>7611</v>
       </c>
-      <c r="K48" s="19" t="n">
+      <c r="K49" s="19" t="n">
         <v>919</v>
       </c>
-      <c r="L48" s="11" t="n">
+      <c r="L49" s="11" t="n">
         <v>7.2</v>
       </c>
-      <c r="M48" s="18" t="inlineStr">
+      <c r="M49" s="18" t="inlineStr">
         <is>
           <t>Var</t>
         </is>
       </c>
-      <c r="N48" s="14" t="inlineStr">
+      <c r="N49" s="14" t="inlineStr">
         <is>
           <t>C · Talep var, sayfa yok</t>
         </is>
       </c>
-      <c r="O48" s="14" t="inlineStr">
+      <c r="O49" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi · Search Console 12 ay</t>
         </is>
       </c>
-      <c r="P48" s="14" t="inlineStr">
+      <c r="P49" s="14" t="inlineStr">
         <is>
           <t>• Aylık hacim: 'esim yurtdışı' 480
 • Search Console: 7.611 impression · 919 click · ağırlıklı konum 7,2
@@ -7139,103 +7250,103 @@
 • Yurt dışı kullanımda paketsiz kullanım ve Tarifen Yurt Dışında Geçerli seçenekleri bulunduğundan cevap, paket tanımlamayı zorunlu değil önerilen yol olarak anlatmaktadır.</t>
         </is>
       </c>
-      <c r="Q48" s="14" t="inlineStr">
+      <c r="Q49" s="14" t="inlineStr">
         <is>
           <t>Turkcell eSIM hattı, fiziksel SIM kartlı hatlarla aynı koşullarda yurt dışında kullanılabilir. Kullanım için hattın yurt dışı kullanıma açık olması gerekir; bu ayar faturalı hatlarda yurt içindeyken ROAM yazıp 2200'e ücretsiz SMS gönderilerek, Hazır Kart hatlarda *111# tuşlanarak ya da turkcell.com.tr İşlem Merkezi'ndeki Yurt Dışı Ayarlarım adımından yapılabilir. Yurt dışındaki internet kullanımı tanımlı yurt dışı paketine, Tarifen Yurt Dışında Geçerli özelliğine ya da paketsiz kullanım ücretlerine göre ücretlendirilir. eSIM destekleyen cihazlarda birden fazla hat saklanabildiği için Turkcell hattı açık tutulurken aynı cihaza gidilen ülkede kullanılacak yerel bir eSIM profili de eklenebilir.</t>
         </is>
       </c>
-      <c r="R48" s="14" t="inlineStr">
+      <c r="R49" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/yurtdisi/yurtdisinda-kullanim/yurtdisina-cikmadan-telefonumu-kullanmak-icin-neler-yapmaliyim
 https://www.turkcell.com.tr/destek/yurtdisi/yurtdisinda-kullanim/yurtdisinda-hesapli-kullanim-icin-nelere-dikkat-etmem-gerekir
 https://www.turkcell.com.tr/esim</t>
         </is>
       </c>
-      <c r="S48" s="14" t="inlineStr">
+      <c r="S49" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/yurtdisi/yurtdisinda-kullanim/yurtdisina-cikmadan-telefonumu-kullanmak-icin-neler-yapmaliyim
 https://www.turkcell.com.tr/destek/yurtdisi/yurtdisinda-kullanim/yurtdisinda-hesapli-kullanim-icin-nelere-dikkat-etmem-gerekir
 Önerilen: https://www.turkcell.com.tr/destek/yurtdisi/yurtdisinda-kullanim/roaming-nedir-ve-nasil-calisir</t>
         </is>
       </c>
-      <c r="T48" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U48" s="14" t="inlineStr">
+      <c r="T49" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U49" s="14" t="inlineStr">
         <is>
           <t>e-sim yurtdışı paketleri turkcell · turkcell e-sim yurtdışı telefon · yurt dışı telefon e sim</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="20" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
         <is>
           <t>Faz 3</t>
         </is>
       </c>
-      <c r="C49" s="14" t="inlineStr">
+      <c r="C50" s="14" t="inlineStr">
         <is>
           <t>Turkcell abonelik sözleşmesine nasıl ulaşılır?</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcellli-olmak/turkcell-abonelik-sozlesmesine-nasil-ulasilir</t>
         </is>
       </c>
-      <c r="E49" s="17" t="inlineStr">
+      <c r="E50" s="17" t="inlineStr">
         <is>
           <t>turkcellli-olmak</t>
         </is>
       </c>
-      <c r="F49" s="17" t="inlineStr">
+      <c r="F50" s="17" t="inlineStr">
         <is>
           <t>turkcellli-olmak</t>
         </is>
       </c>
-      <c r="G49" s="20" t="inlineStr">
+      <c r="G50" s="20" t="inlineStr">
         <is>
           <t>Hayır</t>
         </is>
       </c>
-      <c r="H49" s="14" t="inlineStr">
+      <c r="H50" s="14" t="inlineStr">
         <is>
           <t>turkcell abonelik sözleşmesi</t>
         </is>
       </c>
-      <c r="I49" s="19" t="n">
+      <c r="I50" s="19" t="n">
         <v>210</v>
       </c>
-      <c r="J49" s="19" t="n">
+      <c r="J50" s="19" t="n">
         <v>7591</v>
       </c>
-      <c r="K49" s="19" t="n">
+      <c r="K50" s="19" t="n">
         <v>2099</v>
       </c>
-      <c r="L49" s="11" t="n">
+      <c r="L50" s="11" t="n">
         <v>3.8</v>
       </c>
-      <c r="M49" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N49" s="14" t="inlineStr">
+      <c r="M50" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="14" t="inlineStr">
         <is>
           <t>B · Sorgu başka sayfa tipine düşüyor</t>
         </is>
       </c>
-      <c r="O49" s="14" t="inlineStr">
+      <c r="O50" s="14" t="inlineStr">
         <is>
           <t>Rakip destek karşılaştırması · Search Console 12 ay</t>
         </is>
       </c>
-      <c r="P49" s="14" t="inlineStr">
+      <c r="P50" s="14" t="inlineStr">
         <is>
           <t>• Aylık hacim: 'turkcell abonelik sözleşmesi' 210
 • Search Console: 7.591 impression · 2.099 click · ağırlıklı konum 3,8
@@ -7244,99 +7355,99 @@
 • Erişim kanalları sitede bulunamadığı için cevabın özü marka verisine bağlıdır.</t>
         </is>
       </c>
-      <c r="Q49" s="14" t="inlineStr">
+      <c r="Q50" s="14" t="inlineStr">
         <is>
           <t>Yeni hat ve numara taşıma gibi evraklı işlemlerde abonelik sözleşmesi Güvenli Dijital İmza ile tablet üzerinde imzalanabilmekte ve imza sözleşmeyle birlikte biyometrik olarak saklanmaktadır. [Marka doğrulaması bekliyor] (abonenin kendi adına düzenlenmiş sözleşmenin kopyasına erişim kanalları, talep için gerekli bilgiler ve süre; örnek bireysel abonelik sözleşmesinin yayın adresi)</t>
         </is>
       </c>
-      <c r="R49" s="14" t="inlineStr">
+      <c r="R50" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/guvenli-dijital-imza-nedir-ve-neden-guvenlidir</t>
         </is>
       </c>
-      <c r="S49" s="14" t="inlineStr">
+      <c r="S50" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/guvenli-dijital-imza-nedir-ve-neden-guvenlidir</t>
         </is>
       </c>
-      <c r="T49" s="14" t="inlineStr">
+      <c r="T50" s="14" t="inlineStr">
         <is>
           <t>İmzalı sözleşme kopyasının hangi kanallardan, hangi sürede alınabildiği; e-Devlet üzerinden görüntüleme olup olmadığı.</t>
         </is>
       </c>
-      <c r="U49" s="14" t="inlineStr">
+      <c r="U50" s="14" t="inlineStr">
         <is>
           <t>turkcell abonelik sözleşmesi sorgulama · turkcell abonelik sözleşmesi nasıl alınır · turkcell abonelik sözleşmesi e devlet</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="11" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="20" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
         <is>
           <t>Faz 3</t>
         </is>
       </c>
-      <c r="C50" s="14" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <t>Turkcell mobil internetim neden yavaş?</t>
         </is>
       </c>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="D51" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/internet/internetim-neden-yavas</t>
         </is>
       </c>
-      <c r="E50" s="17" t="inlineStr">
+      <c r="E51" s="17" t="inlineStr">
         <is>
           <t>servisler-ve-internet</t>
         </is>
       </c>
-      <c r="F50" s="17" t="inlineStr">
+      <c r="F51" s="17" t="inlineStr">
         <is>
           <t>internet</t>
         </is>
       </c>
-      <c r="G50" s="20" t="inlineStr">
+      <c r="G51" s="20" t="inlineStr">
         <is>
           <t>Hayır</t>
         </is>
       </c>
-      <c r="H50" s="14" t="inlineStr">
+      <c r="H51" s="14" t="inlineStr">
         <is>
           <t>turkcell internet yavaş</t>
         </is>
       </c>
-      <c r="I50" s="19" t="n">
+      <c r="I51" s="19" t="n">
         <v>210</v>
       </c>
-      <c r="J50" s="19" t="n">
+      <c r="J51" s="19" t="n">
         <v>3313</v>
       </c>
-      <c r="K50" s="19" t="n">
+      <c r="K51" s="19" t="n">
         <v>771</v>
       </c>
-      <c r="L50" s="11" t="n">
+      <c r="L51" s="11" t="n">
         <v>3.1</v>
       </c>
-      <c r="M50" s="18" t="inlineStr">
+      <c r="M51" s="18" t="inlineStr">
         <is>
           <t>Var</t>
         </is>
       </c>
-      <c r="N50" s="14" t="inlineStr">
+      <c r="N51" s="14" t="inlineStr">
         <is>
           <t>C · Talep var, sayfa yok</t>
         </is>
       </c>
-      <c r="O50" s="14" t="inlineStr">
+      <c r="O51" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi · Search Console 12 ay</t>
         </is>
       </c>
-      <c r="P50" s="14" t="inlineStr">
+      <c r="P51" s="14" t="inlineStr">
         <is>
           <t>• Aylık hacim: 'turkcell internet yavaş' 210
 • Search Console: 3.313 impression · 771 click · ağırlıklı konum 3,1
@@ -7345,102 +7456,102 @@
 • Kota sonrası hız düşürme ifadesi bireysel mobil paketler için doğrulanamadığından çıkarılmıştır.</t>
         </is>
       </c>
-      <c r="Q50" s="14" t="inlineStr">
+      <c r="Q51" s="14" t="inlineStr">
         <is>
           <t>Mobil internet hızı; kullanılan cihazın uyumluluğu, bulunulan konum, bölgedeki kullanım yoğunluğu, baz istasyonuna olan uzaklık ve kapalı alandaki sinyal koşullarına göre değişebilir. Arka planda çalışan güncellemeler ve yüksek çözünürlüklü video akışı da bant genişliğini tüketerek hızın düşük hissedilmesine yol açabilir. İlk kontrol adımı kalan internet kullanımının Turkcell Uygulaması ya da İşlem Merkezi üzerinden görüntülenmesidir. Ardından Turkcell hız testi ile ölçüm yapılır ve farklı bir konumda sonucun değişip değişmediği gözlenir; bağlantı Turkcell Uygulaması'ndaki Teknocan aracılığıyla yenilenebilir. İnternete kablosuz ağ üzerinden bağlanılıyorsa modeme yakın bir noktada tekrar ölçüm yapılması, yavaşlığın şebekeden mi yerel ağdan mı kaynaklandığını ayırt etmeye yardımcı olur.</t>
         </is>
       </c>
-      <c r="R50" s="14" t="inlineStr">
+      <c r="R51" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/5g/ayarlar-sorun-giderme-telefon/5g-gorunuyor-ama-internet-yavas-durumunda-ilk-kontrol-adimlari-neler
 https://www.turkcell.com.tr/hiz-testi</t>
         </is>
       </c>
-      <c r="S50" s="14" t="inlineStr">
+      <c r="S51" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/hiz-testi
 https://www.turkcell.com.tr/destek/5g/ayarlar-sorun-giderme-telefon/5g-gorunuyor-ama-internet-yavas-durumunda-ilk-kontrol-adimlari-neler
 Önerilen: https://www.turkcell.com.tr/destek/servisler-ve-internet/internet/turkcell-sebekesinde-kesinti-olup-olmadigi-nasil-ogrenilir</t>
         </is>
       </c>
-      <c r="T50" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U50" s="14" t="inlineStr">
+      <c r="T51" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U51" s="14" t="inlineStr">
         <is>
           <t>turkcell internet neden yavaş · turkcell internet çok yavaş · mobil internet neden yavaş</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="11" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="20" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
         <is>
           <t>Faz 3</t>
         </is>
       </c>
-      <c r="C51" s="14" t="inlineStr">
+      <c r="C52" s="14" t="inlineStr">
         <is>
           <t>Akıllı saat için hangi SIM kart ve hat gerekir?</t>
         </is>
       </c>
-      <c r="D51" s="14" t="inlineStr">
+      <c r="D52" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcellli-olmak/akilli-saat-icin-hangi-sim-kart-ve-hat-gerekir</t>
         </is>
       </c>
-      <c r="E51" s="17" t="inlineStr">
+      <c r="E52" s="17" t="inlineStr">
         <is>
           <t>turkcellli-olmak</t>
         </is>
       </c>
-      <c r="F51" s="17" t="inlineStr">
+      <c r="F52" s="17" t="inlineStr">
         <is>
           <t>turkcellli-olmak</t>
         </is>
       </c>
-      <c r="G51" s="20" t="inlineStr">
+      <c r="G52" s="20" t="inlineStr">
         <is>
           <t>Hayır</t>
         </is>
       </c>
-      <c r="H51" s="14" t="inlineStr">
+      <c r="H52" s="14" t="inlineStr">
         <is>
           <t>akıllı saat sim kart</t>
         </is>
       </c>
-      <c r="I51" s="19" t="n">
+      <c r="I52" s="19" t="n">
         <v>2900</v>
       </c>
-      <c r="J51" s="19" t="n">
+      <c r="J52" s="19" t="n">
         <v>1572</v>
       </c>
-      <c r="K51" s="19" t="n">
+      <c r="K52" s="19" t="n">
         <v>399</v>
       </c>
-      <c r="L51" s="11" t="n">
+      <c r="L52" s="11" t="n">
         <v>4.2</v>
       </c>
-      <c r="M51" s="18" t="inlineStr">
+      <c r="M52" s="18" t="inlineStr">
         <is>
           <t>Var</t>
         </is>
       </c>
-      <c r="N51" s="14" t="inlineStr">
+      <c r="N52" s="14" t="inlineStr">
         <is>
           <t>D · Prompt, İlgili Sorular ya da rakip</t>
         </is>
       </c>
-      <c r="O51" s="14" t="inlineStr">
+      <c r="O52" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi · Search Console 12 ay</t>
         </is>
       </c>
-      <c r="P51" s="14" t="inlineStr">
+      <c r="P52" s="14" t="inlineStr">
         <is>
           <t>• Aylık hacim: 'akıllı saat sim kart' 2.900
 • Search Console: 1.572 impression · 399 click · ağırlıklı konum 4,2
@@ -7449,102 +7560,102 @@
 • Bireysel hücresel saat tarifesi sayfası 'abone alımına kapalı' uyarısı taşıdığı için ürün adı ve fiyat cevaba konmamıştır; ilk taslaktaki 'saatlerin büyük bölümü eSIM yükler' genellemesi Turkcell çocuk saati tarifeleri SIM kartlı saatler için sunulduğundan çıkarılmıştır.</t>
         </is>
       </c>
-      <c r="Q51" s="14" t="inlineStr">
+      <c r="Q52" s="14" t="inlineStr">
         <is>
           <t>Akıllı saatlerde ihtiyaç duyulan hat, saatin türüne göre değişir. Hücresel bağlantı özelliği bulunmayan saatler telefona bağlanarak çalışır ve ayrı bir hat gerektirmez. Akıllı çocuk saatlerinde ise saate ayrı bir hat tanımlanır; Turkcell akıllı çocuk saati tarifeleri, tarife sayfasında listelenen çocuk saati modellerinde sunulur. [Marka doğrulaması bekliyor] (hücresel bağlantılı saatlerde telefon numarasındaki paket içeriklerinin saatte kullanılmasını sağlayan güncel bireysel teklif)</t>
         </is>
       </c>
-      <c r="R51" s="14" t="inlineStr">
+      <c r="R52" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/paket-ve-tarifeler/konusma/akilli-saat-tarifesi
 https://www.turkcell.com.tr/turkcellcocuk</t>
         </is>
       </c>
-      <c r="S51" s="14" t="inlineStr">
+      <c r="S52" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/paket-ve-tarifeler/konusma/akilli-saat-tarifesi
 https://www.turkcell.com.tr/turkcellcocuk
 Önerilen: https://www.turkcell.com.tr/destek/servisler-ve-internet/esim/hangi-cihazlar-esim-destekliyor</t>
         </is>
       </c>
-      <c r="T51" s="14" t="inlineStr">
+      <c r="T52" s="14" t="inlineStr">
         <is>
           <t>Bireysel hücresel saat tarifesinin güncel durumu (bireysel sayfada 'abone alımına kapalı', kurumsalda farklı adla sunuluyor).</t>
         </is>
       </c>
-      <c r="U51" s="14" t="inlineStr">
+      <c r="U52" s="14" t="inlineStr">
         <is>
           <t>turkcell akıllı saat sim kart · çocuk akıllı saat hattı telefona takılır mı · akıllı saate hat nasıl alınır</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="11" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="20" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="11" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
         <is>
           <t>Faz 3</t>
         </is>
       </c>
-      <c r="C52" s="14" t="inlineStr">
+      <c r="C53" s="14" t="inlineStr">
         <is>
           <t>Superbox kurulumu nasıl yapılır?</t>
         </is>
       </c>
-      <c r="D52" s="14" t="inlineStr">
+      <c r="D53" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/tasinabilir-internet/superbox-kurulumu-nasil-yapilir</t>
         </is>
       </c>
-      <c r="E52" s="17" t="inlineStr">
+      <c r="E53" s="17" t="inlineStr">
         <is>
           <t>servisler-ve-internet</t>
         </is>
       </c>
-      <c r="F52" s="17" t="inlineStr">
+      <c r="F53" s="17" t="inlineStr">
         <is>
           <t>tasinabilir-internet</t>
         </is>
       </c>
-      <c r="G52" s="18" t="inlineStr">
+      <c r="G53" s="18" t="inlineStr">
         <is>
           <t>Evet</t>
         </is>
       </c>
-      <c r="H52" s="14" t="inlineStr">
+      <c r="H53" s="14" t="inlineStr">
         <is>
           <t>superbox kurulumu</t>
         </is>
       </c>
-      <c r="I52" s="19" t="n">
+      <c r="I53" s="19" t="n">
         <v>170</v>
       </c>
-      <c r="J52" s="19" t="n">
+      <c r="J53" s="19" t="n">
         <v>353</v>
       </c>
-      <c r="K52" s="19" t="n">
+      <c r="K53" s="19" t="n">
         <v>121</v>
       </c>
-      <c r="L52" s="11" t="n">
+      <c r="L53" s="11" t="n">
         <v>3.6</v>
       </c>
-      <c r="M52" s="18" t="inlineStr">
+      <c r="M53" s="18" t="inlineStr">
         <is>
           <t>Var</t>
         </is>
       </c>
-      <c r="N52" s="14" t="inlineStr">
+      <c r="N53" s="14" t="inlineStr">
         <is>
           <t>C · Talep var, sayfa yok</t>
         </is>
       </c>
-      <c r="O52" s="14" t="inlineStr">
+      <c r="O53" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
-      <c r="P52" s="14" t="inlineStr">
+      <c r="P53" s="14" t="inlineStr">
         <is>
           <t>• Aylık hacim: 'superbox kurulumu' 170
 • Search Console: 353 impression · 121 click · ağırlıklı konum 3,6
@@ -7552,100 +7663,100 @@
 • Kurulum adımı sitede anlatılmamaktadır; talep düşük hacimli olmakla birlikte Superbox şifre ve adres sorularıyla aynı alt bölümü tamamlar.</t>
         </is>
       </c>
-      <c r="Q52" s="14" t="inlineStr">
+      <c r="Q53" s="14" t="inlineStr">
         <is>
           <t>Superbox kurulumu için kablo çekimi ya da bina içi tesisat gerekmez. Modem, 5G ya da 4.5G kapsaması bulunan adreste elektrik prizine takılarak çalıştırılır ve şebekeye bağlandıktan sonra kablosuz ağ yayını başlar. Evdeki cihazlar, kablosuz ağ listesinden modemin ağ adı seçilerek bağlanır. [Marka doğrulaması bekliyor] (modem modeline göre SIM kart yerleştirme adımı, gösterge ışıklarının anlamı ve varsayılan kablosuz ağ şifresinin bulunduğu yer)</t>
         </is>
       </c>
-      <c r="R52" s="14" t="inlineStr">
+      <c r="R53" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/ev-interneti/superbox</t>
         </is>
       </c>
-      <c r="S52" s="14" t="inlineStr">
+      <c r="S53" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/ev-interneti/superbox
 Önerilen: https://www.turkcell.com.tr/destek/servisler-ve-internet/tasinabilir-internet/superbox-modem-sifresi-nasil-degistirilir</t>
         </is>
       </c>
-      <c r="T52" s="14" t="inlineStr">
+      <c r="T53" s="14" t="inlineStr">
         <is>
           <t>Model bazlı kurulum adımları ve gösterge ışıkları.</t>
         </is>
       </c>
-      <c r="U52" s="14" t="inlineStr">
+      <c r="U53" s="14" t="inlineStr">
         <is>
           <t>turkcell superbox kurulum · superbox kurulum ücreti</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="11" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="20" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="20" t="inlineStr">
         <is>
           <t>Faz 3</t>
         </is>
       </c>
-      <c r="C53" s="14" t="inlineStr">
+      <c r="C54" s="14" t="inlineStr">
         <is>
           <t>Yurt dışında WhatsApp ve mesajlaşma uygulamaları nasıl ücretlendirilir?</t>
         </is>
       </c>
-      <c r="D53" s="14" t="inlineStr">
+      <c r="D54" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/yurtdisi/yurtdisinda-kullanim/yurt-disinda-whatsapp-ve-mesajlasma-uygulamalari-nasil-ucretlendirilir</t>
         </is>
       </c>
-      <c r="E53" s="17" t="inlineStr">
+      <c r="E54" s="17" t="inlineStr">
         <is>
           <t>yurtdisi</t>
         </is>
       </c>
-      <c r="F53" s="17" t="inlineStr">
+      <c r="F54" s="17" t="inlineStr">
         <is>
           <t>yurtdisinda-kullanim</t>
         </is>
       </c>
-      <c r="G53" s="20" t="inlineStr">
+      <c r="G54" s="20" t="inlineStr">
         <is>
           <t>Hayır</t>
         </is>
       </c>
-      <c r="H53" s="14" t="inlineStr">
+      <c r="H54" s="14" t="inlineStr">
         <is>
           <t>yurt dışında whatsapp</t>
         </is>
       </c>
-      <c r="I53" s="19" t="n">
+      <c r="I54" s="19" t="n">
         <v>140</v>
       </c>
-      <c r="J53" s="19" t="n">
+      <c r="J54" s="19" t="n">
         <v>73</v>
       </c>
-      <c r="K53" s="19" t="n">
+      <c r="K54" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="L53" s="11" t="n">
+      <c r="L54" s="11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="M53" s="18" t="inlineStr">
+      <c r="M54" s="18" t="inlineStr">
         <is>
           <t>Var</t>
         </is>
       </c>
-      <c r="N53" s="14" t="inlineStr">
+      <c r="N54" s="14" t="inlineStr">
         <is>
           <t>C · Talep var, sayfa yok</t>
         </is>
       </c>
-      <c r="O53" s="14" t="inlineStr">
+      <c r="O54" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
-      <c r="P53" s="14" t="inlineStr">
+      <c r="P54" s="14" t="inlineStr">
         <is>
           <t>• Aylık hacim: 'yurt dışında whatsapp' 140
 • Search Console: 73 impression · 9 click · ağırlıklı konum 9,2
@@ -7654,102 +7765,102 @@
 • İlk taslaktaki 'yurt içi mesajlaşma paketleri kapsamaz' ifadesi doğrulanamadığı için çıkarılmıştır.</t>
         </is>
       </c>
-      <c r="Q53" s="14" t="inlineStr">
+      <c r="Q54" s="14" t="inlineStr">
         <is>
           <t>WhatsApp ve benzeri mesajlaşma uygulamalarında yapılan yazışma, sesli ve görüntülü aramalar internet bağlantısı üzerinden çalışır; yurt dışında bu kullanım mobil veri kullanımı olarak değerlendirilir. Faturalı hatlarda Tarifen Yurt Dışında Geçerli özelliğinin geçerli olduğu ülkelerde kullanım yurt içi tarifedeki internet haklarından, yurt dışı internet paketi tanımlıysa bu paketten düşülür. Paket tanımlı olmadığında kullanım, yurt dışı paketsiz internet ücretleri üzerinden hesaplanır. Yurt içi ek paketlerin yurt dışında geçerli olup olmadığı ilgili paketin sayfasında belirtilir. Kablosuz ağ (Wi-Fi) üzerinden yapılan kullanımlar hattın internet haklarından düşülmez.</t>
         </is>
       </c>
-      <c r="R53" s="14" t="inlineStr">
+      <c r="R54" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/yurtdisi/yurtdisinda-kullanim/yurtici-paket-dakikalarimi-yurtdisinda-da-kullanabilir-miyim
 https://www.turkcell.com.tr/destek/yurtdisi/yurtdisinda-kullanim/yurtdisinda-hesapli-kullanim-icin-nelere-dikkat-etmem-gerekir
 https://www.turkcell.com.tr/paket-ve-tarifeler/ek-paketler/3-gb-internet-paketi</t>
         </is>
       </c>
-      <c r="S53" s="14" t="inlineStr">
+      <c r="S54" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/yurtdisi/yurtdisinda-kullanim/yurtdisinda-hesapli-kullanim-icin-nelere-dikkat-etmem-gerekir
 Önerilen: https://www.turkcell.com.tr/destek/yurtdisi/yurtdisinda-kullanim/roaming-nedir-ve-nasil-calisir</t>
         </is>
       </c>
-      <c r="T53" s="14" t="inlineStr">
+      <c r="T54" s="14" t="inlineStr">
         <is>
           <t>Mesajlaşma uygulamalarına özel yurt dışı paketi olup olmadığı.</t>
         </is>
       </c>
-      <c r="U53" s="14" t="inlineStr">
+      <c r="U54" s="14" t="inlineStr">
         <is>
           <t>yurtdışı whatsapp araması ücretli mi · yurt dışında whatsapp kullanımı</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="B54" s="20" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="11" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="20" t="inlineStr">
         <is>
           <t>Faz 3</t>
         </is>
       </c>
-      <c r="C54" s="14" t="inlineStr">
+      <c r="C55" s="14" t="inlineStr">
         <is>
           <t>Superbox kotası bitince ne olur?</t>
         </is>
       </c>
-      <c r="D54" s="14" t="inlineStr">
+      <c r="D55" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/tasinabilir-internet/superbox-kotasi-bitince-ne-oluyor</t>
         </is>
       </c>
-      <c r="E54" s="17" t="inlineStr">
+      <c r="E55" s="17" t="inlineStr">
         <is>
           <t>servisler-ve-internet</t>
         </is>
       </c>
-      <c r="F54" s="17" t="inlineStr">
+      <c r="F55" s="17" t="inlineStr">
         <is>
           <t>tasinabilir-internet</t>
         </is>
       </c>
-      <c r="G54" s="18" t="inlineStr">
+      <c r="G55" s="18" t="inlineStr">
         <is>
           <t>Evet</t>
         </is>
       </c>
-      <c r="H54" s="14" t="inlineStr">
+      <c r="H55" s="14" t="inlineStr">
         <is>
           <t>superbox kota bitince ne olur</t>
         </is>
       </c>
-      <c r="I54" s="19" t="n">
+      <c r="I55" s="19" t="n">
         <v>40</v>
       </c>
-      <c r="J54" s="19" t="n">
+      <c r="J55" s="19" t="n">
         <v>67</v>
       </c>
-      <c r="K54" s="19" t="n">
+      <c r="K55" s="19" t="n">
         <v>17</v>
       </c>
-      <c r="L54" s="11" t="n">
+      <c r="L55" s="11" t="n">
         <v>2.1</v>
       </c>
-      <c r="M54" s="18" t="inlineStr">
+      <c r="M55" s="18" t="inlineStr">
         <is>
           <t>Var</t>
         </is>
       </c>
-      <c r="N54" s="14" t="inlineStr">
+      <c r="N55" s="14" t="inlineStr">
         <is>
           <t>C · Talep var, sayfa yok</t>
         </is>
       </c>
-      <c r="O54" s="14" t="inlineStr">
+      <c r="O55" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
-      <c r="P54" s="14" t="inlineStr">
+      <c r="P55" s="14" t="inlineStr">
         <is>
           <t>• Aylık hacim: 'superbox kota bitince ne olur' 40
 • Search Console: 67 impression · 17 click · ağırlıklı konum 2,1
@@ -7758,103 +7869,103 @@
 • Kalan kota sorgusu mevcut sayfada karşılandığı için sayfa yalnızca kota bitimindeki işleyişi anlatır.</t>
         </is>
       </c>
-      <c r="Q54" s="14" t="inlineStr">
+      <c r="Q55" s="14" t="inlineStr">
         <is>
           <t>Kotalı Superbox paketlerinde aylık internet kotası tamamlandığında internet kullanımı durur. Kullanıma devam edilebilmesi için Turkcell Uygulaması, Turkcell Müşteri Hizmetleri ya da Turkcell satış noktaları üzerinden Superbox data ek paketi alınabilir. Güncel Superbox ek paket seçenekleri ve ücretleri Superbox ve ek paketler sayfasında yer alır. [Marka doğrulaması bekliyor] (kota bitimi bilgilendirmesi ve kullanılmayan hakların devir kuralı)</t>
         </is>
       </c>
-      <c r="R54" s="14" t="inlineStr">
+      <c r="R55" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/ev-interneti/bireysel-superbox-tarife-detaylari
 https://www.turkcell.com.tr/paket-ve-tarifeler/superbox-ve-ek-paketler</t>
         </is>
       </c>
-      <c r="S54" s="14" t="inlineStr">
+      <c r="S55" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/paket-ve-tarifeler/superbox-ve-ek-paketler
 https://www.turkcell.com.tr/destek/servisler-ve-internet/internet/kalanimi-nasil-sorgulayabilirim</t>
         </is>
       </c>
-      <c r="T54" s="14" t="inlineStr">
+      <c r="T55" s="14" t="inlineStr">
         <is>
           <t>Kota bitiminde bilgilendirme yapılıp yapılmadığı; kalan kota için önerilecek kısa kod (KALAN kısa numarası çelişki listesinde).</t>
         </is>
       </c>
-      <c r="U54" s="14" t="inlineStr">
+      <c r="U55" s="14" t="inlineStr">
         <is>
           <t>superbox kota · superbox ek paket</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="20" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="11" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
         <is>
           <t>Faz 3</t>
         </is>
       </c>
-      <c r="C55" s="14" t="inlineStr">
+      <c r="C56" s="14" t="inlineStr">
         <is>
           <t>Taahhütlü hat devredilebilir mi?</t>
         </is>
       </c>
-      <c r="D55" s="14" t="inlineStr">
+      <c r="D56" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/taahhut-ve-cayma/taahhutlu-hat-devredilebilir-mi</t>
         </is>
       </c>
-      <c r="E55" s="17" t="inlineStr">
+      <c r="E56" s="17" t="inlineStr">
         <is>
           <t>hattiniz</t>
         </is>
       </c>
-      <c r="F55" s="17" t="inlineStr">
+      <c r="F56" s="17" t="inlineStr">
         <is>
           <t>taahhut-ve-cayma</t>
         </is>
       </c>
-      <c r="G55" s="18" t="inlineStr">
+      <c r="G56" s="18" t="inlineStr">
         <is>
           <t>Evet</t>
         </is>
       </c>
-      <c r="H55" s="14" t="inlineStr">
+      <c r="H56" s="14" t="inlineStr">
         <is>
           <t>taahhütlü hat devri</t>
         </is>
       </c>
-      <c r="I55" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="19" t="n">
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J56" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="K55" s="19" t="n">
+      <c r="K56" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="L55" s="11" t="n">
+      <c r="L56" s="11" t="n">
         <v>4.7</v>
       </c>
-      <c r="M55" s="20" t="inlineStr">
+      <c r="M56" s="20" t="inlineStr">
         <is>
           <t>Yok</t>
         </is>
       </c>
-      <c r="N55" s="14" t="inlineStr">
+      <c r="N56" s="14" t="inlineStr">
         <is>
           <t>D · Prompt, İlgili Sorular ya da rakip</t>
         </is>
       </c>
-      <c r="O55" s="14" t="inlineStr">
+      <c r="O56" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
-      <c r="P55" s="14" t="inlineStr">
+      <c r="P56" s="14" t="inlineStr">
         <is>
           <t>• Aylık hacim: 'taahhütlü hat devri' · Keyword Planner'da hacim yok
 • Search Console: 7 impression · 6 click · ağırlıklı konum 4,7
@@ -7863,12 +7974,12 @@
 • Devirde kampanya erken iptal ücretinin kime yansıdığı iki sayfada farklı çerçevede anlatıldığından bu kısım cevaba yazılmamış, doğrulama listesine alınmıştır.</t>
         </is>
       </c>
-      <c r="Q55" s="14" t="inlineStr">
+      <c r="Q56" s="14" t="inlineStr">
         <is>
           <t>Taahhütlü kampanya tanımlı bir hattın başka bir kişiye devri, Turkcell Taahhütlü Abonelik koşullarında kampanya yükümlülüğüne aykırılık olarak tanımlanır ve kampanya yeni aboneye aktarılmaz. Devir başvuru tarihi itibarıyla faturalandırılmış borçlar devreden kişinin ödeme sorumluluğundadır. Hatta Financell kredili cihaz kampanyası bulunuyorsa devir ile birlikte tarife kampanyası ve Financell kredisi de iptal olur. Devir işlemi Turkcell Mağazaları'ndan yapılır; Esnek Devir ile devreden ve devralanın aynı anda aynı mağazada bulunması gerekmez. [Marka doğrulaması bekliyor] (devir durumunda cayma bedelinin devredene mi devralana mı yansıtıldığı)</t>
         </is>
       </c>
-      <c r="R55" s="14" t="inlineStr">
+      <c r="R56" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/hakkimizda/duyurular/taahhutlu-abonelik
 https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/devir-icin-hangi-vergiler-ve-ucretler-odenir
@@ -7876,26 +7987,26 @@
 https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/esnek-devir</t>
         </is>
       </c>
-      <c r="S55" s="14" t="inlineStr">
+      <c r="S56" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/devir-icin-hangi-vergiler-ve-ucretler-odenir
 https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/esnek-devir
 Önerilen: https://www.turkcell.com.tr/destek/hattiniz/taahhut-ve-cayma/cayma-bedeli-nedir-ve-nasil-hesaplanir</t>
         </is>
       </c>
-      <c r="T55" s="14" t="inlineStr">
+      <c r="T56" s="14" t="inlineStr">
         <is>
           <t>Devirde cayma bedeli ve faturaya dönüşmemiş kampanya erken iptal ücretinin hangi tarafa yansıdığı (çelişki listesinde).</t>
         </is>
       </c>
-      <c r="U55" s="14" t="inlineStr">
+      <c r="U56" s="14" t="inlineStr">
         <is>
           <t>taahhüt bitmeden hat devretme · taahhütlü hat devredilir mi</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:U55"/>
+  <autoFilter ref="A4:U56"/>
   <mergeCells count="1">
     <mergeCell ref="A2:U2"/>
   </mergeCells>
@@ -7909,7 +8020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O62"/>
+  <dimension ref="A1:O64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8919,15 +9030,89 @@
       </c>
       <c r="C16" s="14" t="inlineStr">
         <is>
+          <t>https://www.turkcell.com.tr/paket-ve-tarifeler/turkcell-rahat</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>5G Gücünde Turkcell Rahat</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>• Sayfaya soru-cevap bloğu eklenmesi (iptal, ek paket, paket bitiminde kullanımın durması, faturasıza geçiş)
+• Soru-cevap bloğunun FAQPage olarak işaretlenmesi
+• Önerilen Turkcell Rahat iptal destek sayfasına iç link verilmesi</t>
+        </is>
+      </c>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>İçerik + Teknik</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>3472110</v>
+      </c>
+      <c r="I16" s="19" t="n">
+        <v>18150</v>
+      </c>
+      <c r="J16" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>turkcell rahat paket · turkcell rahat nedir · turkcell rahat tarife</t>
+        </is>
+      </c>
+      <c r="L16" s="14" t="inlineStr">
+        <is>
+          <t>Ticari Rahat sayfası tarifenin tanımını, özelliklerini, faturalı ve faturasız modelle karşılaştırmasını ve Rahat'a geçiş adımlarını anlatmaktadır; 'turkcell rahat paket nedir' ve 'turkcell rahat nedir' sorgularında ilk sıralarda yer almaktadır. Sayfada soru-cevap bloğu bulunmamakta, iptal ve Rahat'tan çıkış soruları karşılanmamaktadır.</t>
+        </is>
+      </c>
+      <c r="M16" s="14" t="inlineStr">
+        <is>
+          <t>Sayfaya soru-cevap bloğu eklenmesi ve bu bloğun FAQPage olarak işaretlenmesi; iptal, ek paket ve paket bitiminde kullanımın durması sorularının bu blokta cevaplanması, önerilen Turkcell Rahat iptal destek sayfasına iç link verilmesi.</t>
+        </is>
+      </c>
+      <c r="N16" s="14" t="inlineStr">
+        <is>
+          <t>Turkcell Rahat paketi nasıl iptal edilir?
+Rahat paketi bitince ne olur, ek paket nasıl alınır?
+Turkcell Rahat faturalı hat mıdır?
+Rahat'tan faturasız hatta geçilebilir mi?</t>
+        </is>
+      </c>
+      <c r="O16" s="14" t="inlineStr">
+        <is>
+          <t>Search Console 12 ay · Marka geri bildirimi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Faz 2</t>
+        </is>
+      </c>
+      <c r="C17" s="14" t="inlineStr">
+        <is>
           <t>https://www.turkcell.com.tr/destek/dijitalde-turkcellli-olmak/tik-diye-turkcellli-olmak/yeni-hat-talebiniz-ile-ilgili-merak-ettikleriniz</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>Yeni numara talebiniz ile ilgili merak ettikleriniz</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>• SSS bloklarının ayrı ara başlıklara bölünmesi
 • SSS'in FAQPage olarak işaretlenmesi
@@ -8935,71 +9120,71 @@
 • Yeni 'SIM kart ne zaman teslim edilir?' sayfasına iç link verilmesi</t>
         </is>
       </c>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="F17" s="11" t="inlineStr">
         <is>
           <t>İçerik + Teknik</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="19" t="n">
+      <c r="G17" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="19" t="n">
         <v>1619850</v>
       </c>
-      <c r="I16" s="19" t="n">
+      <c r="I17" s="19" t="n">
         <v>48264</v>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J17" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="K16" s="14" t="inlineStr">
+      <c r="K17" s="14" t="inlineStr">
         <is>
           <t>turkcell numara taşıma · turkcell yeni hat · turkcell hat taşıma</t>
         </is>
       </c>
-      <c r="L16" s="14" t="inlineStr">
+      <c r="L17" s="14" t="inlineStr">
         <is>
           <t>1.402 kelimelik SSS sayfası destek dizininin en yüksek görünürlüklü sayfalarından; soru-cevap blokları tek sayfada akıyor ve numara seçimi, SIM teslimi gibi sorular ayrı cevap olarak öne çıkmıyor.</t>
         </is>
       </c>
-      <c r="M16" s="14" t="inlineStr">
+      <c r="M17" s="14" t="inlineStr">
         <is>
           <t>SSS bloklarının ayrı ara başlıklara bölünmesi ve FAQPage olarak işaretlenmesi, yeni 'Yeni hat alırken numara nasıl seçilir?' ve 'SIM kart ne zaman teslim edilir?' sayfalarına iç link verilmesi önerilir.</t>
         </is>
       </c>
-      <c r="N16" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O16" s="14" t="inlineStr">
+      <c r="N17" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O17" s="14" t="inlineStr">
         <is>
           <t>Search Console 3 ay konum analizi</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/ev-interneti/superbox-basvuru-ve-altyapi-sorgulama</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Turkcell Superbox Başvuru ve Altyapı Sorgulama</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>• Superbox uygunluk sorgusunun ne gösterdiğini anlatan kısa açıklama metninin sayfaya eklenmesi
 • Sabit internet altyapısının Superonline sorgu aracından kontrol edildiğinin belirtilmesi
@@ -9007,359 +9192,431 @@
 • Sayfaya H1 başlığının eklenmesi</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F18" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="19" t="n">
+      <c r="G18" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="19" t="n">
         <v>1134995</v>
       </c>
-      <c r="I17" s="19" t="n">
+      <c r="I18" s="19" t="n">
         <v>44936</v>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="J18" s="11" t="n">
         <v>4.9</v>
       </c>
-      <c r="K17" s="14" t="inlineStr">
+      <c r="K18" s="14" t="inlineStr">
         <is>
           <t>altyapı sorgulama · superonline altyapı sorgulama · turkcell altyapı sorgulama</t>
         </is>
       </c>
-      <c r="L17" s="14" t="inlineStr">
+      <c r="L18" s="14" t="inlineStr">
         <is>
           <t>Superbox için adres bazlı uygunluk aracı; metin katmanı sınırlı ve H1 taşımıyor. 'turkcell altyapı sorgulama' araç niyetli sorgusunda sayfa ilk 3'te. Sabit (fiber, VDSL, ADSL) altyapı sorgusu ayrı alan adındaki Superonline aracında yapılıyor.</t>
         </is>
       </c>
-      <c r="M17" s="14" t="inlineStr">
+      <c r="M18" s="14" t="inlineStr">
         <is>
           <t>Araç niyetli sorgu için yeni destek sayfası yerine araç sayfasına kısa bir açıklama katmanı eklenebilir: Superbox uygunluk sorgusunun ne gösterdiği, sabit internet altyapısının Superonline sorgusundan kontrol edildiği ve sonuç ekranının nasıl okunacağı. Sayfaya H1 eklenmesi önerilir.</t>
         </is>
       </c>
-      <c r="N17" s="14" t="inlineStr">
+      <c r="N18" s="14" t="inlineStr">
         <is>
           <t>Altyapı sorgulama ne işe yarar?
 Superbox uygunluk sorgusu ile sabit internet altyapı sorgusu arasındaki fark nedir?</t>
         </is>
       </c>
-      <c r="O17" s="14" t="inlineStr">
+      <c r="O18" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Paket / Tarife değişikliğini nasıl yapabilirim?</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>• 'Turkcell Rahat tarifesinden çıkış ve geçiş' ara başlığının eklenmesi
+• Rahat'ın taahhütsüz olduğu ve çıkış için hat iptaline gerek olmadığı bilgisinin eklenmesi
+• Önerilen Turkcell Rahat iptal sayfasına ve Rahat'tan Faturalıya Geçiş sayfasına iç link verilmesi</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr">
+        <is>
+          <t>İçerik</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="19" t="n">
+        <v>1111403</v>
+      </c>
+      <c r="I19" s="19" t="n">
+        <v>17547</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" s="14" t="inlineStr">
+        <is>
+          <t>turkcell faturalı tarifeler · turkcell tarifeler · turkcell geçiş tarifeleri</t>
+        </is>
+      </c>
+      <c r="L19" s="14" t="inlineStr">
+        <is>
+          <t>Sayfa faturalı ve faturasız hat için tarife değişikliği adımlarını vermekte, Turkcell Rahat modelini ayrı bir başlık olarak ele almamaktadır. 'Turkcell rahat paket iptali' ailesindeki sorgular bu sayfaya düşmekte ancak sayfada Rahat geçmemektedir.</t>
+        </is>
+      </c>
+      <c r="M19" s="14" t="inlineStr">
+        <is>
+          <t>Sayfaya 'Turkcell Rahat tarifesinden çıkış ve geçiş' ara başlığının eklenmesi, Rahat'ın taahhütsüz olduğu ve çıkış için hat iptaline gerek olmadığı bilgisinin verilmesi, önerilen Turkcell Rahat iptal sayfasına ve Rahat'tan Faturalıya Geçiş sayfasına iç link verilmesi.</t>
+        </is>
+      </c>
+      <c r="N19" s="14" t="inlineStr">
+        <is>
+          <t>Turkcell Rahat tarifesinden faturalı tarifeye nasıl geçilir?
+Turkcell Rahat paketi iptal edilince hat kapanır mı?</t>
+        </is>
+      </c>
+      <c r="O19" s="14" t="inlineStr">
+        <is>
+          <t>Search Console 12 ay · Marka geri bildirimi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Faz 2</t>
+        </is>
+      </c>
+      <c r="C20" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/kendi-numarami-nasil-gizleyebilirim</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D20" s="14" t="inlineStr">
         <is>
           <t>Kendi numaramı nasıl gizleyebilirim?</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>• Başlığa 'gizli numaradan arama' ifadesinin eklenmesi: 'Gizli numaradan nasıl aranır, numara nasıl gizlenir?'
 • #31# kodu için ayrı ara başlık açılması
 • CLIR sayfalarının bu sayfaya bağlanması</t>
         </is>
       </c>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="F20" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="19" t="n">
+      <c r="G20" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" s="19" t="n">
         <v>752402</v>
       </c>
-      <c r="I18" s="19" t="n">
+      <c r="I20" s="19" t="n">
         <v>10359</v>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="J20" s="11" t="n">
         <v>4.2</v>
       </c>
-      <c r="K18" s="14" t="inlineStr">
+      <c r="K20" s="14" t="inlineStr">
         <is>
           <t>numara gizleme · gizli numara nasıl yapılır · gizli numara arama</t>
         </is>
       </c>
-      <c r="L18" s="14" t="inlineStr">
+      <c r="L20" s="14" t="inlineStr">
         <is>
           <t>#31# ile tek seferlik gizli arama ve İşlem Merkezi adımı var (95 kelime); konum 2,7-7 bandında. Tıklamanın önemli kısmı Pasaj Blog 'Gizli Arama Nasıl Yapılır?' yazısına gidiyor; aynı konu CLIR sayfalarında da işleniyor.</t>
         </is>
       </c>
-      <c r="M18" s="14" t="inlineStr">
+      <c r="M20" s="14" t="inlineStr">
         <is>
           <t>Başlığa 'gizli numaradan arama' ifadesinin eklenmesi ('Gizli numaradan nasıl aranır, numara nasıl gizlenir?') ve #31# için ayrı ara başlık açılması önerilir; CLIR sayfaları bu sayfaya bağlanabilir.</t>
         </is>
       </c>
-      <c r="N18" s="14" t="inlineStr">
+      <c r="N20" s="14" t="inlineStr">
         <is>
           <t>Gizli numaradan nasıl aranır?
 #31# kodu ne işe yarar?</t>
         </is>
       </c>
-      <c r="O18" s="14" t="inlineStr">
+      <c r="O20" s="14" t="inlineStr">
         <is>
           <t>Search Console 12 ay</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/servisler/bilgi/turkcell-mobil-imza</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D21" s="14" t="inlineStr">
         <is>
           <t>Mobil İmza</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>• Sayfanın başına 'Mobil İmza nasıl alınır?' özet bloğunun eklenmesi
 • SSS'in FAQPage olarak işaretlenmesi
 • Kurumsal destek sayfalarından bireysel kullanıcılar için bu sayfaya bağlantı verilmesi</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F21" s="11" t="inlineStr">
         <is>
           <t>İçerik + Teknik</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="19" t="n">
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" s="19" t="n">
         <v>450007</v>
       </c>
-      <c r="I19" s="19" t="n">
+      <c r="I21" s="19" t="n">
         <v>55374</v>
       </c>
-      <c r="J19" s="11" t="n">
+      <c r="J21" s="11" t="n">
         <v>4.5</v>
       </c>
-      <c r="K19" s="14" t="inlineStr">
+      <c r="K21" s="14" t="inlineStr">
         <is>
           <t>mobil imza nasıl alınır · turkcell mobil imza · mobil imza nedir</t>
         </is>
       </c>
-      <c r="L19" s="14" t="inlineStr">
+      <c r="L21" s="14" t="inlineStr">
         <is>
           <t>Kapsamlı Mobil İmza ürün sayfası başvuru kanallarını, koşulları ve ücretleri cevaplıyor ve 'mobil imza nasıl alınır' sorgusunda 3-4 bandında. Bireysel destekte Mobil İmza sayfası yok; kurumsal destekte 5 sayfa var.</t>
         </is>
       </c>
-      <c r="M19" s="14" t="inlineStr">
+      <c r="M21" s="14" t="inlineStr">
         <is>
           <t>Ürün sayfası soruyu birebir cevapladığı için Ayrı bir destek sayfası açmak yerine sayfanın başına kısa bir 'Mobil İmza nasıl alınır?' özet bloğu eklenmesi, SSS'in FAQPage olarak işaretlenmesi ve kurumsal destek sayfalarından bireysel kullanıcılar için bu sayfaya bağlantı verilmesi önerilir.</t>
         </is>
       </c>
-      <c r="N19" s="14" t="inlineStr">
+      <c r="N21" s="14" t="inlineStr">
         <is>
           <t>Mobil İmza nasıl alınır?
 Mobil İmza ücreti ne kadar?</t>
         </is>
       </c>
-      <c r="O19" s="14" t="inlineStr">
+      <c r="O21" s="14" t="inlineStr">
         <is>
           <t>Search Console 3 ay konum analizi · Search Console 12 ay</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/numarami-nasil-degistirebilirim</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D22" s="14" t="inlineStr">
         <is>
           <t>Numaramı nasıl değiştirebilirim?</t>
         </is>
       </c>
-      <c r="E20" s="14" t="inlineStr">
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>• Son hane seçimi bilgisinin ara başlıkla eklenmesi
 • Numara değişikliğinin online yapılabilirliğinin belirtilmesi
 • Yeni 'Yeni hat alırken numara nasıl seçilir?' sayfasına iç link verilmesi</t>
         </is>
       </c>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="F22" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="19" t="n">
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" s="19" t="n">
         <v>250689</v>
       </c>
-      <c r="I20" s="19" t="n">
+      <c r="I22" s="19" t="n">
         <v>45001</v>
       </c>
-      <c r="J20" s="11" t="n">
+      <c r="J22" s="11" t="n">
         <v>2.2</v>
       </c>
-      <c r="K20" s="14" t="inlineStr">
+      <c r="K22" s="14" t="inlineStr">
         <is>
           <t>turkcell numara değiştirme · numara değiştirme · telefon numarası değiştirme</t>
         </is>
       </c>
-      <c r="L20" s="14" t="inlineStr">
+      <c r="L22" s="14" t="inlineStr">
         <is>
           <t>69 kelime; mağaza ve 532 kanalı, 208,51 TL ücret, 60 günde bir ve yılda 3 sınırı var. Son hane ve online kanal bilgisi yok; ücret sorgusunda kurumsal kopya sıralanıyor.</t>
         </is>
       </c>
-      <c r="M20" s="14" t="inlineStr">
+      <c r="M22" s="14" t="inlineStr">
         <is>
           <t>Son hane seçimi ve online işlem için ara başlık eklenmesi (marka doğrulamasıyla) ve yeni 'Yeni hat alırken numara nasıl seçilir?' sayfasına iç link verilmesi önerilir.</t>
         </is>
       </c>
-      <c r="N20" s="14" t="inlineStr">
+      <c r="N22" s="14" t="inlineStr">
         <is>
           <t>Numaranın son haneleri değiştirilebilir mi?
 Numara değişikliği online yapılabilir mi?</t>
         </is>
       </c>
-      <c r="O20" s="14" t="inlineStr">
+      <c r="O22" s="14" t="inlineStr">
         <is>
           <t>Search Console 12 ay</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/islem-merkezi/ayarlarim/pin-puk-kodu-nedir-bunlari-bloke-edersem-ne-yapmaliyim</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D23" s="14" t="inlineStr">
         <is>
           <t>PIN kodum bloke oldu, ne yapabilirim?</t>
         </is>
       </c>
-      <c r="E21" s="14" t="inlineStr">
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>• Üç kopyanın tek yayın adresinde toplanması
 • PIN kaldırma sorusu için yeni 'SIM kart PIN kodu nasıl değiştirilir veya kaldırılır?' sayfasına iç link verilmesi</t>
         </is>
       </c>
-      <c r="F21" s="11" t="inlineStr">
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>İçerik + Teknik</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/sikca-sorulan-sorular/pin-puk-kodu-nedir-bunlari-bloke-edersem-ne-yapmaliyim
 https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcellli-olmak/pin-puk-kodu-nedir-bunlari-bloke-edersem-ne-yapmaliyim</t>
         </is>
       </c>
-      <c r="H21" s="19" t="n">
+      <c r="H23" s="19" t="n">
         <v>210761</v>
       </c>
-      <c r="I21" s="19" t="n">
+      <c r="I23" s="19" t="n">
         <v>11495</v>
       </c>
-      <c r="J21" s="11" t="n">
+      <c r="J23" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="K21" s="14" t="inlineStr">
+      <c r="K23" s="14" t="inlineStr">
         <is>
           <t>pin kodu kaldırma · pin kodu öğrenme · turkcell pin kodu kaldırma</t>
         </is>
       </c>
-      <c r="L21" s="14" t="inlineStr">
+      <c r="L23" s="14" t="inlineStr">
         <is>
           <t>'PIN kodum bloke oldu' sayfası 'pin kodu kaldırma' sorgusunu da alıyor; aynı başlık üç bireysel adreste yayınlanıyor.</t>
         </is>
       </c>
-      <c r="M21" s="14" t="inlineStr">
+      <c r="M23" s="14" t="inlineStr">
         <is>
           <t>Üç kopyanın tek yayın adresinde toplanması ve PIN kaldırma sorusu için yeni 'SIM kart PIN kodu nasıl değiştirilir veya kaldırılır?' sayfasına iç link verilmesi önerilir.</t>
         </is>
       </c>
-      <c r="N21" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O21" s="14" t="inlineStr">
+      <c r="N23" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O23" s="14" t="inlineStr">
         <is>
           <t>Search Console 3 ay konum analizi</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/hattimi-nasil-iptal-ettirebilirim</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr">
         <is>
           <t>Hattımı nasıl iptal ettirebilirim?</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>• Cayma bedeli bilgisinin ara başlıkla eklenmesi
 • İptal sonrası son fatura ödeme sürecinin eklenmesi
@@ -9367,192 +9624,50 @@
 • 'İptal ettirdiğim hattımı nasıl geri alabilirim?' sayfasına iç link verilmesi</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F24" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="19" t="n">
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" s="19" t="n">
         <v>203370</v>
       </c>
-      <c r="I22" s="19" t="n">
+      <c r="I24" s="19" t="n">
         <v>30521</v>
       </c>
-      <c r="J22" s="11" t="n">
+      <c r="J24" s="11" t="n">
         <v>2.4</v>
       </c>
-      <c r="K22" s="14" t="inlineStr">
+      <c r="K24" s="14" t="inlineStr">
         <is>
           <t>turkcell hat kapatma · hat kapatma · hat nasıl kapatılır</t>
         </is>
       </c>
-      <c r="L22" s="14" t="inlineStr">
+      <c r="L24" s="14" t="inlineStr">
         <is>
           <t>67 kelime; iptal kanallarını (mağaza, 532, faks, uygulama, e-posta, e-Devlet) veriyor ve sorgu ailesinin tıklama baskın sayfası. İptal ücreti, cayma bedeli ve iptal sonrası süreç bilgisi yok.</t>
         </is>
       </c>
-      <c r="M22" s="14" t="inlineStr">
+      <c r="M24" s="14" t="inlineStr">
         <is>
           <t>Ücret, cayma bedeli ve iptal sonrası süreç için kısa ara başlıklar eklenmesi, yeni 'Cayma bedeli nedir?' sayfasına ve 'İptal ettirdiğim hattımı nasıl geri alabilirim?' sayfasına iç link verilmesi önerilir (ücret değerleri marka doğrulamasıyla).</t>
         </is>
       </c>
-      <c r="N22" s="14" t="inlineStr">
+      <c r="N24" s="14" t="inlineStr">
         <is>
           <t>Hat iptal ettirmek ücretli mi, cayma bedeli yansır mı?
 Hat iptalinden sonra son fatura nasıl ödenir?
 İptal edilen hat geri alınabilir mi?</t>
         </is>
       </c>
-      <c r="O22" s="14" t="inlineStr">
+      <c r="O24" s="14" t="inlineStr">
         <is>
           <t>Search Console 12 ay · Rakip destek karşılaştırması</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>Faz 2</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/devir-icin-hangi-vergiler-ve-ucretler-odenir</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>Devir için hangi vergi ve ücretler ödenir?</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="inlineStr">
-        <is>
-          <t>• Vergi kalemlerinin yıllık tutarlarının tablo olarak eklenmesi
-• Devirde kampanya erken iptal ücretinin hangi tarafa yansıdığı bilgisinin Taahhütlü Abonelik koşullarıyla tutarlı hale getirilmesi</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr">
-        <is>
-          <t>İçerik</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="19" t="n">
-        <v>175199</v>
-      </c>
-      <c r="I23" s="19" t="n">
-        <v>34957</v>
-      </c>
-      <c r="J23" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="K23" s="14" t="inlineStr">
-        <is>
-          <t>hat devir ücreti · turkcell hat devir ücreti · hat sahibi değiştirme ücreti</t>
-        </is>
-      </c>
-      <c r="L23" s="14" t="inlineStr">
-        <is>
-          <t>173 kelime; devralanın ödediği kalemleri sayıyor ancak TL tutarı yok. Sorgular yıl ve 'ne kadar' ile tutar arıyor; tıklama oranı yüksek.</t>
-        </is>
-      </c>
-      <c r="M23" s="14" t="inlineStr">
-        <is>
-          <t>Kalemlerin yıl tutarlarının tabloyla eklenmesi önerilir; devir ücreti tutarı için marka doğrulaması gerekir. Devirde kampanya erken iptal ücretinin hangi tarafa yansıdığı ifadesi Taahhütlü Abonelik koşullarıyla tek doğruya çekilmelidir (çelişki listesinde).</t>
-        </is>
-      </c>
-      <c r="N23" s="14" t="inlineStr">
-        <is>
-          <t>Hat devir ücreti ne kadar?
-Hattı kendi üzerine almak ne kadar tutar?</t>
-        </is>
-      </c>
-      <c r="O23" s="14" t="inlineStr">
-        <is>
-          <t>Search Console 12 ay</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>Faz 2</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/servisler/arama-fatura-tl/turkcellmobilodeme</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>Faturana Yansıt</t>
-        </is>
-      </c>
-      <c r="E24" s="14" t="inlineStr">
-        <is>
-          <t>• Servis sayfasının 'Telefon faturası üzerinden alışveriş nasıl yapılır, mobil ödeme nasıl açılır?' sorularıyla açılması
-• Bireysel destek adresinin bu sayfaya kalıcı (301) yönlendirilmesi</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>İçerik + Teknik</t>
-        </is>
-      </c>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="19" t="n">
-        <v>166966</v>
-      </c>
-      <c r="I24" s="19" t="n">
-        <v>27303</v>
-      </c>
-      <c r="J24" s="11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="K24" s="14" t="inlineStr">
-        <is>
-          <t>faturana yansıt üyelik nedir · turkcell mobil ödeme kapatma · faturana yansıt nedir</t>
-        </is>
-      </c>
-      <c r="L24" s="14" t="inlineStr">
-        <is>
-          <t>Faturana Yansıt servis sayfası fatura üzerinden alışveriş kapsamını, onay yöntemlerini ve hattın ödemeye açılmasını SSS'te birebir cevaplıyor. Bireysel destek adresi /destek/servisler-ve-internet/servisler/telefonumu-mobil-odeme-kullanimina-nasil-acabilirim başka bir sayfanın içeriğini gösteriyor; mobil ödeme açma kodu bireysel ve kurumsal sayfalarda farklı yazılı.</t>
-        </is>
-      </c>
-      <c r="M24" s="14" t="inlineStr">
-        <is>
-          <t>Servis sayfasının 'Telefon faturası üzerinden alışveriş nasıl yapılır, mobil ödeme nasıl açılır?' sorularıyla açılması ve bireysel destek adresinin bu sayfaya kalıcı yönlendirilmesi önerilir (teknik madde). Açma kodu marka tarafından tek doğruya çekilmelidir.</t>
-        </is>
-      </c>
-      <c r="N24" s="14" t="inlineStr">
-        <is>
-          <t>Telefon faturası üzerinden alışveriş yapılabilir mi?
-Hat mobil ödemeye nasıl açılır?</t>
-        </is>
-      </c>
-      <c r="O24" s="14" t="inlineStr">
-        <is>
-          <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
     </row>
@@ -9567,86 +9682,228 @@
       </c>
       <c r="C25" s="14" t="inlineStr">
         <is>
+          <t>https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/devir-icin-hangi-vergiler-ve-ucretler-odenir</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>Devir için hangi vergi ve ücretler ödenir?</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>• Vergi kalemlerinin yıllık tutarlarının tablo olarak eklenmesi
+• Devirde kampanya erken iptal ücretinin hangi tarafa yansıdığı bilgisinin Taahhütlü Abonelik koşullarıyla tutarlı hale getirilmesi</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>İçerik</t>
+        </is>
+      </c>
+      <c r="G25" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" s="19" t="n">
+        <v>175199</v>
+      </c>
+      <c r="I25" s="19" t="n">
+        <v>34957</v>
+      </c>
+      <c r="J25" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K25" s="14" t="inlineStr">
+        <is>
+          <t>hat devir ücreti · turkcell hat devir ücreti · hat sahibi değiştirme ücreti</t>
+        </is>
+      </c>
+      <c r="L25" s="14" t="inlineStr">
+        <is>
+          <t>173 kelime; devralanın ödediği kalemleri sayıyor ancak TL tutarı yok. Sorgular yıl ve 'ne kadar' ile tutar arıyor; tıklama oranı yüksek.</t>
+        </is>
+      </c>
+      <c r="M25" s="14" t="inlineStr">
+        <is>
+          <t>Kalemlerin yıl tutarlarının tabloyla eklenmesi önerilir; devir ücreti tutarı için marka doğrulaması gerekir. Devirde kampanya erken iptal ücretinin hangi tarafa yansıdığı ifadesi Taahhütlü Abonelik koşullarıyla tek doğruya çekilmelidir (çelişki listesinde).</t>
+        </is>
+      </c>
+      <c r="N25" s="14" t="inlineStr">
+        <is>
+          <t>Hat devir ücreti ne kadar?
+Hattı kendi üzerine almak ne kadar tutar?</t>
+        </is>
+      </c>
+      <c r="O25" s="14" t="inlineStr">
+        <is>
+          <t>Search Console 12 ay</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>Faz 2</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/servisler/arama-fatura-tl/turkcellmobilodeme</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>Faturana Yansıt</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>• Servis sayfasının 'Telefon faturası üzerinden alışveriş nasıl yapılır, mobil ödeme nasıl açılır?' sorularıyla açılması
+• Bireysel destek adresinin bu sayfaya kalıcı (301) yönlendirilmesi</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>İçerik + Teknik</t>
+        </is>
+      </c>
+      <c r="G26" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" s="19" t="n">
+        <v>166966</v>
+      </c>
+      <c r="I26" s="19" t="n">
+        <v>27303</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>faturana yansıt üyelik nedir · turkcell mobil ödeme kapatma · faturana yansıt nedir</t>
+        </is>
+      </c>
+      <c r="L26" s="14" t="inlineStr">
+        <is>
+          <t>Faturana Yansıt servis sayfası fatura üzerinden alışveriş kapsamını, onay yöntemlerini ve hattın ödemeye açılmasını SSS'te birebir cevaplıyor. Bireysel destek adresi /destek/servisler-ve-internet/servisler/telefonumu-mobil-odeme-kullanimina-nasil-acabilirim başka bir sayfanın içeriğini gösteriyor; mobil ödeme açma kodu bireysel ve kurumsal sayfalarda farklı yazılı.</t>
+        </is>
+      </c>
+      <c r="M26" s="14" t="inlineStr">
+        <is>
+          <t>Servis sayfasının 'Telefon faturası üzerinden alışveriş nasıl yapılır, mobil ödeme nasıl açılır?' sorularıyla açılması ve bireysel destek adresinin bu sayfaya kalıcı yönlendirilmesi önerilir (teknik madde). Açma kodu marka tarafından tek doğruya çekilmelidir.</t>
+        </is>
+      </c>
+      <c r="N26" s="14" t="inlineStr">
+        <is>
+          <t>Telefon faturası üzerinden alışveriş yapılabilir mi?
+Hat mobil ödemeye nasıl açılır?</t>
+        </is>
+      </c>
+      <c r="O26" s="14" t="inlineStr">
+        <is>
+          <t>Arama talebi ve SERP analizi</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Faz 2</t>
+        </is>
+      </c>
+      <c r="C27" s="14" t="inlineStr">
+        <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/hazirkart/telsiz-kullanim-ucreti</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D27" s="14" t="inlineStr">
         <is>
           <t>Telsiz Kullanım Ücreti</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>• Başlığın 'Telsiz kullanım ücreti nedir, ne kadar?' olarak güncellenmesi
 • Aylık taksit bilgisinin eklenmesi
 • Vergi sayfalarından bu sayfaya iç link verilmesi</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="19" t="n">
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" s="19" t="n">
         <v>152771</v>
       </c>
-      <c r="I25" s="19" t="n">
+      <c r="I27" s="19" t="n">
         <v>5459</v>
       </c>
-      <c r="J25" s="11" t="n">
+      <c r="J27" s="11" t="n">
         <v>2.8</v>
       </c>
-      <c r="K25" s="14" t="inlineStr">
+      <c r="K27" s="14" t="inlineStr">
         <is>
           <t>telsiz kullanım ücreti · tkü borcu nedir · telsiz kullanım ücreti nedir</t>
         </is>
       </c>
-      <c r="L25" s="14" t="inlineStr">
+      <c r="L27" s="14" t="inlineStr">
         <is>
           <t>Bireysel sayfa kapsamlı, ancak 'telsiz kullanım ücreti nedir' sorgusunda kurumsal kopya öne geçiyor. Aylık taksit bilgisi yalnızca kurumsal sayfada.</t>
         </is>
       </c>
-      <c r="M25" s="14" t="inlineStr">
+      <c r="M27" s="14" t="inlineStr">
         <is>
           <t>Başlığın 'Telsiz kullanım ücreti nedir, ne kadar?' olarak güncellenmesi, aylık taksit bilgisinin eklenmesi ve vergi sayfalarından bu sayfaya iç link verilmesi önerilir. Kurumsal kopya ile ilişki teknik maddede ele alınır.</t>
         </is>
       </c>
-      <c r="N25" s="14" t="inlineStr">
+      <c r="N27" s="14" t="inlineStr">
         <is>
           <t>Telsiz kullanım ücreti aylık nasıl yansır?</t>
         </is>
       </c>
-      <c r="O25" s="14" t="inlineStr">
+      <c r="O27" s="14" t="inlineStr">
         <is>
           <t>Search Console 12 ay</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/turkcellliye-her-yer-wi-fi/android-cihazlarda-internetimi-nasil-paylasabilirim</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D28" s="14" t="inlineStr">
         <is>
           <t>Android cihazlarda internetimi nasıl paylaşabilirim?</t>
         </is>
       </c>
-      <c r="E26" s="14" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>• Android ve iOS sayfalarının güncel menü yollarıyla yeniden yazılması
 • Başlık ve title'a 'hotspot' ve 'kişisel erişim noktası' ifadelerinin eklenmesi
@@ -9655,190 +9912,49 @@
 • Yalnızca paylaşımda geçerli Hotspot ek paketlerinin kısa bir bölümle anlatılması</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F28" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="19" t="n">
+      <c r="G28" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" s="19" t="n">
         <v>120964</v>
       </c>
-      <c r="I26" s="19" t="n">
+      <c r="I28" s="19" t="n">
         <v>1811</v>
       </c>
-      <c r="J26" s="11" t="n">
+      <c r="J28" s="11" t="n">
         <v>5.6</v>
       </c>
-      <c r="K26" s="14" t="inlineStr">
+      <c r="K28" s="14" t="inlineStr">
         <is>
           <t>internet paylaşımı nasıl yapılır · internet nasıl paylaşılır · telefondan telefona internet nasıl bağlanır</t>
         </is>
       </c>
-      <c r="L26" s="14" t="inlineStr">
+      <c r="L28" s="14" t="inlineStr">
         <is>
           <t>Android internet paylaşımı sayfası 10.499 kelime ve eski cihaz modeli listesiyle tek blok halinde akıyor; 'internet paylaşımı nasıl yapılır' sorgusunda konum 6 civarında. iOS karşılığı ayrı adreste, hub sayfada güncelliğini yitirmiş ifadeler bulunuyor.</t>
         </is>
       </c>
-      <c r="M26" s="14" t="inlineStr">
+      <c r="M28" s="14" t="inlineStr">
         <is>
           <t>Yeni 'hotspot' sayfası açılmaması, Android ve iOS sayfalarının güncel menü yollarıyla yeniden yazılması önerilir. Başlık ve title'a 'hotspot' ve 'kişisel erişim noktası' ifadeleri eklenebilir; uzun model listesi marka bazlı ara başlıklara bölünebilir. Paylaşımın hangi paket haklarından düştüğü ve yalnızca paylaşımda geçerli Hotspot ek paketleri kısa bir bölümle anlatılabilir.</t>
         </is>
       </c>
-      <c r="N26" s="14" t="inlineStr">
+      <c r="N28" s="14" t="inlineStr">
         <is>
           <t>Hotspot (kişisel erişim noktası) nasıl açılır?
 İnternet paylaşımında kullanılan internet hangi paketten düşer?</t>
         </is>
       </c>
-      <c r="O26" s="14" t="inlineStr">
+      <c r="O28" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi · Search Console 3 ay konum analizi</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>Faz 2</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/destek/5g/genel/5gyi-nasil-iptal-ederim</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>5G’yi nasıl iptal ederim?</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>• Başlığın 'Turkcell 5G nasıl kapatılır veya iptal edilir?' olarak genişletilmesi
-• 4.5G şebeke seçimi için Android/iOS sayfalarına bağlantı ve kısa özet eklenmesi</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>İçerik</t>
-        </is>
-      </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="19" t="n">
-        <v>118484</v>
-      </c>
-      <c r="I27" s="19" t="n">
-        <v>1579</v>
-      </c>
-      <c r="J27" s="11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K27" s="14" t="inlineStr">
-        <is>
-          <t>5g nasıl kapatılır · 5g kapatma · 5 g nasıl kapatılır</t>
-        </is>
-      </c>
-      <c r="L27" s="14" t="inlineStr">
-        <is>
-          <t>Sayfa 18 kelime: Turkcell Uygulaması ya da 4.5G yazıp 2200. Kullanıcı 'kapatma' fiiliyle arıyor; telefonda şebeke modunu 4.5G'ye alma adımı yok, ayrı 4.5G şebeke seçimi sayfaları bağlantılı değil.</t>
-        </is>
-      </c>
-      <c r="M27" s="14" t="inlineStr">
-        <is>
-          <t>Başlığın 'Turkcell 5G nasıl kapatılır veya iptal edilir?' olarak genişletilmesi, cihaz ayarı adımları için 4.5G şebeke seçimi Android/iOS sayfalarına bağlantı ve kısa özet eklenmesi önerilir.</t>
-        </is>
-      </c>
-      <c r="N27" s="14" t="inlineStr">
-        <is>
-          <t>Telefonda 5G nasıl kapatılır?
-5G servisinin iptali ile şebeke modunun değiştirilmesi arasındaki fark nedir?</t>
-        </is>
-      </c>
-      <c r="O27" s="14" t="inlineStr">
-        <is>
-          <t>Search Console 3 ay konum analizi · Search Console 12 ay</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>Faz 2</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/servisler/arama-fatura-tl/turkcell-odemeliara</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Turkcell Ödemeli Ara</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>• Sayfa başlığı ve ilk bölümünün 'Ödemeli arama nasıl yapılır?' sorusuna göre düzenlenmesi
-• *135*numara# adımının ilk paragrafta verilmesi</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>İçerik</t>
-        </is>
-      </c>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="19" t="n">
-        <v>106886</v>
-      </c>
-      <c r="I28" s="19" t="n">
-        <v>1513</v>
-      </c>
-      <c r="J28" s="11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K28" s="14" t="inlineStr">
-        <is>
-          <t>ödemeli nasıl atılır · ödemeli arama nasıl yapılır · turkcell ödemeli arama</t>
-        </is>
-      </c>
-      <c r="L28" s="14" t="inlineStr">
-        <is>
-          <t>Servis sayfası ödemeli aramanın nasıl yapıldığını, ücretini ve süre sınırını SSS ile birebir veriyor; markasız 'ödemeli nasıl atılır' sorgusunda konum 6 civarında.</t>
-        </is>
-      </c>
-      <c r="M28" s="14" t="inlineStr">
-        <is>
-          <t>Sayfa başlığı ve ilk bölümünün 'Ödemeli arama nasıl yapılır?' sorusuna göre düzenlenmesi ve *135*numara# adımının ilk paragrafta verilmesi önerilir.</t>
-        </is>
-      </c>
-      <c r="N28" s="14" t="inlineStr">
-        <is>
-          <t>Ödemeli arama nasıl yapılır?</t>
-        </is>
-      </c>
-      <c r="O28" s="14" t="inlineStr">
-        <is>
-          <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
     </row>
@@ -9853,18 +9969,18 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/yurtdisi/yurtdisinda-kullanim/yurtdisina-cikmadan-telefonumu-kullanmak-icin-neler-yapmaliyim</t>
+          <t>https://www.turkcell.com.tr/destek/5g/genel/5gyi-nasil-iptal-ederim</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
         <is>
-          <t>Yurt dışına çıkmadan telefonumu kullanmak için neler yapmalıyım?</t>
+          <t>5G’yi nasıl iptal ederim?</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
         <is>
-          <t>• Başlık ve title'ın 'Yurt dışı kullanımı nasıl açılır ve kapatılır?' olarak güncellenmesi
-• Kıbrıs sayfasındaki tekrar eden içeriğin bu sayfaya bağlanması</t>
+          <t>• Başlığın 'Turkcell 5G nasıl kapatılır veya iptal edilir?' olarak genişletilmesi
+• 4.5G şebeke seçimi için Android/iOS sayfalarına bağlantı ve kısa özet eklenmesi</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -9878,38 +9994,38 @@
         </is>
       </c>
       <c r="H29" s="19" t="n">
-        <v>90072</v>
+        <v>118484</v>
       </c>
       <c r="I29" s="19" t="n">
-        <v>14242</v>
+        <v>1579</v>
       </c>
       <c r="J29" s="11" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>2200 nerenin numarası · telefonu yurt dışına açma · turkcell yurtdışı açma</t>
+          <t>5g nasıl kapatılır · 5g kapatma · 5 g nasıl kapatılır</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>Sayfa yurt dışı kullanımını açma (ROAM 2200, *111#, İşlem Merkezi) ve yurt dışında interneti kapatma/açma adımlarını veriyor; 'turkcell yurtdışı açma' sorgusunda 1,4 konumda. Başlık açma-kapama sorusunu yansıtmıyor, aynı içerik Kıbrıs sayfasında tekrar ediyor.</t>
+          <t>Sayfa 18 kelime: Turkcell Uygulaması ya da 4.5G yazıp 2200. Kullanıcı 'kapatma' fiiliyle arıyor; telefonda şebeke modunu 4.5G'ye alma adımı yok, ayrı 4.5G şebeke seçimi sayfaları bağlantılı değil.</t>
         </is>
       </c>
       <c r="M29" s="14" t="inlineStr">
         <is>
-          <t>Başlık ve title'ın 'Yurt dışı kullanımı nasıl açılır ve kapatılır?' yönünde güncellenmesi, Kıbrıs sayfasındaki tekrar içeriğin bu sayfaya bağlanması önerilir.</t>
+          <t>Başlığın 'Turkcell 5G nasıl kapatılır veya iptal edilir?' olarak genişletilmesi, cihaz ayarı adımları için 4.5G şebeke seçimi Android/iOS sayfalarına bağlantı ve kısa özet eklenmesi önerilir.</t>
         </is>
       </c>
       <c r="N29" s="14" t="inlineStr">
         <is>
-          <t>Hat yurt dışı kullanıma nasıl açılır?
-Yurt dışında internet nasıl kapatılır?</t>
+          <t>Telefonda 5G nasıl kapatılır?
+5G servisinin iptali ile şebeke modunun değiştirilmesi arasındaki fark nedir?</t>
         </is>
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
-          <t>Arama talebi ve SERP analizi</t>
+          <t>Search Console 3 ay konum analizi · Search Console 12 ay</t>
         </is>
       </c>
     </row>
@@ -9924,15 +10040,156 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
+          <t>https://www.turkcell.com.tr/servisler/arama-fatura-tl/turkcell-odemeliara</t>
+        </is>
+      </c>
+      <c r="D30" s="14" t="inlineStr">
+        <is>
+          <t>Turkcell Ödemeli Ara</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>• Sayfa başlığı ve ilk bölümünün 'Ödemeli arama nasıl yapılır?' sorusuna göre düzenlenmesi
+• *135*numara# adımının ilk paragrafta verilmesi</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>İçerik</t>
+        </is>
+      </c>
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="19" t="n">
+        <v>106886</v>
+      </c>
+      <c r="I30" s="19" t="n">
+        <v>1513</v>
+      </c>
+      <c r="J30" s="11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K30" s="14" t="inlineStr">
+        <is>
+          <t>ödemeli nasıl atılır · ödemeli arama nasıl yapılır · turkcell ödemeli arama</t>
+        </is>
+      </c>
+      <c r="L30" s="14" t="inlineStr">
+        <is>
+          <t>Servis sayfası ödemeli aramanın nasıl yapıldığını, ücretini ve süre sınırını SSS ile birebir veriyor; markasız 'ödemeli nasıl atılır' sorgusunda konum 6 civarında.</t>
+        </is>
+      </c>
+      <c r="M30" s="14" t="inlineStr">
+        <is>
+          <t>Sayfa başlığı ve ilk bölümünün 'Ödemeli arama nasıl yapılır?' sorusuna göre düzenlenmesi ve *135*numara# adımının ilk paragrafta verilmesi önerilir.</t>
+        </is>
+      </c>
+      <c r="N30" s="14" t="inlineStr">
+        <is>
+          <t>Ödemeli arama nasıl yapılır?</t>
+        </is>
+      </c>
+      <c r="O30" s="14" t="inlineStr">
+        <is>
+          <t>Arama talebi ve SERP analizi</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>Faz 2</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/destek/yurtdisi/yurtdisinda-kullanim/yurtdisina-cikmadan-telefonumu-kullanmak-icin-neler-yapmaliyim</t>
+        </is>
+      </c>
+      <c r="D31" s="14" t="inlineStr">
+        <is>
+          <t>Yurt dışına çıkmadan telefonumu kullanmak için neler yapmalıyım?</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>• Başlık ve title'ın 'Yurt dışı kullanımı nasıl açılır ve kapatılır?' olarak güncellenmesi
+• Kıbrıs sayfasındaki tekrar eden içeriğin bu sayfaya bağlanması</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>İçerik</t>
+        </is>
+      </c>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" s="19" t="n">
+        <v>90072</v>
+      </c>
+      <c r="I31" s="19" t="n">
+        <v>14242</v>
+      </c>
+      <c r="J31" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>2200 nerenin numarası · telefonu yurt dışına açma · turkcell yurtdışı açma</t>
+        </is>
+      </c>
+      <c r="L31" s="14" t="inlineStr">
+        <is>
+          <t>Sayfa yurt dışı kullanımını açma (ROAM 2200, *111#, İşlem Merkezi) ve yurt dışında interneti kapatma/açma adımlarını veriyor; 'turkcell yurtdışı açma' sorgusunda 1,4 konumda. Başlık açma-kapama sorusunu yansıtmıyor, aynı içerik Kıbrıs sayfasında tekrar ediyor.</t>
+        </is>
+      </c>
+      <c r="M31" s="14" t="inlineStr">
+        <is>
+          <t>Başlık ve title'ın 'Yurt dışı kullanımı nasıl açılır ve kapatılır?' yönünde güncellenmesi, Kıbrıs sayfasındaki tekrar içeriğin bu sayfaya bağlanması önerilir.</t>
+        </is>
+      </c>
+      <c r="N31" s="14" t="inlineStr">
+        <is>
+          <t>Hat yurt dışı kullanıma nasıl açılır?
+Yurt dışında internet nasıl kapatılır?</t>
+        </is>
+      </c>
+      <c r="O31" s="14" t="inlineStr">
+        <is>
+          <t>Arama talebi ve SERP analizi</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>Faz 2</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/faturali-hattan-hazir-karta-nasil-gecis-yapabilirim</t>
         </is>
       </c>
-      <c r="D30" s="14" t="inlineStr">
+      <c r="D32" s="14" t="inlineStr">
         <is>
           <t>Faturalı hattan Hazır Kart’a nasıl geçiş yapabilirim?</t>
         </is>
       </c>
-      <c r="E30" s="14" t="inlineStr">
+      <c r="E32" s="14" t="inlineStr">
         <is>
           <t>• Başlık ve title'a 'faturasız' ifadesinin eklenmesi: 'Faturalı hattan faturasız hatta (Hazır Kart) nasıl geçilir?'
 • 'Faturalıdan faturasıza geçiş ücretli mi?' sorusunun ara başlık olarak eklenmesi
@@ -9940,361 +10197,361 @@
 • 'Ödeme tipi değişikliği ne sıklıkla yapılabilir?' bilgisinin ara başlık olarak eklenmesi</t>
         </is>
       </c>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="F32" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="19" t="n">
+      <c r="G32" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" s="19" t="n">
         <v>68746</v>
       </c>
-      <c r="I30" s="19" t="n">
+      <c r="I32" s="19" t="n">
         <v>21130</v>
       </c>
-      <c r="J30" s="11" t="n">
+      <c r="J32" s="11" t="n">
         <v>1.5</v>
       </c>
-      <c r="K30" s="14" t="inlineStr">
+      <c r="K32" s="14" t="inlineStr">
         <is>
           <t>turkcell faturalıdan faturasıza geçiş · faturalıdan faturasıza geçiş · faturalı hattan faturasız hatta geçiş</t>
         </is>
       </c>
-      <c r="L30" s="14" t="inlineStr">
+      <c r="L32" s="14" t="inlineStr">
         <is>
           <t>Sayfa faturalıdan Hazır Kart'a geçişi birebir cevaplıyor ve 'faturalıdan faturasıza geçiş' sorgusunda üst sırada. Başlıkta kullanıcının kullandığı 'faturasız' ifadesi yok; ücret, tarife ve 30 gün kuralı üç ayrı kısa sayfaya dağılmış.</t>
         </is>
       </c>
-      <c r="M30" s="14" t="inlineStr">
+      <c r="M32" s="14" t="inlineStr">
         <is>
           <t>Başlık ve title'a 'faturasız' ifadesinin eklenmesi ('Faturalı hattan faturasız hatta (Hazır Kart) nasıl geçilir?') ve ücret, tarife seçimi ve 30 günde bir yapılabilme bilgisinin bu sayfada ara başlıklarla toplanması önerilir.</t>
         </is>
       </c>
-      <c r="N30" s="14" t="inlineStr">
+      <c r="N32" s="14" t="inlineStr">
         <is>
           <t>Faturalıdan faturasıza geçiş ücretli mi?
 Geçişte tarife değişir mi?
 Ödeme tipi değişikliği ne sıklıkla yapılabilir?</t>
         </is>
       </c>
-      <c r="O30" s="14" t="inlineStr">
+      <c r="O32" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="11" t="n">
-        <v>27</v>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C33" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numara-tasima-sorgulamasi-nasil-yapilir</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D33" s="14" t="inlineStr">
         <is>
           <t>Numara taşıma sorgulaması nasıl yapılır?</t>
         </is>
       </c>
-      <c r="E31" s="14" t="inlineStr">
+      <c r="E33" s="14" t="inlineStr">
         <is>
           <t>• e-Devlet sorgu adımlarının eklenmesi
 • Turkcell 'Yeni Hat Başvurusu Sorgulama' formunun ne gösterdiğinin anlatılması</t>
         </is>
       </c>
-      <c r="F31" s="11" t="inlineStr">
+      <c r="F33" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="19" t="n">
+      <c r="G33" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" s="19" t="n">
         <v>63948</v>
       </c>
-      <c r="I31" s="19" t="n">
+      <c r="I33" s="19" t="n">
         <v>2125</v>
       </c>
-      <c r="J31" s="11" t="n">
+      <c r="J33" s="11" t="n">
         <v>5.1</v>
       </c>
-      <c r="K31" s="14" t="inlineStr">
+      <c r="K33" s="14" t="inlineStr">
         <is>
           <t>numara taşıma sorgulama · btk numara sorgulama · operatör sorgulama</t>
         </is>
       </c>
-      <c r="L31" s="14" t="inlineStr">
+      <c r="L33" s="14" t="inlineStr">
         <is>
           <t>Sayfa 11 kelime: yalnızca e-Devlet BTK numara taşıma bağlantısı.</t>
         </is>
       </c>
-      <c r="M31" s="14" t="inlineStr">
+      <c r="M33" s="14" t="inlineStr">
         <is>
           <t>e-Devlet sorgu adımlarının ve Turkcell 'Yeni Hat Başvurusu Sorgulama' formunun ne gösterdiğinin eklenmesi önerilir.</t>
         </is>
       </c>
-      <c r="N31" s="14" t="inlineStr">
+      <c r="N33" s="14" t="inlineStr">
         <is>
           <t>Numara taşıma başvurusunun durumu Turkcell üzerinden nasıl sorgulanır?
 e-Devlet numara taşıma sorgusunda hangi bilgiler görünür?</t>
         </is>
       </c>
-      <c r="O31" s="14" t="inlineStr">
+      <c r="O33" s="14" t="inlineStr">
         <is>
           <t>Search Console 12 ay</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="16" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/islem-merkezi/ayarlarim/guvenli-internet-ayarlarimi-nasil-degistirebilirim</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D34" s="14" t="inlineStr">
         <is>
           <t>Güvenli internet ayarlarımı nasıl değiştirebilirim?</t>
         </is>
       </c>
-      <c r="E32" s="14" t="inlineStr">
+      <c r="E34" s="14" t="inlineStr">
         <is>
           <t>• SMS ile iptal yolunun ara başlıkla eklenmesi
 • Profil değişikliği yolunun eklenmesi
 • Başlığın 'Güvenli İnternet nasıl kapatılır veya değiştirilir?' olarak genişletilmesi</t>
         </is>
       </c>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="F34" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="19" t="n">
+      <c r="G34" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" s="19" t="n">
         <v>44329</v>
       </c>
-      <c r="I32" s="19" t="n">
+      <c r="I34" s="19" t="n">
         <v>5329</v>
       </c>
-      <c r="J32" s="11" t="n">
+      <c r="J34" s="11" t="n">
         <v>3.8</v>
       </c>
-      <c r="K32" s="14" t="inlineStr">
+      <c r="K34" s="14" t="inlineStr">
         <is>
           <t>turkcell güvenli arama kapatma · güvenli arama kapatma turkcell · güvenli arama nasıl kapatılır turkcell</t>
         </is>
       </c>
-      <c r="L32" s="14" t="inlineStr">
+      <c r="L34" s="14" t="inlineStr">
         <is>
           <t>İşlem Merkezi adımlarını veriyor (64 kelime). Ürün sayfasındaki SMS ile iptal ve profil değişikliği yolu destek sayfasında yok; 'güvenli internet nedir' sorgusunda kurumsal kopya sıralanıyor.</t>
         </is>
       </c>
-      <c r="M32" s="14" t="inlineStr">
+      <c r="M34" s="14" t="inlineStr">
         <is>
           <t>SMS ile iptal ve profil değişikliği yolunun ara başlıkla eklenmesi ve başlığın 'Güvenli İnternet nasıl kapatılır veya değiştirilir?' olarak genişletilmesi önerilir.</t>
         </is>
       </c>
-      <c r="N32" s="14" t="inlineStr">
+      <c r="N34" s="14" t="inlineStr">
         <is>
           <t>Güvenli İnternet nasıl kapatılır?
 Güvenli İnternet profili SMS ile nasıl değiştirilir?</t>
         </is>
       </c>
-      <c r="O32" s="14" t="inlineStr">
+      <c r="O34" s="14" t="inlineStr">
         <is>
           <t>Search Console 12 ay</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="B33" s="16" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C35" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcell-faturali-dunyasina-hos-geldiniz/veribilgi-isleme-izni-nedir</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D35" s="14" t="inlineStr">
         <is>
           <t>Veri/Bilgi işleme izni nedir?</t>
         </is>
       </c>
-      <c r="E33" s="14" t="inlineStr">
+      <c r="E35" s="14" t="inlineStr">
         <is>
           <t>• Veri işleme izni tanımının ve kapsamının yazılması
 • İzin verme ve geri alma kanallarının eklenmesi
 • İzin politikasına bağlantı verilmesi</t>
         </is>
       </c>
-      <c r="F33" s="11" t="inlineStr">
+      <c r="F35" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" s="19" t="n">
+      <c r="G35" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" s="19" t="n">
         <v>33205</v>
       </c>
-      <c r="I33" s="19" t="n">
+      <c r="I35" s="19" t="n">
         <v>2129</v>
       </c>
-      <c r="J33" s="11" t="n">
+      <c r="J35" s="11" t="n">
         <v>3.4</v>
       </c>
-      <c r="K33" s="14" t="inlineStr">
+      <c r="K35" s="14" t="inlineStr">
         <is>
           <t>veri işleme izni nedir · turkcell veri işleme izni nedir · dijital veri işleme izni nedir</t>
         </is>
       </c>
-      <c r="L33" s="14" t="inlineStr">
+      <c r="L35" s="14" t="inlineStr">
         <is>
           <t>Sayfa 16 kelime: tanım yok, yalnızca 'DEVAM yazıp 3557'ye gönderebilirsiniz'. 'Zararlı mı' sorusu da geliyor.</t>
         </is>
       </c>
-      <c r="M33" s="14" t="inlineStr">
+      <c r="M35" s="14" t="inlineStr">
         <is>
           <t>Tanım, kapsam, izin verme ve geri alma kanalları ile izin politikasına bağlantıyla yeniden yazılması önerilir; içerik için marka ve hukuk onayı gerekir.</t>
         </is>
       </c>
-      <c r="N33" s="14" t="inlineStr">
+      <c r="N35" s="14" t="inlineStr">
         <is>
           <t>Veri işleme izni hangi verileri kapsar?
 Veri işleme izni nasıl verilir ve geri alınır?
 Veri işleme izni vermek zorunlu mu?</t>
         </is>
       </c>
-      <c r="O33" s="14" t="inlineStr">
+      <c r="O35" s="14" t="inlineStr">
         <is>
           <t>Search Console 12 ay</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="11" t="n">
-        <v>30</v>
-      </c>
-      <c r="B34" s="16" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C36" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numara-tasima-nedir</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="D36" s="14" t="inlineStr">
         <is>
           <t>Numara taşıma nedir?</t>
         </is>
       </c>
-      <c r="E34" s="14" t="inlineStr">
+      <c r="E36" s="14" t="inlineStr">
         <is>
           <t>• Başlığa 'operatör değişikliği' eşanlamının eklenmesi
 • Süreç özetinin (süre, kesinti, 90 gün şartı) kısa bir bölümde toplanması
 • 'Faturasız hattan faturalıya numara taşınabilir mi?' sorusunun eklenmesi</t>
         </is>
       </c>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="F36" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="19" t="n">
+      <c r="G36" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" s="19" t="n">
         <v>27686</v>
       </c>
-      <c r="I34" s="19" t="n">
+      <c r="I36" s="19" t="n">
         <v>271</v>
       </c>
-      <c r="J34" s="11" t="n">
+      <c r="J36" s="11" t="n">
         <v>6.8</v>
       </c>
-      <c r="K34" s="14" t="inlineStr">
+      <c r="K36" s="14" t="inlineStr">
         <is>
           <t>turkcell numara taşıma · numara · turkcell hat taşıma</t>
         </is>
       </c>
-      <c r="L34" s="14" t="inlineStr">
+      <c r="L36" s="14" t="inlineStr">
         <is>
           <t>Sayfa numara taşımayı 'numara değiştirilmeden operatörün değiştirilmesi' olarak tanımlıyor; 'operatör değişikliği' ifadesi başlıkta yok. Süreç (en fazla 4 gün, yaklaşık 15 dakika kesinti, 90 gün şartı) ayrı sayfalarda.</t>
         </is>
       </c>
-      <c r="M34" s="14" t="inlineStr">
+      <c r="M36" s="14" t="inlineStr">
         <is>
           <t>Başlığa 'operatör değişikliği' eşanlamının eklenmesi, süreç özetinin kısa bir bölümle bu sayfada toplanması ve başka operatörde faturasız kullanılan numaranın Turkcell'e faturalı olarak taşınabileceğinin ayrı soru olarak eklenmesi önerilir.</t>
         </is>
       </c>
-      <c r="N34" s="14" t="inlineStr">
+      <c r="N36" s="14" t="inlineStr">
         <is>
           <t>Operatör değişikliği nasıl yapılır?
 Faturasız hattan faturalıya numara taşınabilir mi?</t>
         </is>
       </c>
-      <c r="O34" s="14" t="inlineStr">
+      <c r="O36" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="n">
-        <v>31</v>
-      </c>
-      <c r="B35" s="16" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/yurtdisi/yurtdisinda-kullanim/yurtdisinda-hesapli-kullanim-icin-nelere-dikkat-etmem-gerekir</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D37" s="14" t="inlineStr">
         <is>
           <t>Yurt dışında paketsiz veya paket aşımı internet kullanımında nelere dikkat etmem gerekir?</t>
         </is>
       </c>
-      <c r="E35" s="14" t="inlineStr">
+      <c r="E37" s="14" t="inlineStr">
         <is>
           <t>• Başlık ve title'ın 'Yurt dışında paketsiz kullanım nasıl ücretlendirilir?' olarak güncellenmesi
 • Ücret tablosunun yapılandırılmış tablo haline getirilmesi
@@ -10302,361 +10559,361 @@
 • Bu üç yolu özetleyen bir giriş bölümünün sayfaya eklenmesi</t>
         </is>
       </c>
-      <c r="F35" s="11" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="19" t="n">
+      <c r="G37" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" s="19" t="n">
         <v>15285</v>
       </c>
-      <c r="I35" s="19" t="n">
+      <c r="I37" s="19" t="n">
         <v>612</v>
       </c>
-      <c r="J35" s="11" t="n">
+      <c r="J37" s="11" t="n">
         <v>4.2</v>
       </c>
-      <c r="K35" s="14" t="inlineStr">
+      <c r="K37" s="14" t="inlineStr">
         <is>
           <t>yurtdışında internet kullanımı · yurt dışında internet kullanımı · turkcell müşteri hizmetleri yurtdışı</t>
         </is>
       </c>
-      <c r="L35" s="14" t="inlineStr">
+      <c r="L37" s="14" t="inlineStr">
         <is>
           <t>Sayfa ülke gruplarına göre paketsiz kullanım birim ücretlerini, Tarifen Yurt Dışında Geçerli aşım kurallarını ve harcama limitlerini içeriyor; başlık ücret sorusunu ve 'yurt dışında internet nasıl kullanılır' sorusunu yansıtmıyor. Ücret tablosu 06.02.2024 tarihli.</t>
         </is>
       </c>
-      <c r="M35" s="14" t="inlineStr">
+      <c r="M37" s="14" t="inlineStr">
         <is>
           <t>Başlık ve title'ın 'Yurt dışında paketsiz kullanım nasıl ücretlendirilir?' yönünde güncellenmesi, ücret tablosunun yapılandırılmış tablo haline getirilmesi ve yurt dışında internet kullanımının üç yolunu (Tarifen Yurt Dışında Geçerli, yurt dışı paketi, paketsiz kullanım) anlatan bir giriş bölümünün eklenmesi önerilir. Ücretlerin güncelliği marka tarafından teyit edilmelidir.</t>
         </is>
       </c>
-      <c r="N35" s="14" t="inlineStr">
+      <c r="N37" s="14" t="inlineStr">
         <is>
           <t>Yurt dışında internet nasıl kullanılır?
 Yurt dışında paketsiz kullanım ne kadar tutar?</t>
         </is>
       </c>
-      <c r="O35" s="14" t="inlineStr">
+      <c r="O37" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/faturali/hattimi-gecici-olarak-giden-ve-gelengiden-iletisime-nasil-kapatabilirim</t>
         </is>
       </c>
-      <c r="D36" s="14" t="inlineStr">
+      <c r="D38" s="14" t="inlineStr">
         <is>
           <t>Hattımı geçici olarak giden ve gelen/giden iletişime nasıl kapatabilirim?</t>
         </is>
       </c>
-      <c r="E36" s="14" t="inlineStr">
+      <c r="E38" s="14" t="inlineStr">
         <is>
           <t>• Başlık ve title'a 'hat dondurma' ifadesinin eklenmesi
 • Süre, otomatik açılma ve taahhüt kurallarının bireysel için doğrulanarak eklenmesi</t>
         </is>
       </c>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="F38" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="19" t="n">
+      <c r="G38" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" s="19" t="n">
         <v>14095</v>
       </c>
-      <c r="I36" s="19" t="n">
+      <c r="I38" s="19" t="n">
         <v>1993</v>
       </c>
-      <c r="J36" s="11" t="n">
+      <c r="J38" s="11" t="n">
         <v>3.4</v>
       </c>
-      <c r="K36" s="14" t="inlineStr">
+      <c r="K38" s="14" t="inlineStr">
         <is>
           <t>turkcell hat kapatma · hat dondurma · turkcell hat dondurma</t>
         </is>
       </c>
-      <c r="L36" s="14" t="inlineStr">
+      <c r="L38" s="14" t="inlineStr">
         <is>
           <t>77 kelime; 3 ay sınırı ve 212,70 TL ücret var. Kullanıcının kullandığı 'hat dondurma' ifadesi başlıkta yok; azami süre ve taahhüt bilgisi yalnızca kurumsal sayfada ve tıklamanın çoğunu kurumsal sayfa alıyor.</t>
         </is>
       </c>
-      <c r="M36" s="14" t="inlineStr">
+      <c r="M38" s="14" t="inlineStr">
         <is>
           <t>Başlık ve title'a 'hat dondurma' ifadesinin eklenmesi, kurumsal sayfadaki süre, otomatik açılma ve taahhüt kurallarının bireysel için geçerliliği doğrulanarak eklenmesi önerilir.</t>
         </is>
       </c>
-      <c r="N36" s="14" t="inlineStr">
+      <c r="N38" s="14" t="inlineStr">
         <is>
           <t>Turkcell hat dondurma nasıl yapılır?
 Hat dondurma en fazla ne kadar sürer?
 Hat dondurulduğunda taahhüt süresi ne olur?</t>
         </is>
       </c>
-      <c r="O36" s="14" t="inlineStr">
+      <c r="O38" s="14" t="inlineStr">
         <is>
           <t>Search Console 12 ay · Rakip destek karşılaştırması</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="n">
-        <v>33</v>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C39" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/kullandigim-hattin-yasal-sahibi-vefat-etti-hatti-uzerime-nasil-alabilirim</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="D39" s="14" t="inlineStr">
         <is>
           <t>Kullandığım hattın yasal sahibi vefat etti; hattı üzerime nasıl alabilirim?</t>
         </is>
       </c>
-      <c r="E37" s="14" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>• Evrak listesinin tamamlanması
 • İptal seçeneği ve ücret bilgisinin eklenmesi
 • Başlığın 'Vefat eden kişinin hattı nasıl devralınır ya da iptal edilir?' olarak genişletilmesi</t>
         </is>
       </c>
-      <c r="F37" s="11" t="inlineStr">
+      <c r="F39" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" s="19" t="n">
+      <c r="G39" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" s="19" t="n">
         <v>8793</v>
       </c>
-      <c r="I37" s="19" t="n">
+      <c r="I39" s="19" t="n">
         <v>2033</v>
       </c>
-      <c r="J37" s="11" t="n">
+      <c r="J39" s="11" t="n">
         <v>3.4</v>
       </c>
-      <c r="K37" s="14" t="inlineStr">
+      <c r="K39" s="14" t="inlineStr">
         <is>
           <t>ölen kişinin telefon hattı nasıl kapatılır · vefat eden kişinin hattı ne zaman kapanır turkcell · turkcell ölen kişinin hattını kapatma</t>
         </is>
       </c>
-      <c r="L37" s="14" t="inlineStr">
+      <c r="L39" s="14" t="inlineStr">
         <is>
           <t>Gövde 23 kelime ve evrak listesi yarım kalıyor; iptal niyetli sorgular ('ölen kişinin hattını kapatma') karşılanmıyor.</t>
         </is>
       </c>
-      <c r="M37" s="14" t="inlineStr">
+      <c r="M39" s="14" t="inlineStr">
         <is>
           <t>Evrak listesinin tamamlanması, iptal seçeneği ve ücret bilgisinin eklenmesi, başlığın 'Vefat eden kişinin hattı nasıl devralınır ya da iptal edilir?' olarak genişletilmesi önerilir (içerik marka doğrulamasıyla).</t>
         </is>
       </c>
-      <c r="N37" s="14" t="inlineStr">
+      <c r="N39" s="14" t="inlineStr">
         <is>
           <t>Vefat eden kişinin hattı nasıl iptal edilir?
 Veraseten devir için hangi evraklar gerekir?</t>
         </is>
       </c>
-      <c r="O37" s="14" t="inlineStr">
+      <c r="O39" s="14" t="inlineStr">
         <is>
           <t>Rakip destek karşılaştırması</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="11" t="n">
-        <v>34</v>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="11" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C40" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numarami-tasimak-ucretli-midir</t>
         </is>
       </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="D40" s="14" t="inlineStr">
         <is>
           <t>Numaramı taşımak ücretli midir?</t>
         </is>
       </c>
-      <c r="E38" s="14" t="inlineStr">
+      <c r="E40" s="14" t="inlineStr">
         <is>
           <t>• Eski operatörde cayma bedeli oluşabileceği bilgisinin ara başlık olarak eklenmesi
 • Ödenmemiş borcu olan hattın taşınabileceği ancak eski operatöre karşı yükümlülüğün süreceği bilgisinin eklenmesi
 • Yeni 'Cayma bedeli nedir?' sayfasına iç link verilmesi</t>
         </is>
       </c>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="F40" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G38" s="14" t="inlineStr">
+      <c r="G40" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/kampanya/kampanyalar-faturali/numarami-tasimak-ucretli-midir</t>
         </is>
       </c>
-      <c r="H38" s="19" t="n">
+      <c r="H40" s="19" t="n">
         <v>6962</v>
       </c>
-      <c r="I38" s="19" t="n">
+      <c r="I40" s="19" t="n">
         <v>617</v>
       </c>
-      <c r="J38" s="11" t="n">
+      <c r="J40" s="11" t="n">
         <v>4.4</v>
       </c>
-      <c r="K38" s="14" t="inlineStr">
+      <c r="K40" s="14" t="inlineStr">
         <is>
           <t>numara taşıma ücretli mi · hat tasima ucretlimi · hat taşıma ücretli mi</t>
         </is>
       </c>
-      <c r="L38" s="14" t="inlineStr">
+      <c r="L40" s="14" t="inlineStr">
         <is>
           <t>Sayfa 13 kelime ('Hayır, herhangi bir ücret ödemezsiniz'); 'hat taşıma ücreti' sorgusunda tıklama paket seçimine gidiyor. Eski operatördeki taahhüt, borç ve cayma bedeli sorusu cevapsız.</t>
         </is>
       </c>
-      <c r="M38" s="14" t="inlineStr">
+      <c r="M40" s="14" t="inlineStr">
         <is>
           <t>Eski operatördeki kampanya ve taahhüt ile borcu olan hattın taşınması soruları bu sayfaya ara başlık olarak eklenebilir: taşımanın Turkcell tarafında ücretsiz olması, eski operatördeki taahhüt süresi dolmadan taşımada o operatörün sözleşme koşullarına göre cayma bedeli talep edebilmesi, ödenmemiş borcun taşıma talebinin ret nedenleri arasında yer almaması ancak eski operatöre karşı yükümlülüğün sürmesi. Yeni 'Cayma bedeli nedir?' sayfasına iç link verilebilir.</t>
         </is>
       </c>
-      <c r="N38" s="14" t="inlineStr">
+      <c r="N40" s="14" t="inlineStr">
         <is>
           <t>Numara taşırken mevcut operatörde cayma bedeli oluşur mu?
 Borcu olan hat başka operatöre taşınabilir mi?</t>
         </is>
       </c>
-      <c r="O38" s="14" t="inlineStr">
+      <c r="O40" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi · Search Console 12 ay</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="B39" s="16" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C39" s="14" t="inlineStr">
+      <c r="C41" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/islem-merkezi/ayarlarim/hangi-durumlarda-sim-kart-degisikligi-yapabilirim</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D41" s="14" t="inlineStr">
         <is>
           <t>Hangi durumlarda Sim Kart değişikliği yapabilirim?</t>
         </is>
       </c>
-      <c r="E39" s="14" t="inlineStr">
+      <c r="E41" s="14" t="inlineStr">
         <is>
           <t>• 4.5G bölümündeki ücret sayfasının bu sayfayla birleştirilmesi
 • Ücret, kanal ve kimlik bilgisinin tek sayfada verilmesi
 • eSIM geçişine iç link eklenmesi</t>
         </is>
       </c>
-      <c r="F39" s="11" t="inlineStr">
+      <c r="F41" s="11" t="inlineStr">
         <is>
           <t>İçerik + Teknik</t>
         </is>
       </c>
-      <c r="G39" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="19" t="n">
+      <c r="G41" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" s="19" t="n">
         <v>1066</v>
       </c>
-      <c r="I39" s="19" t="n">
+      <c r="I41" s="19" t="n">
         <v>167</v>
       </c>
-      <c r="J39" s="11" t="n">
+      <c r="J41" s="11" t="n">
         <v>3.7</v>
       </c>
-      <c r="K39" s="14" t="inlineStr">
+      <c r="K41" s="14" t="inlineStr">
         <is>
           <t>sim kart değişikliği nedir · sim kart değiştirme · sim değiştirme</t>
         </is>
       </c>
-      <c r="L39" s="14" t="inlineStr">
+      <c r="L41" s="14" t="inlineStr">
         <is>
           <t>40 kelime; ücret bilgisi yalnızca 4.5G bölümündeki 19 kelimelik 'Sim kart değişikliği ücretli midir?' sayfasında. SIM değişikliği ücret sorgularında kurumsal sayfa sıralanıyor; kayıp SIM sayfası iyi çalışıyor.</t>
         </is>
       </c>
-      <c r="M39" s="14" t="inlineStr">
+      <c r="M41" s="14" t="inlineStr">
         <is>
           <t>4.5G bölümündeki ücret sayfasının bu sayfayla birleştirilmesi (ya da hattiniz/abonelik-islemleri altına taşınması), ücret, kanal ve kimlik bilgisinin tek sayfada verilmesi ve eSIM geçişine iç link eklenmesi önerilir.</t>
         </is>
       </c>
-      <c r="N39" s="14" t="inlineStr">
+      <c r="N41" s="14" t="inlineStr">
         <is>
           <t>SIM kart değişikliği nasıl yapılır?
 SIM kart değişikliği ücreti ne kadar?
 SIM kart değişince numara ve paketler değişir mi?</t>
         </is>
       </c>
-      <c r="O39" s="14" t="inlineStr">
+      <c r="O41" s="14" t="inlineStr">
         <is>
           <t>Search Console 12 ay · Rakip destek karşılaştırması</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="11" t="n">
-        <v>36</v>
-      </c>
-      <c r="B40" s="16" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="11" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
         <is>
           <t>Faz 2</t>
         </is>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C42" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcell-faturali-dunyasina-hos-geldiniz/akilli-fatura-nedir</t>
         </is>
       </c>
-      <c r="D40" s="14" t="inlineStr">
+      <c r="D42" s="14" t="inlineStr">
         <is>
           <t>Akıllı Fatura nedir?</t>
         </is>
       </c>
-      <c r="E40" s="14" t="inlineStr">
+      <c r="E42" s="14" t="inlineStr">
         <is>
           <t>• Sayfanın 'Akıllı Fatura nedir' ara başlığıyla genişletilmesi
 • Ek fayda bilgisinin (her yöne 50 dakika, 50 SMS, 50 MB) eklenmesi
@@ -10665,191 +10922,50 @@
 • 'Paket aşımı nedir, nasıl kapatılır?' sayfasına iç link verilmesi</t>
         </is>
       </c>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="F42" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G40" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="19" t="n">
+      <c r="G42" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" s="19" t="n">
         <v>687</v>
       </c>
-      <c r="I40" s="19" t="n">
+      <c r="I42" s="19" t="n">
         <v>48</v>
       </c>
-      <c r="J40" s="11" t="n">
+      <c r="J42" s="11" t="n">
         <v>3.3</v>
       </c>
-      <c r="K40" s="14" t="inlineStr">
+      <c r="K42" s="14" t="inlineStr">
         <is>
           <t>turkcell akıllı fatura nedir · akıllı fatura nedir · turkcell akıllı fatura</t>
         </is>
       </c>
-      <c r="L40" s="14" t="inlineStr">
+      <c r="L42" s="14" t="inlineStr">
         <is>
           <t>Destek sayfası 23 kelime ve kampanya sayfasına bağlantı veriyor; ek fayda, ücret ve iptal bilgisi yok. 'akıllı fatura ek fayda nedir' sorgusu kampanya sayfasına ve basın bültenine düşüyor.</t>
         </is>
       </c>
-      <c r="M40" s="14" t="inlineStr">
+      <c r="M42" s="14" t="inlineStr">
         <is>
           <t>Sayfanın 4 ara başlıkla genişletilmesi önerilir: Akıllı Fatura nedir, ek fayda (her yöne 50 dakika, 50 SMS, 50 MB), katılımın ücretsiz olması ve katılım/iptal kanalları. Akıllı Fatura ek faydası sorusu ayrı sayfa yerine bu sayfada cevaplanabilir; önerilen 'Paket aşımı nedir, nasıl kapatılır?' sayfasına iç link verilebilir.</t>
         </is>
       </c>
-      <c r="N40" s="14" t="inlineStr">
+      <c r="N42" s="14" t="inlineStr">
         <is>
           <t>Akıllı Fatura ek fayda nedir?
 Akıllı Fatura ücretli mi?
 Akıllı Fatura nasıl iptal edilir?</t>
         </is>
       </c>
-      <c r="O40" s="14" t="inlineStr">
+      <c r="O42" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi · Search Console 12 ay</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="11" t="n">
-        <v>37</v>
-      </c>
-      <c r="B41" s="16" t="inlineStr">
-        <is>
-          <t>Faz 2</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/destek/5g/genel/5g-nedir-4-5gden-temel-farklari-nelerdir</t>
-        </is>
-      </c>
-      <c r="D41" s="14" t="inlineStr">
-        <is>
-          <t>5G nedir, 4.5G’den temel farkları nelerdir?</t>
-        </is>
-      </c>
-      <c r="E41" s="14" t="inlineStr">
-        <is>
-          <t>• 'Turkcell 5G ne zaman başladı?' ara başlığının eklenmesi
-• '5G hangi bölgelerde kullanılabiliyor?' sorusunun eklenmesi</t>
-        </is>
-      </c>
-      <c r="F41" s="11" t="inlineStr">
-        <is>
-          <t>İçerik</t>
-        </is>
-      </c>
-      <c r="G41" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="19" t="n">
-        <v>82</v>
-      </c>
-      <c r="I41" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="J41" s="11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K41" s="14" t="inlineStr">
-        <is>
-          <t>5g mi 4.5g mi · 4.5 g mi daha iyi 5 g mi · 5 g turkcell</t>
-        </is>
-      </c>
-      <c r="L41" s="14" t="inlineStr">
-        <is>
-          <t>35 kelimelik tanım; başlangıç tarihi ve kapsama bilgisi yok. /5g/ sayfasında ülke geneli yaygınlaşma bilgisi yer alıyor.</t>
-        </is>
-      </c>
-      <c r="M41" s="14" t="inlineStr">
-        <is>
-          <t>'Turkcell 5G ne zaman başladı?' ara başlığının /5g/ sayfasındaki bilgiyle eklenmesi önerilir; kapsama sorusu için marka doğrulaması gerekir.</t>
-        </is>
-      </c>
-      <c r="N41" s="14" t="inlineStr">
-        <is>
-          <t>Turkcell 5G ne zaman başladı?
-5G hangi bölgelerde kullanılabiliyor?</t>
-        </is>
-      </c>
-      <c r="O41" s="14" t="inlineStr">
-        <is>
-          <t>Search Console 12 ay</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="11" t="n">
-        <v>38</v>
-      </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>Faz 2</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/destek/financell/financell-turkcell-finansman-a-s/turkcell-finansman-tekliflerinden-kimler-faydalanabilir</t>
-        </is>
-      </c>
-      <c r="D42" s="14" t="inlineStr">
-        <is>
-          <t>Financell tekliflerinden kimler faydalanabilir?</t>
-        </is>
-      </c>
-      <c r="E42" s="14" t="inlineStr">
-        <is>
-          <t>• Başlık ve ilk cümleye 'faturaya ek telefon' ifadesinin eklenmesi
-• Yeni 'Faturaya ek telefon nasıl alınır?' sayfasından iç link verilmesi</t>
-        </is>
-      </c>
-      <c r="F42" s="11" t="inlineStr">
-        <is>
-          <t>İçerik</t>
-        </is>
-      </c>
-      <c r="G42" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="I42" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" s="14" t="inlineStr">
-        <is>
-          <t>turkcellden taksitle telefon almak için gerekenler</t>
-        </is>
-      </c>
-      <c r="L42" s="14" t="inlineStr">
-        <is>
-          <t>Faturaya ek cihaz koşulları bu sayfada birebir yazılı; başlıkta ve metinde kullanıcının kullandığı 'faturaya ek telefon' ifadesi yok.</t>
-        </is>
-      </c>
-      <c r="M42" s="14" t="inlineStr">
-        <is>
-          <t>Başlık ve ilk cümleye 'faturaya ek telefon' ifadesinin eklenmesi ve yeni 'Faturaya ek telefon nasıl alınır?' sayfasından iç link verilmesi önerilir.</t>
-        </is>
-      </c>
-      <c r="N42" s="14" t="inlineStr">
-        <is>
-          <t>Faturaya ek telefon almak için hangi koşullar aranır?</t>
-        </is>
-      </c>
-      <c r="O42" s="14" t="inlineStr">
-        <is>
-          <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
     </row>
@@ -10857,25 +10973,25 @@
       <c r="A43" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="20" t="inlineStr">
-        <is>
-          <t>Faz 3</t>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>Faz 2</t>
         </is>
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim</t>
+          <t>https://www.turkcell.com.tr/destek/5g/genel/5g-nedir-4-5gden-temel-farklari-nelerdir</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
         <is>
-          <t>Paket / Tarife değişikliğini nasıl yapabilirim?</t>
+          <t>5G nedir, 4.5G’den temel farkları nelerdir?</t>
         </is>
       </c>
       <c r="E43" s="14" t="inlineStr">
         <is>
-          <t>• Tarife listeleme sayfalarına yönlendiren bağlantının eklenmesi
-• Sayfanın işlem adımlarına odaklanacak şekilde sadeleştirilmesi</t>
+          <t>• 'Turkcell 5G ne zaman başladı?' ara başlığının eklenmesi
+• '5G hangi bölgelerde kullanılabiliyor?' sorusunun eklenmesi</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -10889,37 +11005,38 @@
         </is>
       </c>
       <c r="H43" s="19" t="n">
-        <v>1111403</v>
+        <v>82</v>
       </c>
       <c r="I43" s="19" t="n">
-        <v>17547</v>
+        <v>4</v>
       </c>
       <c r="J43" s="11" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>turkcell faturalı tarifeler · turkcell tarifeler · turkcell faturalı paketler</t>
+          <t>5g mi 4.5g mi · 4.5 g mi daha iyi 5 g mi · 5 g turkcell</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>Sayfa 'turkcell tarifeler' gibi listeleme niyetli sorgularda görünüyor; aynı içerik 'paket-asim-ucreti-nedir' ve 'tarife-bilgilerimi-nasil-sorgularim' adreslerinde de gösteriliyor.</t>
+          <t>35 kelimelik tanım; başlangıç tarihi ve kapsama bilgisi yok. /5g/ sayfasında ülke geneli yaygınlaşma bilgisi yer alıyor.</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
         <is>
-          <t>Sayfadan tarife listeleme sayfalarına yönlendiren bağlantı eklenmesi ve sayfanın işlem adımlarına odaklanması önerilir. Aynı içeriği gösteren adresler teknik maddede ele alınır.</t>
+          <t>'Turkcell 5G ne zaman başladı?' ara başlığının /5g/ sayfasındaki bilgiyle eklenmesi önerilir; kapsama sorusu için marka doğrulaması gerekir.</t>
         </is>
       </c>
       <c r="N43" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Turkcell 5G ne zaman başladı?
+5G hangi bölgelerde kullanılabiliyor?</t>
         </is>
       </c>
       <c r="O43" s="14" t="inlineStr">
         <is>
-          <t>Search Console 3 ay konum analizi</t>
+          <t>Search Console 12 ay</t>
         </is>
       </c>
     </row>
@@ -10927,24 +11044,25 @@
       <c r="A44" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="20" t="inlineStr">
-        <is>
-          <t>Faz 3</t>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>Faz 2</t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcell-faturali-dunyasina-hos-geldiniz/turkcell-faturali-dunyasina-hos-geldiniz</t>
+          <t>https://www.turkcell.com.tr/destek/financell/financell-turkcell-finansman-a-s/turkcell-finansman-tekliflerinden-kimler-faydalanabilir</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>Turkcell Faturalı Dünyasına Hoş Geldiniz</t>
+          <t>Financell tekliflerinden kimler faydalanabilir?</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t>• Sayfadan ilgili tarife ve başvuru sayfalarına yönlendiren iç link bloğunun eklenmesi</t>
+          <t>• Başlık ve ilk cümleye 'faturaya ek telefon' ifadesinin eklenmesi
+• Yeni 'Faturaya ek telefon nasıl alınır?' sayfasından iç link verilmesi</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr">
@@ -10954,41 +11072,41 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/kampanya/kampanyalar-faturali/turkcell-faturali-dunyasina-hos-geldiniz</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H44" s="19" t="n">
-        <v>834475</v>
+        <v>1</v>
       </c>
       <c r="I44" s="19" t="n">
-        <v>11083</v>
+        <v>1</v>
       </c>
       <c r="J44" s="11" t="n">
-        <v>6.7</v>
+        <v>1</v>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>turkcell yeni gelen · turkcell faturalı tarifeler · turkcell yeni gelen faturalı</t>
+          <t>turkcellden taksitle telefon almak için gerekenler</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>Karşılama sayfası kurgusunda; gelen sorgular tarife ve yeni hat niyetli. Aynı başlık kampanya bölümünde ikinci adreste yayınlanıyor.</t>
+          <t>Faturaya ek cihaz koşulları bu sayfada birebir yazılı; başlıkta ve metinde kullanıcının kullandığı 'faturaya ek telefon' ifadesi yok.</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
         <is>
-          <t>Sayfadan ilgili tarife ve başvuru sayfalarına yönlendiren iç link bloğu eklenmesi önerilir.</t>
+          <t>Başlık ve ilk cümleye 'faturaya ek telefon' ifadesinin eklenmesi ve yeni 'Faturaya ek telefon nasıl alınır?' sayfasından iç link verilmesi önerilir.</t>
         </is>
       </c>
       <c r="N44" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Faturaya ek telefon almak için hangi koşullar aranır?</t>
         </is>
       </c>
       <c r="O44" s="14" t="inlineStr">
         <is>
-          <t>Search Console 3 ay konum analizi</t>
+          <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
     </row>
@@ -11003,204 +11121,203 @@
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
+          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim</t>
+        </is>
+      </c>
+      <c r="D45" s="14" t="inlineStr">
+        <is>
+          <t>Paket / Tarife değişikliğini nasıl yapabilirim?</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>• 'Turkcell Rahat tarifesinden çıkış ve geçiş' ara başlığının eklenmesi
+• Rahat'ın taahhütsüz olduğu ve çıkış için hat iptaline gerek olmadığı bilgisinin eklenmesi
+• Önerilen Turkcell Rahat iptal sayfasına ve Rahat'tan Faturalıya Geçiş sayfasına iç link verilmesi</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr">
+        <is>
+          <t>İçerik</t>
+        </is>
+      </c>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H45" s="19" t="n">
+        <v>1111403</v>
+      </c>
+      <c r="I45" s="19" t="n">
+        <v>17547</v>
+      </c>
+      <c r="J45" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="K45" s="14" t="inlineStr">
+        <is>
+          <t>turkcell faturalı tarifeler · turkcell tarifeler · turkcell faturalı paketler</t>
+        </is>
+      </c>
+      <c r="L45" s="14" t="inlineStr">
+        <is>
+          <t>Sayfa 'turkcell tarifeler' gibi listeleme niyetli sorgularda görünüyor; aynı içerik 'paket-asim-ucreti-nedir' ve 'tarife-bilgilerimi-nasil-sorgularim' adreslerinde de gösteriliyor.</t>
+        </is>
+      </c>
+      <c r="M45" s="14" t="inlineStr">
+        <is>
+          <t>Sayfadan tarife listeleme sayfalarına yönlendiren bağlantı eklenmesi ve sayfanın işlem adımlarına odaklanması önerilir. Aynı içeriği gösteren adresler teknik maddede ele alınır.</t>
+        </is>
+      </c>
+      <c r="N45" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O45" s="14" t="inlineStr">
+        <is>
+          <t>Search Console 3 ay konum analizi</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="20" t="inlineStr">
+        <is>
+          <t>Faz 3</t>
+        </is>
+      </c>
+      <c r="C46" s="14" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcell-faturali-dunyasina-hos-geldiniz/turkcell-faturali-dunyasina-hos-geldiniz</t>
+        </is>
+      </c>
+      <c r="D46" s="14" t="inlineStr">
+        <is>
+          <t>Turkcell Faturalı Dünyasına Hoş Geldiniz</t>
+        </is>
+      </c>
+      <c r="E46" s="14" t="inlineStr">
+        <is>
+          <t>• Sayfadan ilgili tarife ve başvuru sayfalarına yönlendiren iç link bloğunun eklenmesi</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>İçerik</t>
+        </is>
+      </c>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/destek/kampanya/kampanyalar-faturali/turkcell-faturali-dunyasina-hos-geldiniz</t>
+        </is>
+      </c>
+      <c r="H46" s="19" t="n">
+        <v>834475</v>
+      </c>
+      <c r="I46" s="19" t="n">
+        <v>11083</v>
+      </c>
+      <c r="J46" s="11" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="K46" s="14" t="inlineStr">
+        <is>
+          <t>turkcell yeni gelen · turkcell faturalı tarifeler · turkcell yeni gelen faturalı</t>
+        </is>
+      </c>
+      <c r="L46" s="14" t="inlineStr">
+        <is>
+          <t>Karşılama sayfası kurgusunda; gelen sorgular tarife ve yeni hat niyetli. Aynı başlık kampanya bölümünde ikinci adreste yayınlanıyor.</t>
+        </is>
+      </c>
+      <c r="M46" s="14" t="inlineStr">
+        <is>
+          <t>Sayfadan ilgili tarife ve başvuru sayfalarına yönlendiren iç link bloğu eklenmesi önerilir.</t>
+        </is>
+      </c>
+      <c r="N46" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O46" s="14" t="inlineStr">
+        <is>
+          <t>Search Console 3 ay konum analizi</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="11" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="20" t="inlineStr">
+        <is>
+          <t>Faz 3</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="inlineStr">
+        <is>
           <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/fatura-alternatifleri-nelerdir</t>
         </is>
       </c>
-      <c r="D45" s="14" t="inlineStr">
+      <c r="D47" s="14" t="inlineStr">
         <is>
           <t>Fatura alternatifleri nelerdir?</t>
         </is>
       </c>
-      <c r="E45" s="14" t="inlineStr">
+      <c r="E47" s="14" t="inlineStr">
         <is>
           <t>• Numara taşıma sorgularının ticari sayfa ve 'Numara taşıma nedir?' sayfasıyla karşılanması
 • Sayfanın belge alternatifleri konusuna odaklanacak şekilde daraltılması
 • İki kopyadan birinin tek yayın adresi seçilmesi</t>
         </is>
       </c>
-      <c r="F45" s="11" t="inlineStr">
+      <c r="F47" s="11" t="inlineStr">
         <is>
           <t>İçerik + Teknik</t>
         </is>
       </c>
-      <c r="G45" s="14" t="inlineStr">
+      <c r="G47" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/fatura-alternatifleri-nelerdir</t>
         </is>
       </c>
-      <c r="H45" s="19" t="n">
+      <c r="H47" s="19" t="n">
         <v>820348</v>
       </c>
-      <c r="I45" s="19" t="n">
+      <c r="I47" s="19" t="n">
         <v>12235</v>
       </c>
-      <c r="J45" s="11" t="n">
+      <c r="J47" s="11" t="n">
         <v>7.3</v>
       </c>
-      <c r="K45" s="14" t="inlineStr">
+      <c r="K47" s="14" t="inlineStr">
         <is>
           <t>turkcell numara taşıma · turkcell hat taşıma · turkcell numara taşıma kampanyaları</t>
         </is>
       </c>
-      <c r="L45" s="14" t="inlineStr">
+      <c r="L47" s="14" t="inlineStr">
         <is>
           <t>Sayfa 'turkcell numara taşıma' ve 'turkcell hat taşıma' sorgularında görünüyor; başlık belge alternatiflerini anlatıyor. Aynı başlık abonelik işlemleri bölümünde ikinci adreste yayınlanıyor.</t>
         </is>
       </c>
-      <c r="M45" s="14" t="inlineStr">
+      <c r="M47" s="14" t="inlineStr">
         <is>
           <t>Taşıma sorgularının ticari sayfa ve 'Numara taşıma nedir?' sayfasıyla karşılanması, bu sayfanın belge alternatifleri konusuna odaklanması ve iki kopyadan birinin tek yayın adresi seçilmesi önerilir.</t>
         </is>
       </c>
-      <c r="N45" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O45" s="14" t="inlineStr">
+      <c r="N47" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O47" s="14" t="inlineStr">
         <is>
           <t>Search Console 3 ay konum analizi</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="11" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="20" t="inlineStr">
-        <is>
-          <t>Faz 3</t>
-        </is>
-      </c>
-      <c r="C46" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/cagri-bekletme-ozelligini-nasil-aktiflestirebilirim</t>
-        </is>
-      </c>
-      <c r="D46" s="14" t="inlineStr">
-        <is>
-          <t>Çağrı bekletme özelliğini nasıl aktif hale getirebilirim?</t>
-        </is>
-      </c>
-      <c r="E46" s="14" t="inlineStr">
-        <is>
-          <t>• Çağrı bekletme özelliğinin tanımının eklenmesi
-• Anons açıklamasının eklenmesi</t>
-        </is>
-      </c>
-      <c r="F46" s="11" t="inlineStr">
-        <is>
-          <t>İçerik</t>
-        </is>
-      </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="19" t="n">
-        <v>389628</v>
-      </c>
-      <c r="I46" s="19" t="n">
-        <v>30651</v>
-      </c>
-      <c r="J46" s="11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K46" s="14" t="inlineStr">
-        <is>
-          <t>turkcell meşgulken arayanı görme · turkcell arama bekletme · arkadan arayan numarayı görme</t>
-        </is>
-      </c>
-      <c r="L46" s="14" t="inlineStr">
-        <is>
-          <t>44 kelime; *43# / #43# ve UpCall bilgisi var, özellik tanımı yok.</t>
-        </is>
-      </c>
-      <c r="M46" s="14" t="inlineStr">
-        <is>
-          <t>Tanım ve anons açıklamasıyla genişletilmesi önerilir; ücret bilgisi için marka doğrulaması gerekir.</t>
-        </is>
-      </c>
-      <c r="N46" s="14" t="inlineStr">
-        <is>
-          <t>Arama (çağrı) bekletme nedir?
-Meşgulken arayanı görmek ücretli mi?</t>
-        </is>
-      </c>
-      <c r="O46" s="14" t="inlineStr">
-        <is>
-          <t>Search Console 12 ay</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="11" t="n">
-        <v>43</v>
-      </c>
-      <c r="B47" s="20" t="inlineStr">
-        <is>
-          <t>Faz 3</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/tumbara/</t>
-        </is>
-      </c>
-      <c r="D47" s="14" t="inlineStr">
-        <is>
-          <t>Turkcell’de Tumbara Devri Başladı</t>
-        </is>
-      </c>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>• Program sayfası ile kampanya sayfası arasındaki iç link ve kanonik düzeninin kurulması
-• SSS'e 'Tumbara'dan nasıl çıkılır?' sorusunun eklenmesi</t>
-        </is>
-      </c>
-      <c r="F47" s="11" t="inlineStr">
-        <is>
-          <t>İçerik + Teknik</t>
-        </is>
-      </c>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="19" t="n">
-        <v>261825</v>
-      </c>
-      <c r="I47" s="19" t="n">
-        <v>17895</v>
-      </c>
-      <c r="J47" s="11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K47" s="14" t="inlineStr">
-        <is>
-          <t>turkcell indir · tumbara nedir · turkcell</t>
-        </is>
-      </c>
-      <c r="L47" s="14" t="inlineStr">
-        <is>
-          <t>Program sayfası tanım, katılım (TUMBARA 2200) ve ücretsizlik bilgisini SSS'te veriyor; kampanya sayfası aynı sorgularda yarışıyor. Servisten ayrılma yolu sitede yok.</t>
-        </is>
-      </c>
-      <c r="M47" s="14" t="inlineStr">
-        <is>
-          <t>Program sayfası ile kampanya sayfası arasındaki yarışmanın iç link ve kanonik düzeniyle ele alınması ve SSS'e servisten ayrılma sorusunun eklenmesi önerilir (marka doğrulamasıyla).</t>
-        </is>
-      </c>
-      <c r="N47" s="14" t="inlineStr">
-        <is>
-          <t>Tumbara'dan nasıl çıkılır?</t>
-        </is>
-      </c>
-      <c r="O47" s="14" t="inlineStr">
-        <is>
-          <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
     </row>
@@ -11215,417 +11332,418 @@
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
+          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/cagri-bekletme-ozelligini-nasil-aktiflestirebilirim</t>
+        </is>
+      </c>
+      <c r="D48" s="14" t="inlineStr">
+        <is>
+          <t>Çağrı bekletme özelliğini nasıl aktif hale getirebilirim?</t>
+        </is>
+      </c>
+      <c r="E48" s="14" t="inlineStr">
+        <is>
+          <t>• Çağrı bekletme özelliğinin tanımının eklenmesi
+• Anons açıklamasının eklenmesi</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>İçerik</t>
+        </is>
+      </c>
+      <c r="G48" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" s="19" t="n">
+        <v>389628</v>
+      </c>
+      <c r="I48" s="19" t="n">
+        <v>30651</v>
+      </c>
+      <c r="J48" s="11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K48" s="14" t="inlineStr">
+        <is>
+          <t>turkcell meşgulken arayanı görme · turkcell arama bekletme · arkadan arayan numarayı görme</t>
+        </is>
+      </c>
+      <c r="L48" s="14" t="inlineStr">
+        <is>
+          <t>44 kelime; *43# / #43# ve UpCall bilgisi var, özellik tanımı yok.</t>
+        </is>
+      </c>
+      <c r="M48" s="14" t="inlineStr">
+        <is>
+          <t>Tanım ve anons açıklamasıyla genişletilmesi önerilir; ücret bilgisi için marka doğrulaması gerekir.</t>
+        </is>
+      </c>
+      <c r="N48" s="14" t="inlineStr">
+        <is>
+          <t>Arama (çağrı) bekletme nedir?
+Meşgulken arayanı görmek ücretli mi?</t>
+        </is>
+      </c>
+      <c r="O48" s="14" t="inlineStr">
+        <is>
+          <t>Search Console 12 ay</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>Faz 3</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/tumbara/</t>
+        </is>
+      </c>
+      <c r="D49" s="14" t="inlineStr">
+        <is>
+          <t>Turkcell’de Tumbara Devri Başladı</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>• Program sayfası ile kampanya sayfası arasındaki iç link ve kanonik düzeninin kurulması
+• SSS'e 'Tumbara'dan nasıl çıkılır?' sorusunun eklenmesi</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>İçerik + Teknik</t>
+        </is>
+      </c>
+      <c r="G49" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="19" t="n">
+        <v>261825</v>
+      </c>
+      <c r="I49" s="19" t="n">
+        <v>17895</v>
+      </c>
+      <c r="J49" s="11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="K49" s="14" t="inlineStr">
+        <is>
+          <t>turkcell indir · tumbara nedir · turkcell</t>
+        </is>
+      </c>
+      <c r="L49" s="14" t="inlineStr">
+        <is>
+          <t>Program sayfası tanım, katılım (TUMBARA 2200) ve ücretsizlik bilgisini SSS'te veriyor; kampanya sayfası aynı sorgularda yarışıyor. Servisten ayrılma yolu sitede yok.</t>
+        </is>
+      </c>
+      <c r="M49" s="14" t="inlineStr">
+        <is>
+          <t>Program sayfası ile kampanya sayfası arasındaki yarışmanın iç link ve kanonik düzeniyle ele alınması ve SSS'e servisten ayrılma sorusunun eklenmesi önerilir (marka doğrulamasıyla).</t>
+        </is>
+      </c>
+      <c r="N49" s="14" t="inlineStr">
+        <is>
+          <t>Tumbara'dan nasıl çıkılır?</t>
+        </is>
+      </c>
+      <c r="O49" s="14" t="inlineStr">
+        <is>
+          <t>Arama talebi ve SERP analizi</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="20" t="inlineStr">
+        <is>
+          <t>Faz 3</t>
+        </is>
+      </c>
+      <c r="C50" s="14" t="inlineStr">
+        <is>
           <t>https://www.turkcell.com.tr/destek/hizmet-kanallarimiz/magazalar/turkcell-iletisim-merkezleri</t>
         </is>
       </c>
-      <c r="D48" s="14" t="inlineStr">
+      <c r="D50" s="14" t="inlineStr">
         <is>
           <t>Turkcell Mağazaları</t>
         </is>
       </c>
-      <c r="E48" s="14" t="inlineStr">
+      <c r="E50" s="14" t="inlineStr">
         <is>
           <t>• Başlığın 'Turkcell mağazaları (İletişim Merkezleri) kaçta açılır, kaçta kapanır?' olarak güncellenmesi
 • İletişim Merkezi tanımının eklenmesi
 • Pazar günü açılış bilgisinin eklenmesi</t>
         </is>
       </c>
-      <c r="F48" s="11" t="inlineStr">
+      <c r="F50" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="19" t="n">
+      <c r="G50" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H50" s="19" t="n">
         <v>168346</v>
       </c>
-      <c r="I48" s="19" t="n">
+      <c r="I50" s="19" t="n">
         <v>9956</v>
       </c>
-      <c r="J48" s="11" t="n">
+      <c r="J50" s="11" t="n">
         <v>3.6</v>
       </c>
-      <c r="K48" s="14" t="inlineStr">
+      <c r="K50" s="14" t="inlineStr">
         <is>
           <t>turkcell kaçta kapanıyor · turkcell iletişim merkezi · turkcell çalışma saatleri</t>
         </is>
       </c>
-      <c r="L48" s="14" t="inlineStr">
+      <c r="L50" s="14" t="inlineStr">
         <is>
           <t>61 kelime; çalışma saati ve AVM/cadde farkı var. Adres 'iletisim-merkezleri' ancak sayfada İletişim Merkezi tanımı ve pazar günü bilgisi yok.</t>
         </is>
       </c>
-      <c r="M48" s="14" t="inlineStr">
+      <c r="M50" s="14" t="inlineStr">
         <is>
           <t>Başlığın 'Turkcell mağazaları (İletişim Merkezleri) kaçta açılır, kaçta kapanır?' biçiminde güncellenmesi, tanım ve pazar günü bilgisinin eklenmesi önerilir (marka doğrulamasıyla).</t>
         </is>
       </c>
-      <c r="N48" s="14" t="inlineStr">
+      <c r="N50" s="14" t="inlineStr">
         <is>
           <t>Turkcell İletişim Merkezi nedir?
 Turkcell mağazaları pazar günü açık mı?</t>
         </is>
       </c>
-      <c r="O48" s="14" t="inlineStr">
+      <c r="O50" s="14" t="inlineStr">
         <is>
           <t>Search Console 12 ay</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="11" t="n">
-        <v>45</v>
-      </c>
-      <c r="B49" s="20" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="11" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="20" t="inlineStr">
         <is>
           <t>Faz 3</t>
         </is>
       </c>
-      <c r="C49" s="14" t="inlineStr">
+      <c r="C51" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/turkcellailem/</t>
         </is>
       </c>
-      <c r="D49" s="14" t="inlineStr">
+      <c r="D51" s="14" t="inlineStr">
         <is>
           <t>Turkcell Ailem Avantajları Nelerdir?</t>
         </is>
       </c>
-      <c r="E49" s="14" t="inlineStr">
+      <c r="E51" s="14" t="inlineStr">
         <is>
           <t>• SSS bölümünün FAQPage olarak işaretlenmesi
 • Basın bültenlerinden bu sayfaya iç link verilmesi
 • GB transferi kurallarının (ayda en fazla 10 kez, ilk 2 transfer ücretsiz) tek soruda toplanması</t>
         </is>
       </c>
-      <c r="F49" s="11" t="inlineStr">
+      <c r="F51" s="11" t="inlineStr">
         <is>
           <t>İçerik + Teknik</t>
         </is>
       </c>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="19" t="n">
+      <c r="G51" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H51" s="19" t="n">
         <v>97495</v>
       </c>
-      <c r="I49" s="19" t="n">
+      <c r="I51" s="19" t="n">
         <v>19898</v>
       </c>
-      <c r="J49" s="11" t="n">
+      <c r="J51" s="11" t="n">
         <v>3.2</v>
       </c>
-      <c r="K49" s="14" t="inlineStr">
+      <c r="K51" s="14" t="inlineStr">
         <is>
           <t>turkcell aile paketi · turkcell · turkcell ailem</t>
         </is>
       </c>
-      <c r="L49" s="14" t="inlineStr">
+      <c r="L51" s="14" t="inlineStr">
         <is>
           <t>Program sayfası SSS'i Turkcell Ailem tanımını, katılımı ve GB transferi adımlarını birebir cevaplıyor; talep basın bültenleriyle paylaşılıyor.</t>
         </is>
       </c>
-      <c r="M49" s="14" t="inlineStr">
+      <c r="M51" s="14" t="inlineStr">
         <is>
           <t>Yeni destek sayfası açılmaması, SSS bölümünün FAQPage olarak işaretlenmesi ve basın bültenlerinden bu sayfaya iç link verilmesi önerilir. GB transferi kuralları (ayda en fazla 10 kez, ilk 2 transfer ücretsiz) SSS'te tek soruda toplanabilir.</t>
         </is>
       </c>
-      <c r="N49" s="14" t="inlineStr">
+      <c r="N51" s="14" t="inlineStr">
         <is>
           <t>Turkcell Ailem nedir, nasıl katılınır?
 Aile üyeleri arasında GB transferi nasıl yapılır?</t>
         </is>
       </c>
-      <c r="O49" s="14" t="inlineStr">
+      <c r="O51" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="11" t="n">
-        <v>46</v>
-      </c>
-      <c r="B50" s="20" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
         <is>
           <t>Faz 3</t>
         </is>
       </c>
-      <c r="C50" s="14" t="inlineStr">
+      <c r="C52" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/kurumsal/destek/hattiniz/pin-puk/pin-puk-genel-bilgi</t>
         </is>
       </c>
-      <c r="D50" s="14" t="inlineStr">
+      <c r="D52" s="14" t="inlineStr">
         <is>
           <t>PIN/PUK Genel Bilgi</t>
         </is>
       </c>
-      <c r="E50" s="14" t="inlineStr">
+      <c r="E52" s="14" t="inlineStr">
         <is>
           <t>• Bireysel ve kurumsal kapsamın ayrıştırılması
 • Bireysel talebin tek bir bireysel sayfa tarafından karşılanması</t>
         </is>
       </c>
-      <c r="F50" s="11" t="inlineStr">
+      <c r="F52" s="11" t="inlineStr">
         <is>
           <t>Teknik</t>
         </is>
       </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="19" t="n">
+      <c r="G52" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H52" s="19" t="n">
         <v>93497</v>
       </c>
-      <c r="I50" s="19" t="n">
+      <c r="I52" s="19" t="n">
         <v>3073</v>
       </c>
-      <c r="J50" s="11" t="n">
+      <c r="J52" s="11" t="n">
         <v>5.7</v>
       </c>
-      <c r="K50" s="14" t="inlineStr">
+      <c r="K52" s="14" t="inlineStr">
         <is>
           <t>pin kodu kaldırma · pin kodu değiştirme · sim kart pin kodu kaldırma</t>
         </is>
       </c>
-      <c r="L50" s="14" t="inlineStr">
+      <c r="L52" s="14" t="inlineStr">
         <is>
           <t>Kurumsal bölümdeki sayfa bireysel PIN/PUK sayfalarıyla aynı sorguları karşılıyor.</t>
         </is>
       </c>
-      <c r="M50" s="14" t="inlineStr">
+      <c r="M52" s="14" t="inlineStr">
         <is>
           <t>Bireysel ve kurumsal kapsamın ayrıştırılması, bireysel talebin tek bir bireysel sayfa tarafından karşılanması önerilir.</t>
         </is>
       </c>
-      <c r="N50" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O50" s="14" t="inlineStr">
+      <c r="N52" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O52" s="14" t="inlineStr">
         <is>
           <t>Search Console 3 ay konum analizi</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="11" t="n">
-        <v>47</v>
-      </c>
-      <c r="B51" s="20" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="11" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="20" t="inlineStr">
         <is>
           <t>Faz 3</t>
         </is>
       </c>
-      <c r="C51" s="14" t="inlineStr">
+      <c r="C53" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/financell/financell-turkcell-finansman-a-s/kredi-odemelerimi-nasil-yapacagim</t>
         </is>
       </c>
-      <c r="D51" s="14" t="inlineStr">
+      <c r="D53" s="14" t="inlineStr">
         <is>
           <t>Kredi ödemelerimi nasıl yapacağım?</t>
         </is>
       </c>
-      <c r="E51" s="14" t="inlineStr">
+      <c r="E53" s="14" t="inlineStr">
         <is>
           <t>• 'Faturaya ek telefon borcu erken kapatılabilir mi?' ara başlığının eklenmesi
 • Erken iptal hesaplama sayfasına iç link verilmesi
 • Devir sayfasına iç link verilmesi</t>
         </is>
       </c>
-      <c r="F51" s="11" t="inlineStr">
+      <c r="F53" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="19" t="n">
+      <c r="G53" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H53" s="19" t="n">
         <v>83921</v>
       </c>
-      <c r="I51" s="19" t="n">
+      <c r="I53" s="19" t="n">
         <v>9495</v>
       </c>
-      <c r="J51" s="11" t="n">
+      <c r="J53" s="11" t="n">
         <v>2.6</v>
       </c>
-      <c r="K51" s="14" t="inlineStr">
+      <c r="K53" s="14" t="inlineStr">
         <is>
           <t>turkcell finansman · turkcell finansman ödeme · turkcell financell</t>
         </is>
       </c>
-      <c r="L51" s="14" t="inlineStr">
+      <c r="L53" s="14" t="inlineStr">
         <is>
           <t>Erken kapama kanalları bu sayfada; erken ödeme hesabı ve devir senaryosu ayrı Financell sayfalarında.</t>
         </is>
       </c>
-      <c r="M51" s="14" t="inlineStr">
+      <c r="M53" s="14" t="inlineStr">
         <is>
           <t>Sayfaya 'faturaya ek telefon borcu erken kapatılabilir mi?' ara başlığının eklenmesi ve erken iptal hesaplama ile devir sayfalarına iç link verilmesi önerilir.</t>
         </is>
       </c>
-      <c r="N51" s="14" t="inlineStr">
+      <c r="N53" s="14" t="inlineStr">
         <is>
           <t>Faturaya ek alınan cihazın taksitleri erken kapatılabilir mi?</t>
         </is>
       </c>
-      <c r="O51" s="14" t="inlineStr">
+      <c r="O53" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="n">
-        <v>48</v>
-      </c>
-      <c r="B52" s="20" t="inlineStr">
-        <is>
-          <t>Faz 3</t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/destek/dijitalde-turkcellli-olmak/tik-diye-turkcellli-olmak/numara-tasima-sorgulama-formu</t>
-        </is>
-      </c>
-      <c r="D52" s="14" t="inlineStr">
-        <is>
-          <t>Yeni Hat Başvurusu Sorgulama</t>
-        </is>
-      </c>
-      <c r="E52" s="14" t="inlineStr">
-        <is>
-          <t>• Formun ne işe yaradığını ve sonucun nasıl okunacağını anlatan açıklama metninin eklenmesi
-• Yeni 'Numara kime ait' sayfasına bağlantı verilmesi</t>
-        </is>
-      </c>
-      <c r="F52" s="11" t="inlineStr">
-        <is>
-          <t>İçerik</t>
-        </is>
-      </c>
-      <c r="G52" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numara-tasima-sorgulama-formu</t>
-        </is>
-      </c>
-      <c r="H52" s="19" t="n">
-        <v>76149</v>
-      </c>
-      <c r="I52" s="19" t="n">
-        <v>3124</v>
-      </c>
-      <c r="J52" s="11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="K52" s="14" t="inlineStr">
-        <is>
-          <t>numara sorgulama · turkcell numara taşıma sorgulama · operatör sorgulama</t>
-        </is>
-      </c>
-      <c r="L52" s="14" t="inlineStr">
-        <is>
-          <t>Form sayfasında metin içeriği bulunmuyor; 'numara sorgulama' ve 'operatör sorgulama' gibi farklı niyetteki sorgular bu sayfaya düşüyor. Aynı başlık numara taşıma bölümünde ikinci adreste yayınlanıyor.</t>
-        </is>
-      </c>
-      <c r="M52" s="14" t="inlineStr">
-        <is>
-          <t>Formun ne işe yaradığını ve sonucun nasıl okunacağını anlatan kısa bir açıklama metni eklenmesi, farklı niyetteki numara sorgulamaları için yeni 'Numara kime ait' sayfasına bağlantı verilmesi önerilir.</t>
-        </is>
-      </c>
-      <c r="N52" s="14" t="inlineStr">
-        <is>
-          <t>Yeni hat ve numara taşıma başvurusunun durumu nasıl sorgulanır?</t>
-        </is>
-      </c>
-      <c r="O52" s="14" t="inlineStr">
-        <is>
-          <t>Search Console 3 ay konum analizi</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="n">
-        <v>49</v>
-      </c>
-      <c r="B53" s="20" t="inlineStr">
-        <is>
-          <t>Faz 3</t>
-        </is>
-      </c>
-      <c r="C53" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/destek/yardim-araclari/yardim-araclari/bireysel-hat-sorgulama</t>
-        </is>
-      </c>
-      <c r="D53" s="14" t="inlineStr">
-        <is>
-          <t>Bireysel Hat Sorgulama</t>
-        </is>
-      </c>
-      <c r="E53" s="14" t="inlineStr">
-        <is>
-          <t>• Bir kişi adına kayıtlı olabilecek azami hat sayısının belirtilmesi
-• Sınır aşımında yapılacakların alt başlıkla eklenmesi</t>
-        </is>
-      </c>
-      <c r="F53" s="11" t="inlineStr">
-        <is>
-          <t>İçerik</t>
-        </is>
-      </c>
-      <c r="G53" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="19" t="n">
-        <v>68238</v>
-      </c>
-      <c r="I53" s="19" t="n">
-        <v>7083</v>
-      </c>
-      <c r="J53" s="11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K53" s="14" t="inlineStr">
-        <is>
-          <t>mobil hat sorgulama · hat sorgulama · tc ile hat sorgulama</t>
-        </is>
-      </c>
-      <c r="L53" s="14" t="inlineStr">
-        <is>
-          <t>152 kelime; BTK SMS'i, e-Devlet mobil hat sorgulama ve bilgi dışında açılan hat için mağaza yönlendirmesi var; yasal hat sayısı sınırı yok.</t>
-        </is>
-      </c>
-      <c r="M53" s="14" t="inlineStr">
-        <is>
-          <t>Hat sayısı sınırı ve sınır aşımında yapılacaklar için kısa bir alt başlık eklenmesi önerilir (resmi kurum kaynağı ve marka doğrulamasıyla).</t>
-        </is>
-      </c>
-      <c r="N53" s="14" t="inlineStr">
-        <is>
-          <t>Bir kişinin adına en fazla kaç mobil hat kayıtlı olabilir?</t>
-        </is>
-      </c>
-      <c r="O53" s="14" t="inlineStr">
-        <is>
-          <t>Rakip destek karşılaştırması</t>
         </is>
       </c>
     </row>
@@ -11640,18 +11758,18 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/hattiniz/faturali/faturami-nasil-odeyebilirim</t>
+          <t>https://www.turkcell.com.tr/destek/dijitalde-turkcellli-olmak/tik-diye-turkcellli-olmak/numara-tasima-sorgulama-formu</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>Faturamı nasıl ödeyebilirim?</t>
+          <t>Yeni Hat Başvurusu Sorgulama</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>• Ödeme kanallarının ara başlıklarla ayrıştırılması
-• Hizmet numaralarının metin içinde yer alması</t>
+          <t>• Formun ne işe yaradığını ve sonucun nasıl okunacağını anlatan açıklama metninin eklenmesi
+• Yeni 'Numara kime ait' sayfasına bağlantı verilmesi</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr">
@@ -11661,36 +11779,36 @@
       </c>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numara-tasima-sorgulama-formu</t>
         </is>
       </c>
       <c r="H54" s="19" t="n">
-        <v>47477</v>
+        <v>76149</v>
       </c>
       <c r="I54" s="19" t="n">
-        <v>3789</v>
+        <v>3124</v>
       </c>
       <c r="J54" s="11" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="K54" s="14" t="inlineStr">
         <is>
-          <t>turkcell fatura ödeme · 444 0666 hangi banka · turkcell</t>
+          <t>numara sorgulama · turkcell numara taşıma sorgulama · operatör sorgulama</t>
         </is>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>Sayfa 9 civarında konumda; gelen sorguların bir bölümü ödeme hattı numaraları.</t>
+          <t>Form sayfasında metin içeriği bulunmuyor; 'numara sorgulama' ve 'operatör sorgulama' gibi farklı niyetteki sorgular bu sayfaya düşüyor. Aynı başlık numara taşıma bölümünde ikinci adreste yayınlanıyor.</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>Ödeme kanallarının ara başlıklarla ayrıştırılması ve hizmet numaralarının metin içinde yer alması önerilir.</t>
+          <t>Formun ne işe yaradığını ve sonucun nasıl okunacağını anlatan kısa bir açıklama metni eklenmesi, farklı niyetteki numara sorgulamaları için yeni 'Numara kime ait' sayfasına bağlantı verilmesi önerilir.</t>
         </is>
       </c>
       <c r="N54" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Yeni hat ve numara taşıma başvurusunun durumu nasıl sorgulanır?</t>
         </is>
       </c>
       <c r="O54" s="14" t="inlineStr">
@@ -11710,18 +11828,18 @@
       </c>
       <c r="C55" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcell-faturali-dunyasina-hos-geldiniz/asim-cozumu-nedir</t>
+          <t>https://www.turkcell.com.tr/destek/yardim-araclari/yardim-araclari/bireysel-hat-sorgulama</t>
         </is>
       </c>
       <c r="D55" s="14" t="inlineStr">
         <is>
-          <t>Aşım Çözümü nedir?</t>
+          <t>Bireysel Hat Sorgulama</t>
         </is>
       </c>
       <c r="E55" s="14" t="inlineStr">
         <is>
-          <t>• Aşım Çözümü ile Akıllı Fatura ilişkisini anlatan kısa notun eklenmesi
-• Yeni 'Paket aşımı nedir, nasıl kapatılır?' sayfasına iç link eklenmesi</t>
+          <t>• Bir kişi adına kayıtlı olabilecek azami hat sayısının belirtilmesi
+• Sınır aşımında yapılacakların alt başlıkla eklenmesi</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
@@ -11735,37 +11853,37 @@
         </is>
       </c>
       <c r="H55" s="19" t="n">
-        <v>36989</v>
+        <v>68238</v>
       </c>
       <c r="I55" s="19" t="n">
-        <v>2372</v>
+        <v>7083</v>
       </c>
       <c r="J55" s="11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K55" s="14" t="inlineStr">
         <is>
-          <t>data asim nedir · turkcell aşım kapatma · aşım kapatma</t>
+          <t>mobil hat sorgulama · hat sorgulama · tc ile hat sorgulama</t>
         </is>
       </c>
       <c r="L55" s="14" t="inlineStr">
         <is>
-          <t>18 kelime; Aşım Çözümü'nün paket bitince kullanımın devam etmesini sağladığını anlatıyor. 'internet aşım kapatma' sorguları bu sayfaya düşüyor ancak kapatma yolu yok.</t>
+          <t>152 kelime; BTK SMS'i, e-Devlet mobil hat sorgulama ve bilgi dışında açılan hat için mağaza yönlendirmesi var; yasal hat sayısı sınırı yok.</t>
         </is>
       </c>
       <c r="M55" s="14" t="inlineStr">
         <is>
-          <t>Sayfaya aşımın kapatılmasının Akıllı Fatura ile ilişkisini anlatan kısa bir not ve yeni 'Paket aşımı nedir, nasıl kapatılır?' sayfasına iç link eklenmesi önerilir.</t>
+          <t>Hat sayısı sınırı ve sınır aşımında yapılacaklar için kısa bir alt başlık eklenmesi önerilir (resmi kurum kaynağı ve marka doğrulamasıyla).</t>
         </is>
       </c>
       <c r="N55" s="14" t="inlineStr">
         <is>
-          <t>Aşım Çözümü ile Akıllı Fatura arasındaki fark nedir?</t>
+          <t>Bir kişinin adına en fazla kaç mobil hat kayıtlı olabilir?</t>
         </is>
       </c>
       <c r="O55" s="14" t="inlineStr">
         <is>
-          <t>Search Console 12 ay</t>
+          <t>Rakip destek karşılaştırması</t>
         </is>
       </c>
     </row>
@@ -11780,86 +11898,226 @@
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
+          <t>https://www.turkcell.com.tr/destek/hattiniz/faturali/faturami-nasil-odeyebilirim</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>Faturamı nasıl ödeyebilirim?</t>
+        </is>
+      </c>
+      <c r="E56" s="14" t="inlineStr">
+        <is>
+          <t>• Ödeme kanallarının ara başlıklarla ayrıştırılması
+• Hizmet numaralarının metin içinde yer alması</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr">
+        <is>
+          <t>İçerik</t>
+        </is>
+      </c>
+      <c r="G56" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H56" s="19" t="n">
+        <v>47477</v>
+      </c>
+      <c r="I56" s="19" t="n">
+        <v>3789</v>
+      </c>
+      <c r="J56" s="11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K56" s="14" t="inlineStr">
+        <is>
+          <t>turkcell fatura ödeme · 444 0666 hangi banka · turkcell</t>
+        </is>
+      </c>
+      <c r="L56" s="14" t="inlineStr">
+        <is>
+          <t>Sayfa 9 civarında konumda; gelen sorguların bir bölümü ödeme hattı numaraları.</t>
+        </is>
+      </c>
+      <c r="M56" s="14" t="inlineStr">
+        <is>
+          <t>Ödeme kanallarının ara başlıklarla ayrıştırılması ve hizmet numaralarının metin içinde yer alması önerilir.</t>
+        </is>
+      </c>
+      <c r="N56" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O56" s="14" t="inlineStr">
+        <is>
+          <t>Search Console 3 ay konum analizi</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="20" t="inlineStr">
+        <is>
+          <t>Faz 3</t>
+        </is>
+      </c>
+      <c r="C57" s="14" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcell-faturali-dunyasina-hos-geldiniz/asim-cozumu-nedir</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>Aşım Çözümü nedir?</t>
+        </is>
+      </c>
+      <c r="E57" s="14" t="inlineStr">
+        <is>
+          <t>• Aşım Çözümü ile Akıllı Fatura ilişkisini anlatan kısa notun eklenmesi
+• Yeni 'Paket aşımı nedir, nasıl kapatılır?' sayfasına iç link eklenmesi</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr">
+        <is>
+          <t>İçerik</t>
+        </is>
+      </c>
+      <c r="G57" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="19" t="n">
+        <v>36989</v>
+      </c>
+      <c r="I57" s="19" t="n">
+        <v>2372</v>
+      </c>
+      <c r="J57" s="11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K57" s="14" t="inlineStr">
+        <is>
+          <t>data asim nedir · turkcell aşım kapatma · aşım kapatma</t>
+        </is>
+      </c>
+      <c r="L57" s="14" t="inlineStr">
+        <is>
+          <t>18 kelime; Aşım Çözümü'nün paket bitince kullanımın devam etmesini sağladığını anlatıyor. 'internet aşım kapatma' sorguları bu sayfaya düşüyor ancak kapatma yolu yok.</t>
+        </is>
+      </c>
+      <c r="M57" s="14" t="inlineStr">
+        <is>
+          <t>Sayfaya aşımın kapatılmasının Akıllı Fatura ile ilişkisini anlatan kısa bir not ve yeni 'Paket aşımı nedir, nasıl kapatılır?' sayfasına iç link eklenmesi önerilir.</t>
+        </is>
+      </c>
+      <c r="N57" s="14" t="inlineStr">
+        <is>
+          <t>Aşım Çözümü ile Akıllı Fatura arasındaki fark nedir?</t>
+        </is>
+      </c>
+      <c r="O57" s="14" t="inlineStr">
+        <is>
+          <t>Search Console 12 ay</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="20" t="inlineStr">
+        <is>
+          <t>Faz 3</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr">
+        <is>
           <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numarami-tasirken-hattim-kullanima-kapanir-mi</t>
         </is>
       </c>
-      <c r="D56" s="14" t="inlineStr">
+      <c r="D58" s="14" t="inlineStr">
         <is>
           <t>Numaramı taşırken hattım kullanıma kapanır mı?</t>
         </is>
       </c>
-      <c r="E56" s="14" t="inlineStr">
+      <c r="E58" s="14" t="inlineStr">
         <is>
           <t>• 'Taşıma sonrası şebeke gelmiyorsa ne yapılabilir?' bölümünün eklenmesi
 • SIM kart değişimi kontrolü ve cihazın yeniden başlatılması adımlarının sıralanması
 • Şebeke seçiminin otomatiğe alınması ve e-Devlet numara taşıma sorgusunun eklenmesi</t>
         </is>
       </c>
-      <c r="F56" s="11" t="inlineStr">
+      <c r="F58" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="19" t="n">
+      <c r="G58" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H58" s="19" t="n">
         <v>23444</v>
       </c>
-      <c r="I56" s="19" t="n">
+      <c r="I58" s="19" t="n">
         <v>597</v>
       </c>
-      <c r="J56" s="11" t="n">
+      <c r="J58" s="11" t="n">
         <v>7.8</v>
       </c>
-      <c r="K56" s="14" t="inlineStr">
+      <c r="K58" s="14" t="inlineStr">
         <is>
           <t>turkcell numara taşıma · numara taşımada eski hat ne zaman kapanır · turkcell hat taşıma</t>
         </is>
       </c>
-      <c r="L56" s="14" t="inlineStr">
+      <c r="L58" s="14" t="inlineStr">
         <is>
           <t>Sayfa geçişte yaklaşık 15 dakikalık kesintiyi ve SIM değişimini anlatıyor; taşıma sonrası şebeke görünmediğinde yapılacak kontroller yok.</t>
         </is>
       </c>
-      <c r="M56" s="14" t="inlineStr">
+      <c r="M58" s="14" t="inlineStr">
         <is>
           <t>Sayfaya 'Taşıma sonrası şebeke gelmiyorsa ne yapılabilir?' bölümünün eklenmesi önerilir (SIM kartın değiştirildiğinin kontrolü, cihazın yeniden başlatılması, şebeke seçiminin otomatiğe alınması, e-Devlet numara taşıma sorgusu).</t>
         </is>
       </c>
-      <c r="N56" s="14" t="inlineStr">
+      <c r="N58" s="14" t="inlineStr">
         <is>
           <t>Numara taşıma sonrası şebeke gelmiyorsa ne yapılabilir?</t>
         </is>
       </c>
-      <c r="O56" s="14" t="inlineStr">
+      <c r="O58" s="14" t="inlineStr">
         <is>
           <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="20" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="20" t="inlineStr">
         <is>
           <t>Faz 3</t>
         </is>
       </c>
-      <c r="C57" s="14" t="inlineStr">
+      <c r="C59" s="14" t="inlineStr">
         <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/faturali/fatura-kesim-tarihimi-nasil-degistirebilirim</t>
         </is>
       </c>
-      <c r="D57" s="14" t="inlineStr">
+      <c r="D59" s="14" t="inlineStr">
         <is>
           <t>Fatura kesim tarihimi nasıl değiştirebilirim?</t>
         </is>
       </c>
-      <c r="E57" s="14" t="inlineStr">
+      <c r="E59" s="14" t="inlineStr">
         <is>
           <t>• Sayfanın başına fatura kesim tarihi tanımının eklenmesi
 • Kesim tarihi ile son ödeme tarihi farkının açıklanması
@@ -11867,185 +12125,44 @@
 • Son ödeme tarihi sayfasına iç link verilmesi</t>
         </is>
       </c>
-      <c r="F57" s="11" t="inlineStr">
+      <c r="F59" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="19" t="n">
+      <c r="G59" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H59" s="19" t="n">
         <v>12913</v>
       </c>
-      <c r="I57" s="19" t="n">
+      <c r="I59" s="19" t="n">
         <v>994</v>
       </c>
-      <c r="J57" s="11" t="n">
+      <c r="J59" s="11" t="n">
         <v>4.6</v>
       </c>
-      <c r="K57" s="14" t="inlineStr">
+      <c r="K59" s="14" t="inlineStr">
         <is>
           <t>turkcell fatura son ödeme tarihi geçerse ne zaman kapanır · fatura kesim tarihi ne demek · turkcell fatura kesim tarihi değiştirme</t>
         </is>
       </c>
-      <c r="L57" s="14" t="inlineStr">
+      <c r="L59" s="14" t="inlineStr">
         <is>
           <t>Sayfa kesim tarihinin 10, 20 ya da 25 olarak değiştirilmesini anlatıyor; 'fatura kesim tarihi nedir' tanım sorgusu bu sayfaya 3,7-4,1 konumla düşüyor. Son ödeme tarihi ayrı sayfada.</t>
         </is>
       </c>
-      <c r="M57" s="14" t="inlineStr">
+      <c r="M59" s="14" t="inlineStr">
         <is>
           <t>Sayfanın başına fatura kesim tarihi ve son ödeme tarihi tanımının eklenmesi ve son ödeme tarihi sayfasına iç link verilmesi önerilir.</t>
         </is>
       </c>
-      <c r="N57" s="14" t="inlineStr">
+      <c r="N59" s="14" t="inlineStr">
         <is>
           <t>Fatura kesim tarihi nedir, son ödeme tarihinden farkı nedir?
 Fatura kesim tarihi nereden öğrenilir?</t>
-        </is>
-      </c>
-      <c r="O57" s="14" t="inlineStr">
-        <is>
-          <t>Arama talebi ve SERP analizi</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="20" t="inlineStr">
-        <is>
-          <t>Faz 3</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/turkcell-tvye-nasil-giris-yaparim</t>
-        </is>
-      </c>
-      <c r="D58" s="14" t="inlineStr">
-        <is>
-          <t>TV+ uygulamasına nasıl giriş yapılır?</t>
-        </is>
-      </c>
-      <c r="E58" s="14" t="inlineStr">
-        <is>
-          <t>• Giriş adımlarının cihaz kırılımıyla (mobil uygulama, web, televizyon) verilmesi
-• Şifre alma sayfasına iç link eklenmesi</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>İçerik</t>
-        </is>
-      </c>
-      <c r="G58" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="19" t="n">
-        <v>11396</v>
-      </c>
-      <c r="I58" s="19" t="n">
-        <v>346</v>
-      </c>
-      <c r="J58" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="K58" s="14" t="inlineStr">
-        <is>
-          <t>turkcell tv · turkcell tv plus televizyona nasıl bağlanır · tv plus televizyona nasıl bağlanır</t>
-        </is>
-      </c>
-      <c r="L58" s="14" t="inlineStr">
-        <is>
-          <t>17 kelime; 'tv plus giriş' talebinde konum 7 civarında. Televizyona bağlama ve şifre sıfırlama adımı yok.</t>
-        </is>
-      </c>
-      <c r="M58" s="14" t="inlineStr">
-        <is>
-          <t>Giriş adımlarının cihaz kırılımıyla (mobil uygulama, web, televizyon) verilmesi ve şifre adımı sayfasına iç link eklenmesi önerilir (marka doğrulamasıyla).</t>
-        </is>
-      </c>
-      <c r="N58" s="14" t="inlineStr">
-        <is>
-          <t>TV+ televizyona nasıl bağlanır?
-TV+ şifresi nasıl alınır?</t>
-        </is>
-      </c>
-      <c r="O58" s="14" t="inlineStr">
-        <is>
-          <t>Search Console 3 ay konum analizi · Search Console 12 ay</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="11" t="n">
-        <v>55</v>
-      </c>
-      <c r="B59" s="20" t="inlineStr">
-        <is>
-          <t>Faz 3</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/paket-ve-tarife-satisi/avantajli-yurt-disinda-kullanim-paketlerine-nereden-ulasabilirim</t>
-        </is>
-      </c>
-      <c r="D59" s="14" t="inlineStr">
-        <is>
-          <t>Avantajlı yurt dışında kullanım paketlerine nereden ulaşabilirim?</t>
-        </is>
-      </c>
-      <c r="E59" s="14" t="inlineStr">
-        <is>
-          <t>• Satın alma adımlarının güncel menü adlarıyla yeniden yazılması
-• Başlığın 'Yurt dışı internet paketi nasıl alınır?' sorusunu kapsayacak şekilde güncellenmesi</t>
-        </is>
-      </c>
-      <c r="F59" s="11" t="inlineStr">
-        <is>
-          <t>İçerik</t>
-        </is>
-      </c>
-      <c r="G59" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" s="19" t="n">
-        <v>3844</v>
-      </c>
-      <c r="I59" s="19" t="n">
-        <v>177</v>
-      </c>
-      <c r="J59" s="11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="K59" s="14" t="inlineStr">
-        <is>
-          <t>turkcell yurtdışı paketleri · turkcell yurtdışı kullanım · turkcell yurt dışı paketleri</t>
-        </is>
-      </c>
-      <c r="L59" s="14" t="inlineStr">
-        <is>
-          <t>Sayfa hat tipi ve ülke seçilerek paket satın alma adımlarını anlatıyor; menü adları eski ('Ürün ve Hizmetler').</t>
-        </is>
-      </c>
-      <c r="M59" s="14" t="inlineStr">
-        <is>
-          <t>Satın alma adımlarının güncel menü adlarıyla yeniden yazılması ve başlığın 'Yurt dışı internet paketi nasıl alınır?' sorusunu kapsayacak şekilde güncellenmesi önerilir.</t>
-        </is>
-      </c>
-      <c r="N59" s="14" t="inlineStr">
-        <is>
-          <t>Yurt dışı internet paketi nasıl alınır?</t>
         </is>
       </c>
       <c r="O59" s="14" t="inlineStr">
@@ -12065,18 +12182,18 @@
       </c>
       <c r="C60" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcellli-olmak/yabanci-uyrukluyum-nasil-hat-alabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/turkcell-tvye-nasil-giris-yaparim</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>Yabancı uyrukluyum, nasıl hat alabilirim?</t>
+          <t>TV+ uygulamasına nasıl giriş yapılır?</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>• Faturalı hat koşullarının alt başlıkla eklenmesi
-• Kalıcı kimlik güncelleme kuralının eklenmesi</t>
+          <t>• Giriş adımlarının cihaz kırılımıyla (mobil uygulama, web, televizyon) verilmesi
+• Şifre alma sayfasına iç link eklenmesi</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr">
@@ -12086,42 +12203,42 @@
       </c>
       <c r="G60" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/kampanya/kampanyalar-faturali/yabanci-uyrukluyum-nasil-hat-alabilirim</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" s="19" t="n">
-        <v>1466</v>
+        <v>11396</v>
       </c>
       <c r="I60" s="19" t="n">
-        <v>635</v>
+        <v>346</v>
       </c>
       <c r="J60" s="11" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="K60" s="14" t="inlineStr">
         <is>
-          <t>turkcell yabancı uyruklu faturalı hat · yabancılar faturalı hat alabilir mi · yabancılar sim kart alabilir mi</t>
+          <t>turkcell tv · turkcell tv plus televizyona nasıl bağlanır · tv plus televizyona nasıl bağlanır</t>
         </is>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>45 kelime; yalnızca Hazır Kart için kabul edilen belgeler. Kimlik güncelleme ve faturalı hat sorguları karşılanmıyor. Aynı başlık kampanya bölümünde ikinci adreste yayınlanıyor.</t>
+          <t>17 kelime; 'tv plus giriş' talebinde konum 7 civarında. Televizyona bağlama ve şifre sıfırlama adımı yok.</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>Faturalı hat koşulları ve kalıcı kimlik güncelleme kuralı için alt başlık eklenmesi önerilir; dönemsel doğrulama duyuruları için ayrı sayfa açılmasına gerek görülmemiştir.</t>
+          <t>Giriş adımlarının cihaz kırılımıyla (mobil uygulama, web, televizyon) verilmesi ve şifre adımı sayfasına iç link eklenmesi önerilir (marka doğrulamasıyla).</t>
         </is>
       </c>
       <c r="N60" s="14" t="inlineStr">
         <is>
-          <t>Yabancı uyruklu aboneler faturalı hat alabilir mi?
-Yabancı uyruklu aboneler kimlik bilgilerini nasıl günceller?</t>
+          <t>TV+ televizyona nasıl bağlanır?
+TV+ şifresi nasıl alınır?</t>
         </is>
       </c>
       <c r="O60" s="14" t="inlineStr">
         <is>
-          <t>Rakip destek karşılaştırması</t>
+          <t>Search Console 3 ay konum analizi · Search Console 12 ay</t>
         </is>
       </c>
     </row>
@@ -12136,18 +12253,18 @@
       </c>
       <c r="C61" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/paket-dakikalarimi-bitirdigimde-yeni-bir-paket-alabilir-miyim</t>
+          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/paket-ve-tarife-satisi/avantajli-yurt-disinda-kullanim-paketlerine-nereden-ulasabilirim</t>
         </is>
       </c>
       <c r="D61" s="14" t="inlineStr">
         <is>
-          <t>Paket dakikalarımı bitirdiğimde yeni bir paket alabilir miyim?</t>
+          <t>Avantajlı yurt dışında kullanım paketlerine nereden ulaşabilirim?</t>
         </is>
       </c>
       <c r="E61" s="14" t="inlineStr">
         <is>
-          <t>• 'Birden fazla ek paket varsa hangisi önce kullanılır?' sorusunun eklenmesi
-• 'Kullanılmayan ek paket hakları sonraki aya devreder mi?' sorusunun eklenmesi</t>
+          <t>• Satın alma adımlarının güncel menü adlarıyla yeniden yazılması
+• Başlığın 'Yurt dışı internet paketi nasıl alınır?' sorusunu kapsayacak şekilde güncellenmesi</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -12161,38 +12278,37 @@
         </is>
       </c>
       <c r="H61" s="19" t="n">
-        <v>808</v>
+        <v>3844</v>
       </c>
       <c r="I61" s="19" t="n">
-        <v>102</v>
+        <v>177</v>
       </c>
       <c r="J61" s="11" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="K61" s="14" t="inlineStr">
         <is>
-          <t>turkcell paket yükleme · paket bitmeden paket yapılır mı turkcell · turkcell paket yükleme online</t>
+          <t>turkcell yurtdışı paketleri · turkcell yurtdışı kullanım · turkcell yurt dışı paketleri</t>
         </is>
       </c>
       <c r="L61" s="14" t="inlineStr">
         <is>
-          <t>48 kelime; yalnızca satın alma yolu. Talep düşük.</t>
+          <t>Sayfa hat tipi ve ülke seçilerek paket satın alma adımlarını anlatıyor; menü adları eski ('Ürün ve Hizmetler').</t>
         </is>
       </c>
       <c r="M61" s="14" t="inlineStr">
         <is>
-          <t>Yeni sayfa yerine mevcut sayfaya 2-3 kısa soru eklenmesi yeterli görülmüştür (içerik marka doğrulamasıyla).</t>
+          <t>Satın alma adımlarının güncel menü adlarıyla yeniden yazılması ve başlığın 'Yurt dışı internet paketi nasıl alınır?' sorusunu kapsayacak şekilde güncellenmesi önerilir.</t>
         </is>
       </c>
       <c r="N61" s="14" t="inlineStr">
         <is>
-          <t>Birden fazla ek paket varsa hangisi önce kullanılır?
-Kullanılmayan ek paket hakları sonraki aya devreder mi?</t>
+          <t>Yurt dışı internet paketi nasıl alınır?</t>
         </is>
       </c>
       <c r="O61" s="14" t="inlineStr">
         <is>
-          <t>Rakip destek karşılaştırması</t>
+          <t>Arama talebi ve SERP analizi</t>
         </is>
       </c>
     </row>
@@ -12207,68 +12323,210 @@
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
+          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcellli-olmak/yabanci-uyrukluyum-nasil-hat-alabilirim</t>
+        </is>
+      </c>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>Yabancı uyrukluyum, nasıl hat alabilirim?</t>
+        </is>
+      </c>
+      <c r="E62" s="14" t="inlineStr">
+        <is>
+          <t>• Faturalı hat koşullarının alt başlıkla eklenmesi
+• Kalıcı kimlik güncelleme kuralının eklenmesi</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr">
+        <is>
+          <t>İçerik</t>
+        </is>
+      </c>
+      <c r="G62" s="14" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/destek/kampanya/kampanyalar-faturali/yabanci-uyrukluyum-nasil-hat-alabilirim</t>
+        </is>
+      </c>
+      <c r="H62" s="19" t="n">
+        <v>1466</v>
+      </c>
+      <c r="I62" s="19" t="n">
+        <v>635</v>
+      </c>
+      <c r="J62" s="11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="K62" s="14" t="inlineStr">
+        <is>
+          <t>turkcell yabancı uyruklu faturalı hat · yabancılar faturalı hat alabilir mi · yabancılar sim kart alabilir mi</t>
+        </is>
+      </c>
+      <c r="L62" s="14" t="inlineStr">
+        <is>
+          <t>45 kelime; yalnızca Hazır Kart için kabul edilen belgeler. Kimlik güncelleme ve faturalı hat sorguları karşılanmıyor. Aynı başlık kampanya bölümünde ikinci adreste yayınlanıyor.</t>
+        </is>
+      </c>
+      <c r="M62" s="14" t="inlineStr">
+        <is>
+          <t>Faturalı hat koşulları ve kalıcı kimlik güncelleme kuralı için alt başlık eklenmesi önerilir; dönemsel doğrulama duyuruları için ayrı sayfa açılmasına gerek görülmemiştir.</t>
+        </is>
+      </c>
+      <c r="N62" s="14" t="inlineStr">
+        <is>
+          <t>Yabancı uyruklu aboneler faturalı hat alabilir mi?
+Yabancı uyruklu aboneler kimlik bilgilerini nasıl günceller?</t>
+        </is>
+      </c>
+      <c r="O62" s="14" t="inlineStr">
+        <is>
+          <t>Rakip destek karşılaştırması</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="20" t="inlineStr">
+        <is>
+          <t>Faz 3</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="inlineStr">
+        <is>
+          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/paket-dakikalarimi-bitirdigimde-yeni-bir-paket-alabilir-miyim</t>
+        </is>
+      </c>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>Paket dakikalarımı bitirdiğimde yeni bir paket alabilir miyim?</t>
+        </is>
+      </c>
+      <c r="E63" s="14" t="inlineStr">
+        <is>
+          <t>• 'Birden fazla ek paket varsa hangisi önce kullanılır?' sorusunun eklenmesi
+• 'Kullanılmayan ek paket hakları sonraki aya devreder mi?' sorusunun eklenmesi</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr">
+        <is>
+          <t>İçerik</t>
+        </is>
+      </c>
+      <c r="G63" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" s="19" t="n">
+        <v>808</v>
+      </c>
+      <c r="I63" s="19" t="n">
+        <v>102</v>
+      </c>
+      <c r="J63" s="11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="K63" s="14" t="inlineStr">
+        <is>
+          <t>turkcell paket yükleme · paket bitmeden paket yapılır mı turkcell · turkcell paket yükleme online</t>
+        </is>
+      </c>
+      <c r="L63" s="14" t="inlineStr">
+        <is>
+          <t>48 kelime; yalnızca satın alma yolu. Talep düşük.</t>
+        </is>
+      </c>
+      <c r="M63" s="14" t="inlineStr">
+        <is>
+          <t>Yeni sayfa yerine mevcut sayfaya 2-3 kısa soru eklenmesi yeterli görülmüştür (içerik marka doğrulamasıyla).</t>
+        </is>
+      </c>
+      <c r="N63" s="14" t="inlineStr">
+        <is>
+          <t>Birden fazla ek paket varsa hangisi önce kullanılır?
+Kullanılmayan ek paket hakları sonraki aya devreder mi?</t>
+        </is>
+      </c>
+      <c r="O63" s="14" t="inlineStr">
+        <is>
+          <t>Rakip destek karşılaştırması</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="20" t="inlineStr">
+        <is>
+          <t>Faz 3</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
           <t>https://www.turkcell.com.tr/destek/hattiniz/faturali/faturamdaki-kalemler-nelerdir</t>
         </is>
       </c>
-      <c r="D62" s="14" t="inlineStr">
+      <c r="D64" s="14" t="inlineStr">
         <is>
           <t>Faturamdaki kalemler nelerdir?</t>
         </is>
       </c>
-      <c r="E62" s="14" t="inlineStr">
+      <c r="E64" s="14" t="inlineStr">
         <is>
           <t>• 'Mobil ödeme kullanım bedeli' kaleminin tanımının eklenmesi
 • 'Dijital servis ücreti' kaleminin tanımının eklenmesi</t>
         </is>
       </c>
-      <c r="F62" s="11" t="inlineStr">
+      <c r="F64" s="11" t="inlineStr">
         <is>
           <t>İçerik</t>
         </is>
       </c>
-      <c r="G62" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" s="19" t="n">
+      <c r="G64" s="14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" s="19" t="n">
         <v>503</v>
       </c>
-      <c r="I62" s="19" t="n">
+      <c r="I64" s="19" t="n">
         <v>51</v>
       </c>
-      <c r="J62" s="11" t="n">
+      <c r="J64" s="11" t="n">
         <v>2.4</v>
       </c>
-      <c r="K62" s="14" t="inlineStr">
+      <c r="K64" s="14" t="inlineStr">
         <is>
           <t>tahsilatına aracılık edilen hizmetler nedir · yuvarlama farkı nedir · tohas pf nedir</t>
         </is>
       </c>
-      <c r="L62" s="14" t="inlineStr">
+      <c r="L64" s="14" t="inlineStr">
         <is>
           <t>Fatura kalemi sorguları ('mobil ödeme kullanım bedeli', 'dijital servis ücreti') Financell aidat sayfasına ve servis listesine düşüyor; kalem tanımı yok.</t>
         </is>
       </c>
-      <c r="M62" s="14" t="inlineStr">
+      <c r="M64" s="14" t="inlineStr">
         <is>
           <t>Fatura kalemleri sayfasına iki kalem için tanım eklenmesi önerilir; tanımlar için marka doğrulaması gerekir.</t>
         </is>
       </c>
-      <c r="N62" s="14" t="inlineStr">
+      <c r="N64" s="14" t="inlineStr">
         <is>
           <t>Faturadaki 'mobil ödeme kullanım bedeli' nedir?
 Faturadaki 'dijital servis ücreti' nedir?</t>
         </is>
       </c>
-      <c r="O62" s="14" t="inlineStr">
+      <c r="O64" s="14" t="inlineStr">
         <is>
           <t>Search Console 12 ay</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:O62"/>
+  <autoFilter ref="A4:O64"/>
   <mergeCells count="1">
     <mergeCell ref="A2:O2"/>
   </mergeCells>

--- a/Turkcell-Destek-Sayfa-Onerileri-22-09-2026.xlsx
+++ b/Turkcell-Destek-Sayfa-Onerileri-22-09-2026.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Talepler'!$A$4:$I$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Yeni Sayfa Önerileri'!$A$4:$U$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Mevcut Sayfa Güçlendirme'!$A$4:$O$64</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sitemap Dışı Adresler'!$A$4:$L$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sitemap Dışı Adresler'!$A$4:$L$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Doğrulanacak Bilgiler'!$A$4:$G$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Duplicate Adresler'!$A$4:$G$129</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Rakip Karşılaştırması'!$A$4:$K$79</definedName>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Geçerli bir kategori ve alt bölüm altında yayında olmayan bir soru adresi istendiğinde sunucu 200 status code döndürmekte, alt bölümdeki başka bir sayfanın içeriğini göstermekte, adresin kendisine canonical vermekte ve index,follow taşımaktadır (test: /destek/tarife-ve-paketler/konusma/bu-sayfa-yok-deneme-xyz, 14 Eyl 2026). Geçersiz kategori ya da alt bölüm altında adres doğru biçimde 404 dönmektedir. Search Console'da 1 Eyl 2025 - 31 Ağu 2026 penceresinde bu davranışı gösteren 28 adres görülmüştür: 24 adres başka bir sayfanın içeriğini tekrar etmekte (212.184 impression, 5.168 tıklama), 4 adres ise gerçek bir sayfanın yazım varyantı olarak kopyasını sunmaktadır (95.306 impression). Toplam 307.490 impression. Şikayet talebi oluşturma ve Pasaj satıcı sayfaları kendi içeriğini gösterdiği için bu listeye alınmamıştır.</t>
+          <t>Geçerli bir kategori ve alt bölüm altında yayında olmayan bir soru adresi istendiğinde sunucu 200 status code döndürmekte, alt bölümdeki başka bir sayfanın içeriğini göstermekte, adresin kendisine canonical vermekte ve index,follow taşımaktadır (test: /destek/tarife-ve-paketler/konusma/bu-sayfa-yok-deneme-xyz, 14 Eyl 2026). Geçersiz kategori ya da alt bölüm altında adres doğru biçimde 404 dönmektedir. Search Console'da 1 Eyl 2025 - 31 Ağu 2026 penceresinde bu davranışı gösteren 24 adres görülmüştür: 21 adres başka bir sayfanın içeriğini tekrar etmekte (209.530 impression, 5.055 tıklama), 3 adres ise gerçek bir sayfanın yazım varyantı olarak kopyasını sunmaktadır (95.299 impression). Toplam 304.829 impression. Şikayet talebi oluşturma ve Pasaj satıcı sayfaları kendi içeriğini gösterdiği için bu listeye alınmamıştır.</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="I5" s="14" t="inlineStr">
         <is>
-          <t>28 adres · 307.490 impression (Search Console, 1 Eyl 2025 - 31 Ağu 2026) + şablon kuralı</t>
+          <t>24 adres · 304.829 impression (Search Console, 1 Eyl 2025 - 31 Ağu 2026) + şablon kuralı</t>
         </is>
       </c>
     </row>
@@ -1785,22 +1785,18 @@
 /destek/servisler-ve-internet/servisler/avans-tl-nedir-nasil-abone-olurum · 4.580 impression → 410 dönmesi (Avans TL servis sayfası da kaldırılmış)
 /destek/kampanya/kampanyalar-faturali/numarami-nasil-tasiyabilirim · 4.541 impression → 301 → /turkcellli-olmak/paket-secimi
 /destek/turkcellli-olmak/turkcellli-olmak/nasil-hazirkart-alirim · 2.934 impression → 301 → /destek/turkcellli-olmak/numara-tasima/nasil-hazirkart-alirim
-/destek/turkcell-akademi/sikca-sorulan-sorular/turkcell-akademi-egitimlerine-nereden-ulasabilirim · 2.481 impression → 301 → https://tag.turkcell.com.tr/
 /destek/servisler-ve-internet/servisler/kredi-transfer-nedir · 1.268 impression → 301 → /destek/hattiniz/hazirkart/kreditransfer-nedir
 /destek/servisler-ve-internet/servisler/telefonumu-mobil-odeme-kullanimina-nasil-acabilirim · 1.227 impression → 301 → /servisler/arama-fatura-tl/yonlendir
 /destek/kampanya/kampanyalar-faturali/numarami-tasirken-hattim-kullanima-kapanir-mi · 779 impression → 301 → /destek/turkcellli-olmak/numara-tasima/numarami-tasirken-hattim-kullanima-kapanir-mi
 /destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/paket-ve-tarifelerim-sayfasindan-hangi-islemleri-yapabilirim · 382 impression → 301 → /destek/islem-merkezi
 /destek/sosyal-destek-iletisim · 257 impression → 301 → /sosyal-destek
-/destek/turkcell-akademi/sikca-sorulan-sorular/mevcut-egitimlerden-baska-egitimler-olacak-mi · 172 impression → 301 → https://tag.turkcell.com.tr/
 /destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/tl-ayarlarim-sayfasindan-hangi-ayarlari-yapabilirim · 145 impression → 404 ya da 410 dönmesi (karşılayan sayfa yok)
 /destek/islem-merkezi/ayarlarim/arayan-numarayi-goster-clip-ozelligi-nedir · 129 impression → 301 → /destek/hattiniz/sikca-sorulan-sorular/arayan-numarayi-goster-clip-ozelligi-nedir
 /destek/tarife-ve-paketler/konusma/tarifemi-nerden-ogrenebilirim-ve-nasil-degistirebilirim · 55 impression → 301 → /destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim
 /kurumsal/destek/hattiniz/faturali/hattimi-gecici-olarak- · 33 impression → 301 → /kurumsal/destek/hattiniz/faturali/hattimi-gecici-olarak-gelen-ve-gelen-giden-iletisime-ne-kadar-sureyle-kapatabilirim-ve-faturama-herhangi-bir-ucret-yansir-m
 /destek/islem-merkezi/ayarlarim/hat-iptalimi-nasil-gerceklestirebilirim · 14 impression → 301 → /destek/hattiniz/abonelik-islemleri/hattimi-nasil-iptal-ettirebilirim
 /destek/financell/ucretlendirme/financell-kredi-taksitlerim-disinda-odemem-gereken · 14 impression → 301 → /destek/financell/ucretlendirme/financell-kredi-taksitlerim-disinda-odemem-gereken-diger-ucretler-nelerdir
-/destek/financell/paycell-alisveris-limiti/online-alisverislerde-paycell-alisveris-limiti-nasil-kullanilir · 7 impression → 301 → /destek/financell/paycell-alisveris-limiti/online-alisverislerde-paycell-alisveris-limiti-nasil-kullanilir
-/destek/hizmet-kanallarimiz/musteri-hizmetleri/gencaver · 1 impression → 404 ya da 410 dönmesi
-/destek/online-alisveris · 1 impression → 301 → /destek/online-alisveris</t>
+/destek/hizmet-kanallarimiz/musteri-hizmetleri/gencaver · 1 impression → 404 ya da 410 dönmesi</t>
         </is>
       </c>
       <c r="I7" s="14" t="inlineStr">
@@ -12540,7 +12536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13857,7 +13853,7 @@
       </c>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/turkcell-akademi-egitimlerine-nereden-ulasabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/kredi-transfer-nedir</t>
         </is>
       </c>
       <c r="D26" s="11" t="n">
@@ -13865,7 +13861,7 @@
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Yönleniyor: https://www.turkcell.com.tr/destek</t>
+          <t>Kendi adresi</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -13875,28 +13871,28 @@
       </c>
       <c r="G26" s="14" t="inlineStr">
         <is>
-          <t>Turkcell Destek - Size Nasıl Yardımcı Olabiliriz?</t>
+          <t>Kredi Transfer Nedir? | Sıkça Sorulan Sorular</t>
         </is>
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Merhaba, Size Nasıl Yardımcı Olabiliriz?</t>
+          <t>Kendi numaramı nasıl gizleyebilirim?</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/kendi-numarami-nasil-gizleyebilirim</t>
         </is>
       </c>
       <c r="J26" s="19" t="n">
-        <v>2481</v>
+        <v>1268</v>
       </c>
       <c r="K26" s="19" t="n">
-        <v>108</v>
+        <v>242</v>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>301 ile Turkcell Akademi platformuna yönlendirilmesi (sorgular 'turkcell akademi'): https://tag.turkcell.com.tr/</t>
+          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/hattiniz/hazirkart/kreditransfer-nedir</t>
         </is>
       </c>
     </row>
@@ -13911,7 +13907,7 @@
       </c>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/kredi-transfer-nedir</t>
+          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/telefonumu-mobil-odeme-kullanimina-nasil-acabilirim</t>
         </is>
       </c>
       <c r="D27" s="11" t="n">
@@ -13929,7 +13925,7 @@
       </c>
       <c r="G27" s="14" t="inlineStr">
         <is>
-          <t>Kredi Transfer Nedir? | Sıkça Sorulan Sorular</t>
+          <t>Kendi numaramı nasıl gizleyebilirim?</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
@@ -13943,14 +13939,14 @@
         </is>
       </c>
       <c r="J27" s="19" t="n">
-        <v>1268</v>
+        <v>1227</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>242</v>
+        <v>12</v>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/hattiniz/hazirkart/kreditransfer-nedir</t>
+          <t>301 ile yönlendirilmesi (sorgular 'telefonu kapalı gösterme', 'açıkken ulaşılamıyor'): https://www.turkcell.com.tr/servisler/arama-fatura-tl/yonlendir</t>
         </is>
       </c>
     </row>
@@ -13965,7 +13961,7 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/telefonumu-mobil-odeme-kullanimina-nasil-acabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/kampanya/kampanyalar-faturali/numarami-tasirken-hattim-kullanima-kapanir-mi</t>
         </is>
       </c>
       <c r="D28" s="11" t="n">
@@ -13983,28 +13979,28 @@
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>Kendi numaramı nasıl gizleyebilirim?</t>
+          <t>Numaramı Taşırken Hattım Kullanıma Kapanır Mı?</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Kendi numaramı nasıl gizleyebilirim?</t>
+          <t>Numaramı taşımak ücretli midir?</t>
         </is>
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/servisler-ve-internet/servisler/kendi-numarami-nasil-gizleyebilirim</t>
+          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numarami-tasimak-ucretli-midir</t>
         </is>
       </c>
       <c r="J28" s="19" t="n">
-        <v>1227</v>
+        <v>779</v>
       </c>
       <c r="K28" s="19" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi (sorgular 'telefonu kapalı gösterme', 'açıkken ulaşılamıyor'): https://www.turkcell.com.tr/servisler/arama-fatura-tl/yonlendir</t>
+          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numarami-tasirken-hattim-kullanima-kapanir-mi</t>
         </is>
       </c>
     </row>
@@ -14019,7 +14015,7 @@
       </c>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/kampanya/kampanyalar-faturali/numarami-tasirken-hattim-kullanima-kapanir-mi</t>
+          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/paket-ve-tarifelerim-sayfasindan-hangi-islemleri-yapabilirim</t>
         </is>
       </c>
       <c r="D29" s="11" t="n">
@@ -14037,28 +14033,28 @@
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>Numaramı Taşırken Hattım Kullanıma Kapanır Mı?</t>
+          <t>Paket ve Tarifelerim Sayfasında Neler Yapabilirim?</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Numaramı taşımak ücretli midir?</t>
+          <t>Hat Özetimde hattım ile ilgili hangi bilgilere ulaşabilirim?</t>
         </is>
       </c>
       <c r="I29" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numarami-tasimak-ucretli-midir</t>
+          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/hat-ozetimde-hattim-ile-ilgili-hangi-bilgilere-ulasabilirim</t>
         </is>
       </c>
       <c r="J29" s="19" t="n">
-        <v>779</v>
+        <v>382</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/turkcellli-olmak/numara-tasima/numarami-tasirken-hattim-kullanima-kapanir-mi</t>
+          <t>301 ile yönlendirilmesi (sorgular 'turkcell online işlemler'): https://www.turkcell.com.tr/destek/islem-merkezi</t>
         </is>
       </c>
     </row>
@@ -14073,7 +14069,7 @@
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/paket-ve-tarifelerim-sayfasindan-hangi-islemleri-yapabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/sosyal-destek-iletisim</t>
         </is>
       </c>
       <c r="D30" s="11" t="n">
@@ -14091,28 +14087,28 @@
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>Paket ve Tarifelerim Sayfasında Neler Yapabilirim?</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Hat Özetimde hattım ile ilgili hangi bilgilere ulaşabilirim?</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/hat-ozetimde-hattim-ile-ilgili-hangi-bilgilere-ulasabilirim</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J30" s="19" t="n">
-        <v>382</v>
+        <v>257</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi (sorgular 'turkcell online işlemler'): https://www.turkcell.com.tr/destek/islem-merkezi</t>
+          <t>301 ile yönlendirilmesi (sorgular 'turkcell sosyal destek'): https://www.turkcell.com.tr/sosyal-destek</t>
         </is>
       </c>
     </row>
@@ -14127,7 +14123,7 @@
       </c>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/sosyal-destek-iletisim</t>
+          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/tl-ayarlarim-sayfasindan-hangi-ayarlari-yapabilirim</t>
         </is>
       </c>
       <c r="D31" s="11" t="n">
@@ -14145,28 +14141,28 @@
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TL Ayarlarım Sayfasından Neler Yapabilirim?</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Hat Özetimde hattım ile ilgili hangi bilgilere ulaşabilirim?</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/hat-ozetimde-hattim-ile-ilgili-hangi-bilgilere-ulasabilirim</t>
         </is>
       </c>
       <c r="J31" s="19" t="n">
-        <v>257</v>
+        <v>145</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi (sorgular 'turkcell sosyal destek'): https://www.turkcell.com.tr/sosyal-destek</t>
+          <t>404 ya da 410 dönmesi (karşılayan sayfa yok)</t>
         </is>
       </c>
     </row>
@@ -14176,12 +14172,12 @@
       </c>
       <c r="B32" s="22" t="inlineStr">
         <is>
-          <t>Soft 404 - tekrar eden sayfa</t>
+          <t>Soft 404 - tekrar eden sayfa · yazım varyantı</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/mevcut-egitimlerden-baska-egitimler-olacak-mi</t>
+          <t>https://www.turkcell.com.tr/destek/islem-merkezi/ayarlarim/arayan-numarayi-goster-clip-ozelligi-nedir</t>
         </is>
       </c>
       <c r="D32" s="11" t="n">
@@ -14189,38 +14185,38 @@
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>Yönleniyor: https://www.turkcell.com.tr/destek</t>
+          <t>https://www.turkcell.com.tr/destek/hattiniz/sikca-sorulan-sorular/arayan-numarayi-goster-clip-ozelligi-nedir</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>index,follow</t>
+          <t>noindex,follow</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>Turkcell Destek - Size Nasıl Yardımcı Olabiliriz?</t>
+          <t>CLIP Özelliği Nedir? | Turkcell Destek</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Merhaba, Size Nasıl Yardımcı Olabiliriz?</t>
+          <t>Arayan numarayı göster (CLIP) özelliği nedir?</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcellli-olmak/arayan-numarayi-goster-clip-ozelligi-nedir</t>
         </is>
       </c>
       <c r="J32" s="19" t="n">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="K32" s="19" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>301 ile Turkcell Akademi platformuna yönlendirilmesi (sorgular 'turkcell akademi'): https://tag.turkcell.com.tr/</t>
+          <t>Doğru adrese 301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/hattiniz/sikca-sorulan-sorular/arayan-numarayi-goster-clip-ozelligi-nedir</t>
         </is>
       </c>
     </row>
@@ -14235,7 +14231,7 @@
       </c>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/tl-ayarlarim-sayfasindan-hangi-ayarlari-yapabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nerden-ogrenebilirim-ve-nasil-degistirebilirim</t>
         </is>
       </c>
       <c r="D33" s="11" t="n">
@@ -14253,28 +14249,28 @@
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>TL Ayarlarım Sayfasından Neler Yapabilirim?</t>
+          <t>Paket / Tarife değişikliğini nasıl yapabilirim?</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Hat Özetimde hattım ile ilgili hangi bilgilere ulaşabilirim?</t>
+          <t>Paket / Tarife değişikliğini nasıl yapabilirim?</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/islem-merkezi/islem-merkezinden-yapilabilen-online-islemler/hat-ozetimde-hattim-ile-ilgili-hangi-bilgilere-ulasabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim</t>
         </is>
       </c>
       <c r="J33" s="19" t="n">
-        <v>145</v>
+        <v>55</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>404 ya da 410 dönmesi (karşılayan sayfa yok)</t>
+          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim</t>
         </is>
       </c>
     </row>
@@ -14284,12 +14280,12 @@
       </c>
       <c r="B34" s="22" t="inlineStr">
         <is>
-          <t>Soft 404 - tekrar eden sayfa · yazım varyantı</t>
+          <t>Soft 404 - tekrar eden sayfa</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/islem-merkezi/ayarlarim/arayan-numarayi-goster-clip-ozelligi-nedir</t>
+          <t>https://www.turkcell.com.tr/kurumsal/destek/hattiniz/faturali/hattimi-gecici-olarak-</t>
         </is>
       </c>
       <c r="D34" s="11" t="n">
@@ -14297,38 +14293,38 @@
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/hattiniz/sikca-sorulan-sorular/arayan-numarayi-goster-clip-ozelligi-nedir</t>
+          <t>Kendi adresi</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>noindex,follow</t>
+          <t>index,follow</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>CLIP Özelliği Nedir? | Turkcell Destek</t>
+          <t>Hattım fatura borcu nedeniyle kapanırsa, yeniden kapama/açma için bir ücret öder miyim?</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Arayan numarayı göster (CLIP) özelliği nedir?</t>
+          <t>Hattım fatura borcu nedeniyle kapanırsa, yeniden kapama/açma için bir ücret öder miyim?</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcellli-olmak/turkcellli-olmak/arayan-numarayi-goster-clip-ozelligi-nedir</t>
+          <t>https://www.turkcell.com.tr/destek/hattiniz/faturali/hattim-fatura-borcu-nedeniyle-kapanirsa-yeniden-actirmak-icin-bir-ucret-oder-miyim</t>
         </is>
       </c>
       <c r="J34" s="19" t="n">
-        <v>129</v>
+        <v>33</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>Doğru adrese 301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/hattiniz/sikca-sorulan-sorular/arayan-numarayi-goster-clip-ozelligi-nedir</t>
+          <t>Kesik adresin sayfanın tam adresine 301 ile yönlendirilmesi: https://www.turkcell.com.tr/kurumsal/destek/hattiniz/faturali/hattimi-gecici-olarak-gelen-ve-gelen-giden-iletisime-ne-kadar-sureyle-kapatabilirim-ve-faturama-herhangi-bir-ucret-yansir-m</t>
         </is>
       </c>
     </row>
@@ -14343,7 +14339,7 @@
       </c>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nerden-ogrenebilirim-ve-nasil-degistirebilirim</t>
+          <t>https://www.turkcell.com.tr/destek/islem-merkezi/ayarlarim/hat-iptalimi-nasil-gerceklestirebilirim</t>
         </is>
       </c>
       <c r="D35" s="11" t="n">
@@ -14361,28 +14357,28 @@
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>Paket / Tarife değişikliğini nasıl yapabilirim?</t>
+          <t>Profil bilgilerim nedir?</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Paket / Tarife değişikliğini nasıl yapabilirim?</t>
+          <t>Profil bilgilerim nedir?</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim</t>
+          <t>https://www.turkcell.com.tr/destek/islem-merkezi/ayarlarim/profil-bilgilerim-nedir</t>
         </is>
       </c>
       <c r="J35" s="19" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/tarife-ve-paketler/konusma/tarifemi-nasil-degistirebilirim</t>
+          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/hattimi-nasil-iptal-ettirebilirim</t>
         </is>
       </c>
     </row>
@@ -14392,12 +14388,12 @@
       </c>
       <c r="B36" s="22" t="inlineStr">
         <is>
-          <t>Soft 404 - tekrar eden sayfa</t>
+          <t>Soft 404 - tekrar eden sayfa · yazım varyantı</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/kurumsal/destek/hattiniz/faturali/hattimi-gecici-olarak-</t>
+          <t>https://www.turkcell.com.tr/destek/financell/ucretlendirme/financell-kredi-taksitlerim-disinda-odemem-gereken</t>
         </is>
       </c>
       <c r="D36" s="11" t="n">
@@ -14415,28 +14411,28 @@
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>Hattım fatura borcu nedeniyle kapanırsa, yeniden kapama/açma için bir ücret öder miyim?</t>
+          <t>Financell kredi taksitlerim dışında ödemem gereken diğer ücretler nelerdir?</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Hattım fatura borcu nedeniyle kapanırsa, yeniden kapama/açma için bir ücret öder miyim?</t>
+          <t>Financell kredi taksitlerim dışında ödemem gereken diğer ücretler nelerdir?</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/hattiniz/faturali/hattim-fatura-borcu-nedeniyle-kapanirsa-yeniden-actirmak-icin-bir-ucret-oder-miyim</t>
+          <t>https://www.turkcell.com.tr/destek/financell/ucretlendirme/financell-kredi-taksitlerim-disinda-odemem-gereken-diger-ucretler-nelerdir</t>
         </is>
       </c>
       <c r="J36" s="19" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>Kesik adresin sayfanın tam adresine 301 ile yönlendirilmesi: https://www.turkcell.com.tr/kurumsal/destek/hattiniz/faturali/hattimi-gecici-olarak-gelen-ve-gelen-giden-iletisime-ne-kadar-sureyle-kapatabilirim-ve-faturama-herhangi-bir-ucret-yansir-m</t>
+          <t>Doğru adrese 301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/financell/ucretlendirme/financell-kredi-taksitlerim-disinda-odemem-gereken-diger-ucretler-nelerdir</t>
         </is>
       </c>
     </row>
@@ -14451,7 +14447,7 @@
       </c>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/islem-merkezi/ayarlarim/hat-iptalimi-nasil-gerceklestirebilirim</t>
+          <t>https://www.turkcell.com.tr/destek/hizmet-kanallarimiz/musteri-hizmetleri/gencaver</t>
         </is>
       </c>
       <c r="D37" s="11" t="n">
@@ -14469,28 +14465,28 @@
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>Profil bilgilerim nedir?</t>
+          <t>Turkcell Hizmet</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Profil bilgilerim nedir?</t>
+          <t>Turkcell Hizmet</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/islem-merkezi/ayarlarim/profil-bilgilerim-nedir</t>
+          <t>https://www.turkcell.com.tr/destek/hizmet-kanallarimiz/musteri-hizmetleri/turkcell-hizmet</t>
         </is>
       </c>
       <c r="J37" s="19" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/hattiniz/abonelik-islemleri/hattimi-nasil-iptal-ettirebilirim</t>
+          <t>404 ya da 410 dönmesi</t>
         </is>
       </c>
     </row>
@@ -14498,53 +14494,53 @@
       <c r="A38" s="11" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="22" t="inlineStr">
-        <is>
-          <t>Soft 404 - tekrar eden sayfa · yazım varyantı</t>
+      <c r="B38" s="23" t="inlineStr">
+        <is>
+          <t>404 · kaldırılmış</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/financell/ucretlendirme/financell-kredi-taksitlerim-disinda-odemem-gereken</t>
+          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/turkcell-akademi-nedir</t>
         </is>
       </c>
       <c r="D38" s="11" t="n">
-        <v>200</v>
+        <v>404</v>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>Kendi adresi</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>index,follow</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>Financell kredi taksitlerim dışında ödemem gereken diğer ücretler nelerdir?</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Financell kredi taksitlerim dışında ödemem gereken diğer ücretler nelerdir?</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/financell/ucretlendirme/financell-kredi-taksitlerim-disinda-odemem-gereken-diger-ucretler-nelerdir</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J38" s="19" t="n">
-        <v>14</v>
+        <v>17389</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>Doğru adrese 301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/financell/ucretlendirme/financell-kredi-taksitlerim-disinda-odemem-gereken-diger-ucretler-nelerdir</t>
+          <t>İşlem gerekmiyor</t>
         </is>
       </c>
     </row>
@@ -14552,53 +14548,53 @@
       <c r="A39" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="22" t="inlineStr">
-        <is>
-          <t>Soft 404 - tekrar eden sayfa · yazım varyantı</t>
+      <c r="B39" s="23" t="inlineStr">
+        <is>
+          <t>404 · kaldırılmış</t>
         </is>
       </c>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/financell/paycell-alisveris-limiti/online-alisverislerde-paycell-alisveris-limiti-nasil-kullanilir</t>
+          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/bazi-egitimleri-izlemeye-calistigimda-hizli-giris-ile-giris-yapmam-isteniyor-neden</t>
         </is>
       </c>
       <c r="D39" s="11" t="n">
-        <v>200</v>
+        <v>404</v>
       </c>
       <c r="E39" s="14" t="inlineStr">
         <is>
-          <t>Kendi adresi</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
         <is>
-          <t>index,follow</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>Online Alışverişlerde Paycell Alışveriş Limiti Nasıl Kullanılır?</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Online alışverişlerde Paycell Alışveriş Limiti nasıl kullanılır?</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/financell/paycell-alisveris-limiti/online-alisverislerde-paycell-alisveris-limiti-nasil-kullanilir</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J39" s="19" t="n">
-        <v>7</v>
+        <v>2744</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>0</v>
+        <v>481</v>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>Doğru adrese 301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/financell/paycell-alisveris-limiti/online-alisverislerde-paycell-alisveris-limiti-nasil-kullanilir</t>
+          <t>İşlem gerekmiyor</t>
         </is>
       </c>
     </row>
@@ -14606,53 +14602,53 @@
       <c r="A40" s="11" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>Soft 404 - tekrar eden sayfa</t>
+      <c r="B40" s="23" t="inlineStr">
+        <is>
+          <t>404 · kaldırılmış</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/hizmet-kanallarimiz/musteri-hizmetleri/gencaver</t>
+          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/coursera-nedir</t>
         </is>
       </c>
       <c r="D40" s="11" t="n">
-        <v>200</v>
+        <v>404</v>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t>Kendi adresi</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>index,follow</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>Turkcell Hizmet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Turkcell Hizmet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/hizmet-kanallarimiz/musteri-hizmetleri/turkcell-hizmet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J40" s="19" t="n">
-        <v>1</v>
+        <v>1703</v>
       </c>
       <c r="K40" s="19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>404 ya da 410 dönmesi</t>
+          <t>İşlem gerekmiyor</t>
         </is>
       </c>
     </row>
@@ -14660,53 +14656,53 @@
       <c r="A41" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="22" t="inlineStr">
-        <is>
-          <t>Soft 404 - tekrar eden sayfa</t>
+      <c r="B41" s="23" t="inlineStr">
+        <is>
+          <t>404 · kaldırılmış</t>
         </is>
       </c>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/online-alisveris</t>
+          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/turkcell-akademide-hangi-tur-egitimler-bulabilirim</t>
         </is>
       </c>
       <c r="D41" s="11" t="n">
-        <v>200</v>
+        <v>404</v>
       </c>
       <c r="E41" s="14" t="inlineStr">
         <is>
-          <t>Kendi adresi</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>index,follow</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>Turkcell Pasaj'da Online Alışveriş | Turkcell Destek</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Turkcell Pasaj</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/online-alisveris</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J41" s="19" t="n">
-        <v>1</v>
+        <v>740</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>m. alt alan adının www adresine 301 ile yönlendirilmesi: https://www.turkcell.com.tr/destek/online-alisveris</t>
+          <t>İşlem gerekmiyor</t>
         </is>
       </c>
     </row>
@@ -14721,7 +14717,7 @@
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/turkcell-akademi-nedir</t>
+          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/istedigim-egitime-nasil-kayit-yaparim</t>
         </is>
       </c>
       <c r="D42" s="11" t="n">
@@ -14753,10 +14749,10 @@
         </is>
       </c>
       <c r="J42" s="19" t="n">
-        <v>17389</v>
+        <v>580</v>
       </c>
       <c r="K42" s="19" t="n">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
@@ -14775,7 +14771,7 @@
       </c>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/bazi-egitimleri-izlemeye-calistigimda-hizli-giris-ile-giris-yapmam-isteniyor-neden</t>
+          <t>https://www.turkcell.com.tr/destek/wiyo/dask/zorunlu-deprem-sigortasi-gecerlilik-suresi-ne-kadardir</t>
         </is>
       </c>
       <c r="D43" s="11" t="n">
@@ -14807,10 +14803,10 @@
         </is>
       </c>
       <c r="J43" s="19" t="n">
-        <v>2744</v>
+        <v>287</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>481</v>
+        <v>3</v>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
@@ -14829,7 +14825,7 @@
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/coursera-nedir</t>
+          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/program-nedir</t>
         </is>
       </c>
       <c r="D44" s="11" t="n">
@@ -14861,10 +14857,10 @@
         </is>
       </c>
       <c r="J44" s="19" t="n">
-        <v>1703</v>
+        <v>150</v>
       </c>
       <c r="K44" s="19" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
@@ -14883,7 +14879,7 @@
       </c>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/turkcell-akademide-hangi-tur-egitimler-bulabilirim</t>
+          <t>https://www.turkcell.com.tr/destek/wiyo/dask/dask-zorunlu-deprem-sigortasi-nedir</t>
         </is>
       </c>
       <c r="D45" s="11" t="n">
@@ -14915,10 +14911,10 @@
         </is>
       </c>
       <c r="J45" s="19" t="n">
-        <v>740</v>
+        <v>132</v>
       </c>
       <c r="K45" s="19" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
@@ -14937,7 +14933,7 @@
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/istedigim-egitime-nasil-kayit-yaparim</t>
+          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/turkcell-akademi-ile-courseranin-nasil-bir-isbirligi-var</t>
         </is>
       </c>
       <c r="D46" s="11" t="n">
@@ -14969,10 +14965,10 @@
         </is>
       </c>
       <c r="J46" s="19" t="n">
-        <v>580</v>
+        <v>108</v>
       </c>
       <c r="K46" s="19" t="n">
-        <v>78</v>
+        <v>7</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
@@ -14991,7 +14987,7 @@
       </c>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/wiyo/dask/zorunlu-deprem-sigortasi-gecerlilik-suresi-ne-kadardir</t>
+          <t>https://www.turkcell.com.tr/destek/wiyo/dask/dask-zorunlu-deprem-sigortasi-primini-belirleyen-faktorler-nelerdir</t>
         </is>
       </c>
       <c r="D47" s="11" t="n">
@@ -15023,10 +15019,10 @@
         </is>
       </c>
       <c r="J47" s="19" t="n">
-        <v>287</v>
+        <v>90</v>
       </c>
       <c r="K47" s="19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
@@ -15045,7 +15041,7 @@
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/program-nedir</t>
+          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/coursera-egitimleri-ucretli-mi</t>
         </is>
       </c>
       <c r="D48" s="11" t="n">
@@ -15077,10 +15073,10 @@
         </is>
       </c>
       <c r="J48" s="19" t="n">
-        <v>150</v>
+        <v>26</v>
       </c>
       <c r="K48" s="19" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
@@ -15099,7 +15095,7 @@
       </c>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/wiyo/dask/dask-zorunlu-deprem-sigortasi-nedir</t>
+          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/egitime-kayit-oldum-ancak-icerikler-ingilizce-nasil-ilerlemeliyim</t>
         </is>
       </c>
       <c r="D49" s="11" t="n">
@@ -15131,10 +15127,10 @@
         </is>
       </c>
       <c r="J49" s="19" t="n">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="K49" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
@@ -15153,7 +15149,7 @@
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/turkcell-akademi-ile-courseranin-nasil-bir-isbirligi-var</t>
+          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/izleyeceklerime-ekle-nedir</t>
         </is>
       </c>
       <c r="D50" s="11" t="n">
@@ -15185,10 +15181,10 @@
         </is>
       </c>
       <c r="J50" s="19" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="K50" s="19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
@@ -15207,7 +15203,7 @@
       </c>
       <c r="C51" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/wiyo/dask/dask-zorunlu-deprem-sigortasi-primini-belirleyen-faktorler-nelerdir</t>
+          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/devam-eden-egitimler-nedir</t>
         </is>
       </c>
       <c r="D51" s="11" t="n">
@@ -15239,10 +15235,10 @@
         </is>
       </c>
       <c r="J51" s="19" t="n">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="K51" s="19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L51" s="14" t="inlineStr">
         <is>
@@ -15261,7 +15257,7 @@
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/coursera-egitimleri-ucretli-mi</t>
+          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/egitimleri-izlemek-icin-gereksinimler-nelerdir</t>
         </is>
       </c>
       <c r="D52" s="11" t="n">
@@ -15293,10 +15289,10 @@
         </is>
       </c>
       <c r="J52" s="19" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="K52" s="19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
@@ -15315,7 +15311,7 @@
       </c>
       <c r="C53" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/egitime-kayit-oldum-ancak-icerikler-ingilizce-nasil-ilerlemeliyim</t>
+          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/isaret-dili-ile-anlatim-iceren-egitimlere-nasil-ulasabilirim</t>
         </is>
       </c>
       <c r="D53" s="11" t="n">
@@ -15347,7 +15343,7 @@
         </is>
       </c>
       <c r="J53" s="19" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="K53" s="19" t="n">
         <v>1</v>
@@ -15369,7 +15365,7 @@
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/izleyeceklerime-ekle-nedir</t>
+          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/turkcell-akademi-egitimleri-veya-portaliyle-ilgili-goruslerimi-nasil-iletebilirim</t>
         </is>
       </c>
       <c r="D54" s="11" t="n">
@@ -15401,7 +15397,7 @@
         </is>
       </c>
       <c r="J54" s="19" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K54" s="19" t="n">
         <v>1</v>
@@ -15412,224 +15408,8 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="11" t="n">
-        <v>51</v>
-      </c>
-      <c r="B55" s="23" t="inlineStr">
-        <is>
-          <t>404 · kaldırılmış</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/devam-eden-egitimler-nedir</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="n">
-        <v>404</v>
-      </c>
-      <c r="E55" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G55" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I55" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="19" t="n">
-        <v>13</v>
-      </c>
-      <c r="K55" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L55" s="14" t="inlineStr">
-        <is>
-          <t>İşlem gerekmiyor</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="B56" s="23" t="inlineStr">
-        <is>
-          <t>404 · kaldırılmış</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/egitimleri-izlemek-icin-gereksinimler-nelerdir</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="n">
-        <v>404</v>
-      </c>
-      <c r="E56" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G56" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I56" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="K56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="14" t="inlineStr">
-        <is>
-          <t>İşlem gerekmiyor</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="B57" s="23" t="inlineStr">
-        <is>
-          <t>404 · kaldırılmış</t>
-        </is>
-      </c>
-      <c r="C57" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/isaret-dili-ile-anlatim-iceren-egitimlere-nasil-ulasabilirim</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="n">
-        <v>404</v>
-      </c>
-      <c r="E57" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F57" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G57" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I57" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J57" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K57" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L57" s="14" t="inlineStr">
-        <is>
-          <t>İşlem gerekmiyor</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="n">
-        <v>54</v>
-      </c>
-      <c r="B58" s="23" t="inlineStr">
-        <is>
-          <t>404 · kaldırılmış</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="inlineStr">
-        <is>
-          <t>https://www.turkcell.com.tr/destek/turkcell-akademi/sikca-sorulan-sorular/turkcell-akademi-egitimleri-veya-portaliyle-ilgili-goruslerimi-nasil-iletebilirim</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="n">
-        <v>404</v>
-      </c>
-      <c r="E58" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I58" s="14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J58" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K58" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L58" s="14" t="inlineStr">
-        <is>
-          <t>İşlem gerekmiyor</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:L58"/>
+  <autoFilter ref="A4:L54"/>
   <mergeCells count="1">
     <mergeCell ref="A2:L2"/>
   </mergeCells>
